--- a/Import_Sample.xlsx
+++ b/Import_Sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Surya\OneDrive - Evanke\Documents\projects\customer-billing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9C3554-66E6-491E-8E92-20D01F722FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E618EA-0630-46C0-8723-311426A72A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IOP" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="771">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -2335,6 +2335,15 @@
   </si>
   <si>
     <t>12/30-12/31</t>
+  </si>
+  <si>
+    <t>kovvuri surya</t>
+  </si>
+  <si>
+    <t>venkata reddy</t>
+  </si>
+  <si>
+    <t>MD0000834177</t>
   </si>
 </sst>
 </file>
@@ -2343,8 +2352,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yy"/>
-    <numFmt numFmtId="168" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="169" formatCode="m/d"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="166" formatCode="m/d"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -3327,7 +3336,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3466,8 +3475,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="15" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3484,7 +3493,7 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3511,7 +3520,7 @@
     <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3944,7 +3953,7 @@
     <xf numFmtId="14" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3993,7 +4002,7 @@
     <xf numFmtId="14" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4216,7 +4225,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4243,14 +4252,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4288,7 +4293,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -4394,7 +4399,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4536,7 +4541,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4548,35 +4553,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AC798"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="7.5703125" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" customWidth="1"/>
-    <col min="18" max="18" width="19.42578125" customWidth="1"/>
-    <col min="19" max="19" width="27.42578125" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="8.7109375" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="24" max="28" width="8.7109375" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="8.7109375" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="45.6640625" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="15.75">
+    <row r="1" spans="1:29" ht="15.6">
       <c r="A1" s="6" t="s">
         <v>142</v>
       </c>
@@ -4676,7 +4655,7 @@
       <c r="AB2" s="21"/>
       <c r="AC2" s="21"/>
     </row>
-    <row r="3" spans="1:29" ht="15.75">
+    <row r="3" spans="1:29" ht="15.6">
       <c r="A3" s="36"/>
       <c r="B3" s="37"/>
       <c r="C3" s="38"/>
@@ -4707,7 +4686,7 @@
       <c r="AB3" s="21"/>
       <c r="AC3" s="21"/>
     </row>
-    <row r="4" spans="1:29" ht="15.75">
+    <row r="4" spans="1:29" ht="15.6">
       <c r="A4" s="54"/>
       <c r="B4" s="55"/>
       <c r="C4" s="56"/>
@@ -4808,7 +4787,7 @@
       <c r="AB6" s="21"/>
       <c r="AC6" s="21"/>
     </row>
-    <row r="7" spans="1:29" ht="15.75">
+    <row r="7" spans="1:29" ht="15.6">
       <c r="A7" s="38"/>
       <c r="B7" s="55"/>
       <c r="C7" s="56"/>
@@ -4839,7 +4818,7 @@
       <c r="AB7" s="21"/>
       <c r="AC7" s="21"/>
     </row>
-    <row r="8" spans="1:29" ht="15.75">
+    <row r="8" spans="1:29" ht="15.6">
       <c r="A8" s="91">
         <v>1</v>
       </c>
@@ -4921,7 +4900,7 @@
       <c r="AB9" s="21"/>
       <c r="AC9" s="21"/>
     </row>
-    <row r="10" spans="1:29" ht="15.75">
+    <row r="10" spans="1:29" ht="15.6">
       <c r="A10" s="105"/>
       <c r="B10" s="121">
         <v>1530677</v>
@@ -4958,7 +4937,7 @@
       <c r="AB10" s="21"/>
       <c r="AC10" s="21"/>
     </row>
-    <row r="11" spans="1:29" ht="15.75">
+    <row r="11" spans="1:29" ht="15.6">
       <c r="A11" s="105"/>
       <c r="B11" s="106"/>
       <c r="C11" s="123"/>
@@ -4991,7 +4970,7 @@
       <c r="AB11" s="21"/>
       <c r="AC11" s="21"/>
     </row>
-    <row r="12" spans="1:29" ht="15.75">
+    <row r="12" spans="1:29" ht="15.6">
       <c r="A12" s="105"/>
       <c r="B12" s="126">
         <v>28094</v>
@@ -5026,7 +5005,7 @@
       <c r="AB12" s="21"/>
       <c r="AC12" s="21"/>
     </row>
-    <row r="13" spans="1:29" ht="15.75">
+    <row r="13" spans="1:29" ht="15.6">
       <c r="A13" s="105"/>
       <c r="B13" s="132" t="s">
         <v>167</v>
@@ -5063,7 +5042,7 @@
       <c r="AB13" s="21"/>
       <c r="AC13" s="21"/>
     </row>
-    <row r="14" spans="1:29" ht="15.75">
+    <row r="14" spans="1:29" ht="15.6">
       <c r="A14" s="147">
         <v>2</v>
       </c>
@@ -5114,7 +5093,7 @@
       <c r="AB14" s="21"/>
       <c r="AC14" s="21"/>
     </row>
-    <row r="15" spans="1:29" ht="15.75">
+    <row r="15" spans="1:29" ht="15.6">
       <c r="A15" s="105"/>
       <c r="B15" s="157" t="s">
         <v>174</v>
@@ -5155,7 +5134,7 @@
       <c r="AB15" s="21"/>
       <c r="AC15" s="21"/>
     </row>
-    <row r="16" spans="1:29" ht="15.75">
+    <row r="16" spans="1:29" ht="15.6">
       <c r="A16" s="105"/>
       <c r="B16" s="161">
         <v>3158407</v>
@@ -5196,7 +5175,7 @@
       <c r="AB16" s="21"/>
       <c r="AC16" s="21"/>
     </row>
-    <row r="17" spans="1:29" ht="15.75">
+    <row r="17" spans="1:29" ht="15.6">
       <c r="A17" s="105"/>
       <c r="B17" s="162">
         <v>22762</v>
@@ -5235,7 +5214,7 @@
       <c r="AB17" s="21"/>
       <c r="AC17" s="21"/>
     </row>
-    <row r="18" spans="1:29" ht="15.75">
+    <row r="18" spans="1:29" ht="15.6">
       <c r="A18" s="105"/>
       <c r="B18" s="163"/>
       <c r="C18" s="133"/>
@@ -5270,7 +5249,7 @@
       <c r="AB18" s="21"/>
       <c r="AC18" s="21"/>
     </row>
-    <row r="19" spans="1:29" ht="15.75">
+    <row r="19" spans="1:29" ht="15.6">
       <c r="A19" s="91">
         <v>3</v>
       </c>
@@ -5317,7 +5296,7 @@
       <c r="AB19" s="21"/>
       <c r="AC19" s="21"/>
     </row>
-    <row r="20" spans="1:29" ht="15.75">
+    <row r="20" spans="1:29" ht="15.6">
       <c r="A20" s="105"/>
       <c r="B20" s="157" t="s">
         <v>183</v>
@@ -5360,7 +5339,7 @@
       <c r="AB20" s="21"/>
       <c r="AC20" s="21"/>
     </row>
-    <row r="21" spans="1:29" ht="15.75">
+    <row r="21" spans="1:29" ht="15.6">
       <c r="A21" s="105"/>
       <c r="B21" s="161">
         <v>1029782</v>
@@ -5399,7 +5378,7 @@
       <c r="AB21" s="21"/>
       <c r="AC21" s="21"/>
     </row>
-    <row r="22" spans="1:29" ht="15.75">
+    <row r="22" spans="1:29" ht="15.6">
       <c r="A22" s="105"/>
       <c r="B22" s="162">
         <v>23122</v>
@@ -5433,7 +5412,7 @@
       <c r="AB22" s="21"/>
       <c r="AC22" s="21"/>
     </row>
-    <row r="23" spans="1:29" ht="15.75">
+    <row r="23" spans="1:29" ht="15.6">
       <c r="A23" s="180"/>
       <c r="B23" s="132" t="s">
         <v>191</v>
@@ -5470,7 +5449,7 @@
       <c r="AB23" s="21"/>
       <c r="AC23" s="21"/>
     </row>
-    <row r="24" spans="1:29" ht="15.75">
+    <row r="24" spans="1:29" ht="15.6">
       <c r="A24" s="105">
         <v>4</v>
       </c>
@@ -5515,7 +5494,7 @@
       <c r="AB24" s="21"/>
       <c r="AC24" s="21"/>
     </row>
-    <row r="25" spans="1:29" ht="15.75">
+    <row r="25" spans="1:29" ht="15.6">
       <c r="A25" s="105"/>
       <c r="B25" s="195" t="s">
         <v>195</v>
@@ -5551,7 +5530,7 @@
       <c r="AB25" s="21"/>
       <c r="AC25" s="21"/>
     </row>
-    <row r="26" spans="1:29" ht="15.75">
+    <row r="26" spans="1:29" ht="15.6">
       <c r="A26" s="105"/>
       <c r="B26" s="200">
         <v>3708657</v>
@@ -5585,7 +5564,7 @@
       <c r="AB26" s="21"/>
       <c r="AC26" s="21"/>
     </row>
-    <row r="27" spans="1:29" ht="15.75">
+    <row r="27" spans="1:29" ht="15.6">
       <c r="A27" s="105"/>
       <c r="B27" s="201">
         <v>28356</v>
@@ -5619,7 +5598,7 @@
       <c r="AB27" s="21"/>
       <c r="AC27" s="21"/>
     </row>
-    <row r="28" spans="1:29" ht="15.75">
+    <row r="28" spans="1:29" ht="15.6">
       <c r="A28" s="180"/>
       <c r="B28" s="132" t="s">
         <v>198</v>
@@ -5654,7 +5633,7 @@
       <c r="AB28" s="21"/>
       <c r="AC28" s="21"/>
     </row>
-    <row r="29" spans="1:29" ht="15.75">
+    <row r="29" spans="1:29" ht="15.6">
       <c r="A29" s="105">
         <v>5</v>
       </c>
@@ -5701,7 +5680,7 @@
       <c r="AB29" s="21"/>
       <c r="AC29" s="21"/>
     </row>
-    <row r="30" spans="1:29" ht="15.75">
+    <row r="30" spans="1:29" ht="15.6">
       <c r="A30" s="105"/>
       <c r="B30" s="200">
         <v>3532874</v>
@@ -5739,7 +5718,7 @@
       <c r="AB30" s="21"/>
       <c r="AC30" s="21"/>
     </row>
-    <row r="31" spans="1:29" ht="15.75">
+    <row r="31" spans="1:29" ht="15.6">
       <c r="A31" s="105"/>
       <c r="B31" s="209" t="s">
         <v>204</v>
@@ -5807,7 +5786,7 @@
       <c r="AB32" s="21"/>
       <c r="AC32" s="21"/>
     </row>
-    <row r="33" spans="1:29" ht="15.75">
+    <row r="33" spans="1:29" ht="15.6">
       <c r="A33" s="180"/>
       <c r="B33" s="210"/>
       <c r="C33" s="203"/>
@@ -5840,7 +5819,7 @@
       <c r="AB33" s="21"/>
       <c r="AC33" s="21"/>
     </row>
-    <row r="34" spans="1:29" ht="15.75">
+    <row r="34" spans="1:29" ht="15.6">
       <c r="A34" s="105">
         <v>6</v>
       </c>
@@ -5889,7 +5868,7 @@
       <c r="AB34" s="21"/>
       <c r="AC34" s="21"/>
     </row>
-    <row r="35" spans="1:29" ht="15.75">
+    <row r="35" spans="1:29" ht="15.6">
       <c r="A35" s="105"/>
       <c r="B35" s="157" t="s">
         <v>208</v>
@@ -5928,7 +5907,7 @@
       <c r="AB35" s="21"/>
       <c r="AC35" s="21"/>
     </row>
-    <row r="36" spans="1:29" ht="15.75">
+    <row r="36" spans="1:29" ht="15.6">
       <c r="A36" s="105"/>
       <c r="B36" s="121">
         <v>2870624</v>
@@ -5967,7 +5946,7 @@
       <c r="AB36" s="21"/>
       <c r="AC36" s="21"/>
     </row>
-    <row r="37" spans="1:29" ht="15.75">
+    <row r="37" spans="1:29" ht="15.6">
       <c r="A37" s="38"/>
       <c r="B37" s="176">
         <v>24879</v>
@@ -6004,7 +5983,7 @@
       <c r="AB37" s="21"/>
       <c r="AC37" s="21"/>
     </row>
-    <row r="38" spans="1:29" ht="15.75">
+    <row r="38" spans="1:29" ht="15.6">
       <c r="A38" s="180"/>
       <c r="B38" s="132" t="s">
         <v>210</v>
@@ -6037,7 +6016,7 @@
       <c r="AB38" s="21"/>
       <c r="AC38" s="21"/>
     </row>
-    <row r="39" spans="1:29" ht="15.75">
+    <row r="39" spans="1:29" ht="15.6">
       <c r="A39" s="105">
         <v>7</v>
       </c>
@@ -6080,11 +6059,11 @@
       <c r="Z39" s="21"/>
       <c r="AA39" s="21"/>
       <c r="AB39" s="21"/>
-      <c r="AC39" s="21" t="s">
+      <c r="AC39" s="299" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="15.75">
+    <row r="40" spans="1:29" ht="15.6">
       <c r="A40" s="105"/>
       <c r="B40" s="230" t="s">
         <v>213</v>
@@ -6119,7 +6098,7 @@
       <c r="AB40" s="21"/>
       <c r="AC40" s="21"/>
     </row>
-    <row r="41" spans="1:29" ht="15.75">
+    <row r="41" spans="1:29" ht="15.6">
       <c r="A41" s="105"/>
       <c r="B41" s="231">
         <v>27450</v>
@@ -6154,7 +6133,7 @@
       <c r="AB41" s="21"/>
       <c r="AC41" s="21"/>
     </row>
-    <row r="42" spans="1:29" ht="15.75">
+    <row r="42" spans="1:29" ht="15.6">
       <c r="A42" s="105"/>
       <c r="B42" s="232"/>
       <c r="C42" s="176"/>
@@ -6185,7 +6164,7 @@
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
     </row>
-    <row r="43" spans="1:29" ht="15.75">
+    <row r="43" spans="1:29" ht="15.6">
       <c r="A43" s="105"/>
       <c r="B43" s="132" t="s">
         <v>214</v>
@@ -6218,7 +6197,7 @@
       <c r="AB43" s="21"/>
       <c r="AC43" s="21"/>
     </row>
-    <row r="44" spans="1:29" ht="15.75">
+    <row r="44" spans="1:29" ht="15.6">
       <c r="A44" s="91">
         <v>8</v>
       </c>
@@ -6265,7 +6244,7 @@
       <c r="AB44" s="21"/>
       <c r="AC44" s="21"/>
     </row>
-    <row r="45" spans="1:29" ht="15.75">
+    <row r="45" spans="1:29" ht="15.6">
       <c r="A45" s="105"/>
       <c r="B45" s="245" t="s">
         <v>218</v>
@@ -6302,7 +6281,7 @@
       <c r="AB45" s="21"/>
       <c r="AC45" s="21"/>
     </row>
-    <row r="46" spans="1:29" ht="15.75">
+    <row r="46" spans="1:29" ht="15.6">
       <c r="A46" s="105"/>
       <c r="B46" s="252">
         <v>1589643</v>
@@ -6337,7 +6316,7 @@
       <c r="AB46" s="21"/>
       <c r="AC46" s="21"/>
     </row>
-    <row r="47" spans="1:29" ht="15.75">
+    <row r="47" spans="1:29" ht="15.6">
       <c r="A47" s="105"/>
       <c r="B47" s="253">
         <v>30672</v>
@@ -6376,7 +6355,7 @@
       <c r="AB47" s="21"/>
       <c r="AC47" s="21"/>
     </row>
-    <row r="48" spans="1:29" ht="15.75">
+    <row r="48" spans="1:29" ht="15.6">
       <c r="A48" s="105"/>
       <c r="B48" s="256" t="s">
         <v>223</v>
@@ -6411,7 +6390,7 @@
       <c r="AB48" s="21"/>
       <c r="AC48" s="21"/>
     </row>
-    <row r="49" spans="1:29" ht="15.75">
+    <row r="49" spans="1:29" ht="15.6">
       <c r="A49" s="91">
         <v>9</v>
       </c>
@@ -6458,7 +6437,7 @@
       <c r="AB49" s="21"/>
       <c r="AC49" s="21"/>
     </row>
-    <row r="50" spans="1:29" ht="15.75">
+    <row r="50" spans="1:29" ht="15.6">
       <c r="A50" s="105"/>
       <c r="B50" s="261" t="s">
         <v>226</v>
@@ -6493,7 +6472,7 @@
       <c r="AB50" s="21"/>
       <c r="AC50" s="21"/>
     </row>
-    <row r="51" spans="1:29" ht="15.75">
+    <row r="51" spans="1:29" ht="15.6">
       <c r="A51" s="105"/>
       <c r="B51" s="105">
         <v>3740943</v>
@@ -6528,7 +6507,7 @@
       <c r="AB51" s="21"/>
       <c r="AC51" s="21"/>
     </row>
-    <row r="52" spans="1:29" ht="15.75">
+    <row r="52" spans="1:29" ht="15.6">
       <c r="A52" s="105"/>
       <c r="B52" s="265">
         <v>26665</v>
@@ -6563,7 +6542,7 @@
       <c r="AB52" s="21"/>
       <c r="AC52" s="21"/>
     </row>
-    <row r="53" spans="1:29" ht="15.75">
+    <row r="53" spans="1:29" ht="15.6">
       <c r="A53" s="105"/>
       <c r="B53" s="267" t="s">
         <v>228</v>
@@ -6598,7 +6577,7 @@
       <c r="AB53" s="21"/>
       <c r="AC53" s="21"/>
     </row>
-    <row r="54" spans="1:29" ht="15.75">
+    <row r="54" spans="1:29" ht="15.6">
       <c r="A54" s="91">
         <v>10</v>
       </c>
@@ -6645,7 +6624,7 @@
       <c r="AB54" s="21"/>
       <c r="AC54" s="21"/>
     </row>
-    <row r="55" spans="1:29" ht="15.75">
+    <row r="55" spans="1:29" ht="15.6">
       <c r="A55" s="105"/>
       <c r="B55" s="230" t="s">
         <v>233</v>
@@ -6682,7 +6661,7 @@
       <c r="AB55" s="21"/>
       <c r="AC55" s="21"/>
     </row>
-    <row r="56" spans="1:29" ht="15.75">
+    <row r="56" spans="1:29" ht="15.6">
       <c r="A56" s="105"/>
       <c r="B56" s="105">
         <v>1576322</v>
@@ -6719,7 +6698,7 @@
       <c r="AB56" s="21"/>
       <c r="AC56" s="21"/>
     </row>
-    <row r="57" spans="1:29" ht="15.75">
+    <row r="57" spans="1:29" ht="15.6">
       <c r="A57" s="105"/>
       <c r="B57" s="230"/>
       <c r="C57" s="176">
@@ -6756,7 +6735,7 @@
       <c r="AB57" s="21"/>
       <c r="AC57" s="21"/>
     </row>
-    <row r="58" spans="1:29" ht="15.75">
+    <row r="58" spans="1:29" ht="15.6">
       <c r="A58" s="105"/>
       <c r="B58" s="276" t="s">
         <v>240</v>
@@ -6793,7 +6772,7 @@
       <c r="AB58" s="21"/>
       <c r="AC58" s="21"/>
     </row>
-    <row r="59" spans="1:29" ht="15.75">
+    <row r="59" spans="1:29" ht="15.6">
       <c r="A59" s="91">
         <v>11</v>
       </c>
@@ -6838,7 +6817,7 @@
       <c r="AB59" s="21"/>
       <c r="AC59" s="21"/>
     </row>
-    <row r="60" spans="1:29" ht="15.75">
+    <row r="60" spans="1:29" ht="15.6">
       <c r="A60" s="105"/>
       <c r="B60" s="281" t="s">
         <v>246</v>
@@ -6875,7 +6854,7 @@
       <c r="AB60" s="21"/>
       <c r="AC60" s="21"/>
     </row>
-    <row r="61" spans="1:29" ht="15.75">
+    <row r="61" spans="1:29" ht="15.6">
       <c r="A61" s="105"/>
       <c r="B61" s="105"/>
       <c r="C61" s="38"/>
@@ -6908,7 +6887,7 @@
       <c r="AB61" s="21"/>
       <c r="AC61" s="21"/>
     </row>
-    <row r="62" spans="1:29" ht="15.75">
+    <row r="62" spans="1:29" ht="15.6">
       <c r="A62" s="105"/>
       <c r="B62" s="283">
         <v>23911</v>
@@ -6942,7 +6921,7 @@
       <c r="AB62" s="21"/>
       <c r="AC62" s="21"/>
     </row>
-    <row r="63" spans="1:29" ht="15.75">
+    <row r="63" spans="1:29" ht="15.6">
       <c r="A63" s="105"/>
       <c r="B63" s="284" t="s">
         <v>249</v>
@@ -6977,7 +6956,7 @@
       <c r="AB63" s="21"/>
       <c r="AC63" s="21"/>
     </row>
-    <row r="64" spans="1:29" ht="15.75">
+    <row r="64" spans="1:29" ht="15.6">
       <c r="A64" s="91">
         <v>12</v>
       </c>
@@ -7028,7 +7007,7 @@
       <c r="AB64" s="21"/>
       <c r="AC64" s="21"/>
     </row>
-    <row r="65" spans="1:29" ht="15.75">
+    <row r="65" spans="1:29" ht="15.6">
       <c r="A65" s="105"/>
       <c r="B65" s="295" t="s">
         <v>252</v>
@@ -7067,7 +7046,7 @@
       <c r="AB65" s="21"/>
       <c r="AC65" s="21"/>
     </row>
-    <row r="66" spans="1:29" ht="15.75">
+    <row r="66" spans="1:29" ht="15.6">
       <c r="A66" s="105"/>
       <c r="B66" s="298"/>
       <c r="C66" s="38"/>
@@ -7104,7 +7083,7 @@
       <c r="AB66" s="21"/>
       <c r="AC66" s="21"/>
     </row>
-    <row r="67" spans="1:29" ht="15.75">
+    <row r="67" spans="1:29" ht="15.6">
       <c r="A67" s="105"/>
       <c r="B67" s="298">
         <v>24128</v>
@@ -7143,7 +7122,7 @@
       <c r="AB67" s="21"/>
       <c r="AC67" s="21"/>
     </row>
-    <row r="68" spans="1:29" ht="15.75">
+    <row r="68" spans="1:29" ht="15.6">
       <c r="A68" s="105"/>
       <c r="B68" s="300" t="s">
         <v>254</v>
@@ -7178,7 +7157,7 @@
       <c r="AB68" s="21"/>
       <c r="AC68" s="21"/>
     </row>
-    <row r="69" spans="1:29" ht="15.75">
+    <row r="69" spans="1:29" ht="15.6">
       <c r="A69" s="91">
         <v>13</v>
       </c>
@@ -7223,7 +7202,7 @@
       <c r="AB69" s="21"/>
       <c r="AC69" s="21"/>
     </row>
-    <row r="70" spans="1:29" ht="15.75">
+    <row r="70" spans="1:29" ht="15.6">
       <c r="A70" s="105"/>
       <c r="B70" s="306" t="s">
         <v>257</v>
@@ -7289,7 +7268,7 @@
       <c r="AB71" s="21"/>
       <c r="AC71" s="21"/>
     </row>
-    <row r="72" spans="1:29" ht="15.75">
+    <row r="72" spans="1:29" ht="15.6">
       <c r="A72" s="105"/>
       <c r="B72" s="310">
         <v>29234</v>
@@ -7322,7 +7301,7 @@
       <c r="AB72" s="21"/>
       <c r="AC72" s="21"/>
     </row>
-    <row r="73" spans="1:29" ht="15.75">
+    <row r="73" spans="1:29" ht="15.6">
       <c r="A73" s="105"/>
       <c r="B73" s="311" t="s">
         <v>258</v>
@@ -7355,7 +7334,7 @@
       <c r="AB73" s="21"/>
       <c r="AC73" s="21"/>
     </row>
-    <row r="74" spans="1:29" ht="15.75">
+    <row r="74" spans="1:29" ht="15.6">
       <c r="A74" s="56">
         <v>14</v>
       </c>
@@ -7400,7 +7379,7 @@
       <c r="AB74" s="21"/>
       <c r="AC74" s="21"/>
     </row>
-    <row r="75" spans="1:29" ht="15.75">
+    <row r="75" spans="1:29" ht="15.6">
       <c r="A75" s="38"/>
       <c r="B75" s="230" t="s">
         <v>261</v>
@@ -7435,7 +7414,7 @@
       <c r="AB75" s="21"/>
       <c r="AC75" s="21"/>
     </row>
-    <row r="76" spans="1:29" ht="15.75">
+    <row r="76" spans="1:29" ht="15.6">
       <c r="A76" s="105"/>
       <c r="B76" s="247"/>
       <c r="C76" s="330"/>
@@ -7466,7 +7445,7 @@
       <c r="AB76" s="21"/>
       <c r="AC76" s="21"/>
     </row>
-    <row r="77" spans="1:29" ht="15.75">
+    <row r="77" spans="1:29" ht="15.6">
       <c r="A77" s="105"/>
       <c r="B77" s="310">
         <v>28005</v>
@@ -7499,7 +7478,7 @@
       <c r="AB77" s="21"/>
       <c r="AC77" s="21"/>
     </row>
-    <row r="78" spans="1:29" ht="15.75">
+    <row r="78" spans="1:29" ht="15.6">
       <c r="A78" s="105"/>
       <c r="B78" s="338" t="s">
         <v>263</v>
@@ -7532,7 +7511,7 @@
       <c r="AB78" s="21"/>
       <c r="AC78" s="21"/>
     </row>
-    <row r="79" spans="1:29" ht="15.75">
+    <row r="79" spans="1:29" ht="15.6">
       <c r="A79" s="91">
         <v>15</v>
       </c>
@@ -7583,7 +7562,7 @@
       <c r="AB79" s="21"/>
       <c r="AC79" s="21"/>
     </row>
-    <row r="80" spans="1:29" ht="15.75">
+    <row r="80" spans="1:29" ht="15.6">
       <c r="A80" s="105"/>
       <c r="B80" s="195" t="s">
         <v>267</v>
@@ -7624,7 +7603,7 @@
       <c r="AB80" s="21"/>
       <c r="AC80" s="21"/>
     </row>
-    <row r="81" spans="1:29" ht="15.75">
+    <row r="81" spans="1:29" ht="15.6">
       <c r="A81" s="105"/>
       <c r="B81" s="121"/>
       <c r="C81" s="38"/>
@@ -7663,7 +7642,7 @@
       <c r="AB81" s="21"/>
       <c r="AC81" s="21"/>
     </row>
-    <row r="82" spans="1:29" ht="15.75">
+    <row r="82" spans="1:29" ht="15.6">
       <c r="A82" s="105"/>
       <c r="B82" s="352">
         <v>21007</v>
@@ -7701,7 +7680,7 @@
       <c r="AB82" s="21"/>
       <c r="AC82" s="21"/>
     </row>
-    <row r="83" spans="1:29" ht="15.75">
+    <row r="83" spans="1:29" ht="15.6">
       <c r="A83" s="105"/>
       <c r="B83" s="353" t="s">
         <v>273</v>
@@ -7736,7 +7715,7 @@
       <c r="AB83" s="21"/>
       <c r="AC83" s="21"/>
     </row>
-    <row r="84" spans="1:29" ht="15.75">
+    <row r="84" spans="1:29" ht="15.6">
       <c r="A84" s="91">
         <v>16</v>
       </c>
@@ -7785,7 +7764,7 @@
       <c r="AB84" s="21"/>
       <c r="AC84" s="21"/>
     </row>
-    <row r="85" spans="1:29" ht="15.75">
+    <row r="85" spans="1:29" ht="15.6">
       <c r="A85" s="105"/>
       <c r="B85" s="359" t="s">
         <v>277</v>
@@ -7824,7 +7803,7 @@
       <c r="AB85" s="21"/>
       <c r="AC85" s="21"/>
     </row>
-    <row r="86" spans="1:29" ht="15.75">
+    <row r="86" spans="1:29" ht="15.6">
       <c r="A86" s="105"/>
       <c r="B86" s="121"/>
       <c r="C86" s="105"/>
@@ -7859,7 +7838,7 @@
       <c r="AB86" s="21"/>
       <c r="AC86" s="21"/>
     </row>
-    <row r="87" spans="1:29" ht="15.75">
+    <row r="87" spans="1:29" ht="15.6">
       <c r="A87" s="105"/>
       <c r="B87" s="231">
         <v>32825</v>
@@ -7894,7 +7873,7 @@
       <c r="AB87" s="21"/>
       <c r="AC87" s="21"/>
     </row>
-    <row r="88" spans="1:29" ht="15.75">
+    <row r="88" spans="1:29" ht="15.6">
       <c r="A88" s="105"/>
       <c r="B88" s="353" t="s">
         <v>280</v>
@@ -7927,7 +7906,7 @@
       <c r="AB88" s="21"/>
       <c r="AC88" s="21"/>
     </row>
-    <row r="89" spans="1:29" ht="15.75">
+    <row r="89" spans="1:29" ht="15.6">
       <c r="A89" s="91">
         <v>17</v>
       </c>
@@ -7978,7 +7957,7 @@
       <c r="AB89" s="21"/>
       <c r="AC89" s="21"/>
     </row>
-    <row r="90" spans="1:29" ht="15.75">
+    <row r="90" spans="1:29" ht="15.6">
       <c r="A90" s="38"/>
       <c r="B90" s="195" t="s">
         <v>284</v>
@@ -8021,7 +8000,7 @@
       <c r="AB90" s="21"/>
       <c r="AC90" s="21"/>
     </row>
-    <row r="91" spans="1:29" ht="15.75">
+    <row r="91" spans="1:29" ht="15.6">
       <c r="A91" s="105"/>
       <c r="B91" s="364"/>
       <c r="C91" s="160"/>
@@ -8060,7 +8039,7 @@
       <c r="AB91" s="21"/>
       <c r="AC91" s="21"/>
     </row>
-    <row r="92" spans="1:29" ht="15.75">
+    <row r="92" spans="1:29" ht="15.6">
       <c r="A92" s="105"/>
       <c r="B92" s="364">
         <v>25746</v>
@@ -8095,7 +8074,7 @@
       <c r="AB92" s="21"/>
       <c r="AC92" s="21"/>
     </row>
-    <row r="93" spans="1:29" ht="15.75">
+    <row r="93" spans="1:29" ht="15.6">
       <c r="A93" s="105"/>
       <c r="B93" s="353" t="s">
         <v>289</v>
@@ -8128,7 +8107,7 @@
       <c r="AB93" s="21"/>
       <c r="AC93" s="21"/>
     </row>
-    <row r="94" spans="1:29" ht="15.75">
+    <row r="94" spans="1:29" ht="15.6">
       <c r="A94" s="91">
         <v>18</v>
       </c>
@@ -8179,7 +8158,7 @@
       <c r="AB94" s="21"/>
       <c r="AC94" s="21"/>
     </row>
-    <row r="95" spans="1:29" ht="15.75">
+    <row r="95" spans="1:29" ht="15.6">
       <c r="A95" s="105"/>
       <c r="B95" s="230" t="s">
         <v>292</v>
@@ -8222,7 +8201,7 @@
       <c r="AB95" s="21"/>
       <c r="AC95" s="21"/>
     </row>
-    <row r="96" spans="1:29" ht="15.75">
+    <row r="96" spans="1:29" ht="15.6">
       <c r="A96" s="105"/>
       <c r="B96" s="105"/>
       <c r="C96" s="373"/>
@@ -8261,7 +8240,7 @@
       <c r="AB96" s="21"/>
       <c r="AC96" s="21"/>
     </row>
-    <row r="97" spans="1:29" ht="15.75">
+    <row r="97" spans="1:29" ht="15.6">
       <c r="A97" s="105"/>
       <c r="B97" s="298">
         <v>23540</v>
@@ -8296,7 +8275,7 @@
       <c r="AB97" s="21"/>
       <c r="AC97" s="21"/>
     </row>
-    <row r="98" spans="1:29" ht="15.75">
+    <row r="98" spans="1:29" ht="15.6">
       <c r="A98" s="105"/>
       <c r="B98" s="338" t="s">
         <v>293</v>
@@ -8329,7 +8308,7 @@
       <c r="AB98" s="21"/>
       <c r="AC98" s="21"/>
     </row>
-    <row r="99" spans="1:29" ht="15.75">
+    <row r="99" spans="1:29" ht="15.6">
       <c r="A99" s="91">
         <v>19</v>
       </c>
@@ -8378,7 +8357,7 @@
       <c r="AB99" s="21"/>
       <c r="AC99" s="21"/>
     </row>
-    <row r="100" spans="1:29" ht="15.75">
+    <row r="100" spans="1:29" ht="15.6">
       <c r="A100" s="105"/>
       <c r="B100" s="230" t="s">
         <v>296</v>
@@ -8417,7 +8396,7 @@
       <c r="AB100" s="21"/>
       <c r="AC100" s="21"/>
     </row>
-    <row r="101" spans="1:29" ht="15.75">
+    <row r="101" spans="1:29" ht="15.6">
       <c r="A101" s="105"/>
       <c r="B101" s="247"/>
       <c r="C101" s="330"/>
@@ -8454,7 +8433,7 @@
       <c r="AB101" s="21"/>
       <c r="AC101" s="21"/>
     </row>
-    <row r="102" spans="1:29" ht="15.75">
+    <row r="102" spans="1:29" ht="15.6">
       <c r="A102" s="105"/>
       <c r="B102" s="310">
         <v>31153</v>
@@ -8493,7 +8472,7 @@
       <c r="AB102" s="21"/>
       <c r="AC102" s="21"/>
     </row>
-    <row r="103" spans="1:29" ht="15.75">
+    <row r="103" spans="1:29" ht="15.6">
       <c r="A103" s="105"/>
       <c r="B103" s="338" t="s">
         <v>300</v>
@@ -8526,7 +8505,7 @@
       <c r="AB103" s="21"/>
       <c r="AC103" s="21"/>
     </row>
-    <row r="104" spans="1:29" ht="15.75">
+    <row r="104" spans="1:29" ht="15.6">
       <c r="A104" s="91">
         <v>20</v>
       </c>
@@ -8575,7 +8554,7 @@
       <c r="AB104" s="21"/>
       <c r="AC104" s="21"/>
     </row>
-    <row r="105" spans="1:29" ht="15.75">
+    <row r="105" spans="1:29" ht="15.6">
       <c r="A105" s="105"/>
       <c r="B105" s="295" t="s">
         <v>304</v>
@@ -8614,7 +8593,7 @@
       <c r="AB105" s="21"/>
       <c r="AC105" s="21"/>
     </row>
-    <row r="106" spans="1:29" ht="15.75">
+    <row r="106" spans="1:29" ht="15.6">
       <c r="A106" s="38"/>
       <c r="B106" s="105"/>
       <c r="C106" s="373"/>
@@ -8649,7 +8628,7 @@
       <c r="AB106" s="21"/>
       <c r="AC106" s="21"/>
     </row>
-    <row r="107" spans="1:29" ht="15.75">
+    <row r="107" spans="1:29" ht="15.6">
       <c r="A107" s="38"/>
       <c r="B107" s="298">
         <v>28328</v>
@@ -8686,7 +8665,7 @@
       <c r="AB107" s="21"/>
       <c r="AC107" s="21"/>
     </row>
-    <row r="108" spans="1:29" ht="15.75">
+    <row r="108" spans="1:29" ht="15.6">
       <c r="A108" s="38"/>
       <c r="B108" s="392" t="s">
         <v>307</v>
@@ -8719,7 +8698,7 @@
       <c r="AB108" s="21"/>
       <c r="AC108" s="21"/>
     </row>
-    <row r="109" spans="1:29" ht="15.75">
+    <row r="109" spans="1:29" ht="15.6">
       <c r="A109" s="92">
         <v>21</v>
       </c>
@@ -8764,7 +8743,7 @@
       <c r="AB109" s="21"/>
       <c r="AC109" s="21"/>
     </row>
-    <row r="110" spans="1:29" ht="15.75">
+    <row r="110" spans="1:29" ht="15.6">
       <c r="A110" s="200"/>
       <c r="B110" s="359" t="s">
         <v>309</v>
@@ -8797,7 +8776,7 @@
       <c r="AB110" s="21"/>
       <c r="AC110" s="21"/>
     </row>
-    <row r="111" spans="1:29" ht="15.75">
+    <row r="111" spans="1:29" ht="15.6">
       <c r="A111" s="200"/>
       <c r="B111" s="121"/>
       <c r="C111" s="105"/>
@@ -8828,7 +8807,7 @@
       <c r="AB111" s="21"/>
       <c r="AC111" s="21"/>
     </row>
-    <row r="112" spans="1:29" ht="15.75">
+    <row r="112" spans="1:29" ht="15.6">
       <c r="A112" s="121"/>
       <c r="B112" s="231">
         <v>36120</v>
@@ -8861,7 +8840,7 @@
       <c r="AB112" s="21"/>
       <c r="AC112" s="21"/>
     </row>
-    <row r="113" spans="1:29" ht="15.75">
+    <row r="113" spans="1:29" ht="15.6">
       <c r="A113" s="121"/>
       <c r="B113" s="399" t="s">
         <v>310</v>
@@ -8894,7 +8873,7 @@
       <c r="AB113" s="21"/>
       <c r="AC113" s="21"/>
     </row>
-    <row r="114" spans="1:29" ht="15.75">
+    <row r="114" spans="1:29" ht="15.6">
       <c r="A114" s="92">
         <v>22</v>
       </c>
@@ -8943,7 +8922,7 @@
       <c r="AB114" s="21"/>
       <c r="AC114" s="21"/>
     </row>
-    <row r="115" spans="1:29" ht="15.75">
+    <row r="115" spans="1:29" ht="15.6">
       <c r="A115" s="105"/>
       <c r="B115" s="295" t="s">
         <v>312</v>
@@ -8982,7 +8961,7 @@
       <c r="AB115" s="21"/>
       <c r="AC115" s="21"/>
     </row>
-    <row r="116" spans="1:29" ht="15.75">
+    <row r="116" spans="1:29" ht="15.6">
       <c r="A116" s="38"/>
       <c r="B116" s="247"/>
       <c r="C116" s="330"/>
@@ -9017,7 +8996,7 @@
       <c r="AB116" s="21"/>
       <c r="AC116" s="21"/>
     </row>
-    <row r="117" spans="1:29" ht="15.75">
+    <row r="117" spans="1:29" ht="15.6">
       <c r="A117" s="38"/>
       <c r="B117" s="310">
         <v>34377</v>
@@ -9054,7 +9033,7 @@
       <c r="AB117" s="21"/>
       <c r="AC117" s="21"/>
     </row>
-    <row r="118" spans="1:29" ht="15.75">
+    <row r="118" spans="1:29" ht="15.6">
       <c r="A118" s="38"/>
       <c r="B118" s="338" t="s">
         <v>314</v>
@@ -9087,7 +9066,7 @@
       <c r="AB118" s="21"/>
       <c r="AC118" s="21"/>
     </row>
-    <row r="119" spans="1:29" ht="15.75">
+    <row r="119" spans="1:29" ht="15.6">
       <c r="A119" s="91">
         <v>23</v>
       </c>
@@ -9136,7 +9115,7 @@
       <c r="AB119" s="21"/>
       <c r="AC119" s="21"/>
     </row>
-    <row r="120" spans="1:29" ht="15.75">
+    <row r="120" spans="1:29" ht="15.6">
       <c r="A120" s="38"/>
       <c r="B120" s="359" t="s">
         <v>316</v>
@@ -9171,7 +9150,7 @@
       <c r="AB120" s="21"/>
       <c r="AC120" s="21"/>
     </row>
-    <row r="121" spans="1:29" ht="15.75">
+    <row r="121" spans="1:29" ht="15.6">
       <c r="A121" s="38"/>
       <c r="B121" s="121"/>
       <c r="C121" s="105"/>
@@ -9206,7 +9185,7 @@
       <c r="AB121" s="21"/>
       <c r="AC121" s="21"/>
     </row>
-    <row r="122" spans="1:29" ht="15.75">
+    <row r="122" spans="1:29" ht="15.6">
       <c r="A122" s="38"/>
       <c r="B122" s="231">
         <v>24192</v>
@@ -9241,7 +9220,7 @@
       <c r="AB122" s="21"/>
       <c r="AC122" s="21"/>
     </row>
-    <row r="123" spans="1:29" ht="15.75">
+    <row r="123" spans="1:29" ht="15.6">
       <c r="A123" s="38"/>
       <c r="B123" s="353" t="s">
         <v>319</v>
@@ -9274,7 +9253,7 @@
       <c r="AB123" s="21"/>
       <c r="AC123" s="21"/>
     </row>
-    <row r="124" spans="1:29" ht="15.75">
+    <row r="124" spans="1:29" ht="15.6">
       <c r="A124" s="91">
         <v>24</v>
       </c>
@@ -9323,7 +9302,7 @@
       <c r="AB124" s="21"/>
       <c r="AC124" s="21"/>
     </row>
-    <row r="125" spans="1:29" ht="15.75">
+    <row r="125" spans="1:29" ht="15.6">
       <c r="A125" s="38"/>
       <c r="B125" s="295" t="s">
         <v>321</v>
@@ -9360,7 +9339,7 @@
       <c r="AB125" s="21"/>
       <c r="AC125" s="21"/>
     </row>
-    <row r="126" spans="1:29" ht="15.75">
+    <row r="126" spans="1:29" ht="15.6">
       <c r="A126" s="38"/>
       <c r="B126" s="247"/>
       <c r="C126" s="330"/>
@@ -9395,7 +9374,7 @@
       <c r="AB126" s="21"/>
       <c r="AC126" s="21"/>
     </row>
-    <row r="127" spans="1:29" ht="15.75">
+    <row r="127" spans="1:29" ht="15.6">
       <c r="A127" s="38"/>
       <c r="B127" s="310">
         <v>30991</v>
@@ -9432,7 +9411,7 @@
       <c r="AB127" s="21"/>
       <c r="AC127" s="21"/>
     </row>
-    <row r="128" spans="1:29" ht="15.75">
+    <row r="128" spans="1:29" ht="15.6">
       <c r="A128" s="38"/>
       <c r="B128" s="300" t="s">
         <v>323</v>
@@ -9465,7 +9444,7 @@
       <c r="AB128" s="21"/>
       <c r="AC128" s="21"/>
     </row>
-    <row r="129" spans="1:29" ht="15.75">
+    <row r="129" spans="1:29" ht="15.6">
       <c r="A129" s="91">
         <v>25</v>
       </c>
@@ -9516,7 +9495,7 @@
       <c r="AB129" s="21"/>
       <c r="AC129" s="21"/>
     </row>
-    <row r="130" spans="1:29" ht="15.75">
+    <row r="130" spans="1:29" ht="15.6">
       <c r="A130" s="38"/>
       <c r="B130" s="295" t="s">
         <v>327</v>
@@ -9557,7 +9536,7 @@
       <c r="AB130" s="21"/>
       <c r="AC130" s="21"/>
     </row>
-    <row r="131" spans="1:29" ht="15.75">
+    <row r="131" spans="1:29" ht="15.6">
       <c r="A131" s="38"/>
       <c r="B131" s="105"/>
       <c r="C131" s="373"/>
@@ -9594,7 +9573,7 @@
       <c r="AB131" s="21"/>
       <c r="AC131" s="21"/>
     </row>
-    <row r="132" spans="1:29" ht="15.75">
+    <row r="132" spans="1:29" ht="15.6">
       <c r="A132" s="38"/>
       <c r="B132" s="298">
         <v>30978</v>
@@ -9633,7 +9612,7 @@
       <c r="AB132" s="21"/>
       <c r="AC132" s="21"/>
     </row>
-    <row r="133" spans="1:29" ht="15.75">
+    <row r="133" spans="1:29" ht="15.6">
       <c r="A133" s="38"/>
       <c r="B133" s="338" t="s">
         <v>332</v>
@@ -9667,7 +9646,7 @@
       <c r="AA133" s="21"/>
       <c r="AB133" s="21"/>
     </row>
-    <row r="134" spans="1:29" ht="15.75">
+    <row r="134" spans="1:29" ht="15.6">
       <c r="A134" s="92">
         <v>26</v>
       </c>
@@ -9715,7 +9694,7 @@
       <c r="AA134" s="409"/>
       <c r="AB134" s="409"/>
     </row>
-    <row r="135" spans="1:29" ht="15.75">
+    <row r="135" spans="1:29" ht="15.6">
       <c r="A135" s="38"/>
       <c r="B135" s="295" t="s">
         <v>336</v>
@@ -9755,7 +9734,7 @@
       <c r="AA135" s="21"/>
       <c r="AB135" s="21"/>
     </row>
-    <row r="136" spans="1:29" ht="15.75">
+    <row r="136" spans="1:29" ht="15.6">
       <c r="A136" s="38"/>
       <c r="B136" s="247"/>
       <c r="C136" s="247"/>
@@ -9795,7 +9774,7 @@
       <c r="AA136" s="21"/>
       <c r="AB136" s="21"/>
     </row>
-    <row r="137" spans="1:29" ht="15.75">
+    <row r="137" spans="1:29" ht="15.6">
       <c r="A137" s="38"/>
       <c r="B137" s="310">
         <v>36045</v>
@@ -9833,7 +9812,7 @@
       <c r="AA137" s="21"/>
       <c r="AB137" s="21"/>
     </row>
-    <row r="138" spans="1:29" ht="15.75">
+    <row r="138" spans="1:29" ht="15.6">
       <c r="A138" s="38"/>
       <c r="B138" s="338" t="s">
         <v>341</v>
@@ -9867,7 +9846,7 @@
       <c r="AA138" s="21"/>
       <c r="AB138" s="21"/>
     </row>
-    <row r="139" spans="1:29" ht="15.75">
+    <row r="139" spans="1:29" ht="15.6">
       <c r="A139" s="91">
         <v>27</v>
       </c>
@@ -9907,7 +9886,7 @@
       <c r="AA139" s="21"/>
       <c r="AB139" s="21"/>
     </row>
-    <row r="140" spans="1:29" ht="15.75">
+    <row r="140" spans="1:29" ht="15.6">
       <c r="A140" s="38"/>
       <c r="B140" s="295" t="s">
         <v>343</v>
@@ -9939,7 +9918,7 @@
       <c r="AA140" s="21"/>
       <c r="AB140" s="21"/>
     </row>
-    <row r="141" spans="1:29" ht="15.75">
+    <row r="141" spans="1:29" ht="15.6">
       <c r="A141" s="38"/>
       <c r="B141" s="247"/>
       <c r="C141" s="247"/>
@@ -9969,7 +9948,7 @@
       <c r="AA141" s="21"/>
       <c r="AB141" s="21"/>
     </row>
-    <row r="142" spans="1:29" ht="15.75">
+    <row r="142" spans="1:29" ht="15.6">
       <c r="A142" s="105"/>
       <c r="B142" s="310">
         <v>26190</v>
@@ -10001,7 +9980,7 @@
       <c r="AA142" s="21"/>
       <c r="AB142" s="21"/>
     </row>
-    <row r="143" spans="1:29" ht="15.75">
+    <row r="143" spans="1:29" ht="15.6">
       <c r="A143" s="105"/>
       <c r="B143" s="338" t="s">
         <v>344</v>
@@ -10033,7 +10012,7 @@
       <c r="AA143" s="21"/>
       <c r="AB143" s="21"/>
     </row>
-    <row r="144" spans="1:29" ht="15.75">
+    <row r="144" spans="1:29" ht="15.6">
       <c r="A144" s="91">
         <v>28</v>
       </c>
@@ -10077,7 +10056,7 @@
       <c r="AA144" s="21"/>
       <c r="AB144" s="21"/>
     </row>
-    <row r="145" spans="1:29" ht="15.75">
+    <row r="145" spans="1:29" ht="15.6">
       <c r="A145" s="105"/>
       <c r="B145" s="106" t="s">
         <v>347</v>
@@ -10109,7 +10088,7 @@
       <c r="AA145" s="21"/>
       <c r="AB145" s="21"/>
     </row>
-    <row r="146" spans="1:29" ht="15.75">
+    <row r="146" spans="1:29" ht="15.6">
       <c r="A146" s="38"/>
       <c r="B146" s="247"/>
       <c r="C146" s="247"/>
@@ -10139,7 +10118,7 @@
       <c r="AA146" s="21"/>
       <c r="AB146" s="21"/>
     </row>
-    <row r="147" spans="1:29" ht="15.75">
+    <row r="147" spans="1:29" ht="15.6">
       <c r="A147" s="38"/>
       <c r="B147" s="310">
         <v>28305</v>
@@ -10171,7 +10150,7 @@
       <c r="AA147" s="21"/>
       <c r="AB147" s="21"/>
     </row>
-    <row r="148" spans="1:29" ht="15.75">
+    <row r="148" spans="1:29" ht="15.6">
       <c r="A148" s="38"/>
       <c r="B148" s="338" t="s">
         <v>348</v>
@@ -10203,7 +10182,7 @@
       <c r="AA148" s="413"/>
       <c r="AB148" s="413"/>
     </row>
-    <row r="149" spans="1:29" ht="15.75">
+    <row r="149" spans="1:29" ht="15.6">
       <c r="A149" s="91">
         <v>29</v>
       </c>
@@ -10253,7 +10232,7 @@
       <c r="AA149" s="21"/>
       <c r="AB149" s="21"/>
     </row>
-    <row r="150" spans="1:29" ht="15.75">
+    <row r="150" spans="1:29" ht="15.6">
       <c r="A150" s="38"/>
       <c r="B150" s="359" t="s">
         <v>351</v>
@@ -10293,7 +10272,7 @@
       <c r="AA150" s="21"/>
       <c r="AB150" s="21"/>
     </row>
-    <row r="151" spans="1:29" ht="15.75">
+    <row r="151" spans="1:29" ht="15.6">
       <c r="A151" s="38"/>
       <c r="B151" s="121"/>
       <c r="C151" s="38"/>
@@ -10332,7 +10311,7 @@
       <c r="AB151" s="21"/>
       <c r="AC151" s="21"/>
     </row>
-    <row r="152" spans="1:29" ht="15.75">
+    <row r="152" spans="1:29" ht="15.6">
       <c r="A152" s="38"/>
       <c r="B152" s="231">
         <v>34181</v>
@@ -10371,7 +10350,7 @@
       <c r="AB152" s="21"/>
       <c r="AC152" s="21"/>
     </row>
-    <row r="153" spans="1:29" ht="15.75">
+    <row r="153" spans="1:29" ht="15.6">
       <c r="A153" s="38"/>
       <c r="B153" s="353" t="s">
         <v>356</v>
@@ -10406,7 +10385,7 @@
       <c r="AB153" s="21"/>
       <c r="AC153" s="21"/>
     </row>
-    <row r="154" spans="1:29" ht="15.75">
+    <row r="154" spans="1:29" ht="15.6">
       <c r="A154" s="91">
         <v>30</v>
       </c>
@@ -10459,7 +10438,7 @@
       <c r="AB154" s="21"/>
       <c r="AC154" s="21"/>
     </row>
-    <row r="155" spans="1:29" ht="15.75">
+    <row r="155" spans="1:29" ht="15.6">
       <c r="A155" s="38"/>
       <c r="B155" s="359" t="s">
         <v>361</v>
@@ -10504,7 +10483,7 @@
       <c r="AB155" s="21"/>
       <c r="AC155" s="21"/>
     </row>
-    <row r="156" spans="1:29" ht="15.75">
+    <row r="156" spans="1:29" ht="15.6">
       <c r="A156" s="38"/>
       <c r="B156" s="121"/>
       <c r="C156" s="38"/>
@@ -10545,7 +10524,7 @@
       <c r="AB156" s="21"/>
       <c r="AC156" s="21"/>
     </row>
-    <row r="157" spans="1:29" ht="15.75">
+    <row r="157" spans="1:29" ht="15.6">
       <c r="A157" s="38"/>
       <c r="B157" s="231">
         <v>25816</v>
@@ -10586,7 +10565,7 @@
       <c r="AB157" s="21"/>
       <c r="AC157" s="21"/>
     </row>
-    <row r="158" spans="1:29" ht="15.75">
+    <row r="158" spans="1:29" ht="15.6">
       <c r="A158" s="38"/>
       <c r="B158" s="422" t="s">
         <v>367</v>
@@ -10627,7 +10606,7 @@
       <c r="AB158" s="21"/>
       <c r="AC158" s="21"/>
     </row>
-    <row r="159" spans="1:29" ht="15.75">
+    <row r="159" spans="1:29" ht="15.6">
       <c r="A159" s="105"/>
       <c r="B159" s="161"/>
       <c r="C159" s="38"/>
@@ -10662,7 +10641,7 @@
       <c r="AB159" s="21"/>
       <c r="AC159" s="21"/>
     </row>
-    <row r="160" spans="1:29" ht="15.75">
+    <row r="160" spans="1:29" ht="15.6">
       <c r="A160" s="38"/>
       <c r="B160" s="121"/>
       <c r="C160" s="38"/>
@@ -10697,7 +10676,7 @@
       <c r="AB160" s="21"/>
       <c r="AC160" s="21"/>
     </row>
-    <row r="161" spans="1:29" ht="15.75">
+    <row r="161" spans="1:29" ht="15.6">
       <c r="A161" s="38"/>
       <c r="B161" s="121"/>
       <c r="C161" s="38"/>
@@ -10730,7 +10709,7 @@
       <c r="AB161" s="21"/>
       <c r="AC161" s="21"/>
     </row>
-    <row r="162" spans="1:29" ht="15.75">
+    <row r="162" spans="1:29" ht="15.6">
       <c r="A162" s="105"/>
       <c r="B162" s="121"/>
       <c r="C162" s="38"/>
@@ -10763,7 +10742,7 @@
       <c r="AB162" s="21"/>
       <c r="AC162" s="21"/>
     </row>
-    <row r="163" spans="1:29" ht="15.75">
+    <row r="163" spans="1:29" ht="15.6">
       <c r="A163" s="105"/>
       <c r="B163" s="423"/>
       <c r="C163" s="203"/>
@@ -10800,7 +10779,7 @@
       <c r="AB163" s="21"/>
       <c r="AC163" s="21"/>
     </row>
-    <row r="164" spans="1:29" ht="15.75">
+    <row r="164" spans="1:29" ht="15.6">
       <c r="A164" s="91">
         <v>31</v>
       </c>
@@ -10849,7 +10828,7 @@
       <c r="AB164" s="21"/>
       <c r="AC164" s="21"/>
     </row>
-    <row r="165" spans="1:29" ht="15.75">
+    <row r="165" spans="1:29" ht="15.6">
       <c r="A165" s="121"/>
       <c r="B165" s="295" t="s">
         <v>374</v>
@@ -10890,7 +10869,7 @@
       <c r="AB165" s="21"/>
       <c r="AC165" s="21"/>
     </row>
-    <row r="166" spans="1:29" ht="15.75">
+    <row r="166" spans="1:29" ht="15.6">
       <c r="A166" s="121"/>
       <c r="B166" s="247"/>
       <c r="C166" s="330"/>
@@ -10925,7 +10904,7 @@
       <c r="AB166" s="21"/>
       <c r="AC166" s="21"/>
     </row>
-    <row r="167" spans="1:29" ht="15.75">
+    <row r="167" spans="1:29" ht="15.6">
       <c r="A167" s="121"/>
       <c r="B167" s="310">
         <v>20302</v>
@@ -10962,7 +10941,7 @@
       <c r="AB167" s="21"/>
       <c r="AC167" s="21"/>
     </row>
-    <row r="168" spans="1:29" ht="15.75">
+    <row r="168" spans="1:29" ht="15.6">
       <c r="A168" s="121"/>
       <c r="B168" s="436" t="s">
         <v>377</v>
@@ -10997,7 +10976,7 @@
       <c r="AB168" s="21"/>
       <c r="AC168" s="21"/>
     </row>
-    <row r="169" spans="1:29" ht="15.75">
+    <row r="169" spans="1:29" ht="15.6">
       <c r="A169" s="105"/>
       <c r="B169" s="373"/>
       <c r="C169" s="373"/>
@@ -11030,7 +11009,7 @@
       <c r="AB169" s="21"/>
       <c r="AC169" s="21"/>
     </row>
-    <row r="170" spans="1:29" ht="15.75">
+    <row r="170" spans="1:29" ht="15.6">
       <c r="A170" s="121"/>
       <c r="B170" s="105"/>
       <c r="C170" s="373"/>
@@ -11063,7 +11042,7 @@
       <c r="AB170" s="21"/>
       <c r="AC170" s="21"/>
     </row>
-    <row r="171" spans="1:29" ht="15.75">
+    <row r="171" spans="1:29" ht="15.6">
       <c r="A171" s="121"/>
       <c r="B171" s="105"/>
       <c r="C171" s="373"/>
@@ -11094,7 +11073,7 @@
       <c r="AB171" s="21"/>
       <c r="AC171" s="21"/>
     </row>
-    <row r="172" spans="1:29" ht="15.75">
+    <row r="172" spans="1:29" ht="15.6">
       <c r="A172" s="121"/>
       <c r="B172" s="105"/>
       <c r="C172" s="373"/>
@@ -11125,7 +11104,7 @@
       <c r="AB172" s="21"/>
       <c r="AC172" s="21"/>
     </row>
-    <row r="173" spans="1:29" ht="15.75">
+    <row r="173" spans="1:29" ht="15.6">
       <c r="A173" s="121"/>
       <c r="B173" s="105"/>
       <c r="C173" s="373"/>
@@ -11158,7 +11137,7 @@
       <c r="AB173" s="21"/>
       <c r="AC173" s="21"/>
     </row>
-    <row r="174" spans="1:29" ht="15.75">
+    <row r="174" spans="1:29" ht="15.6">
       <c r="A174" s="92">
         <v>32</v>
       </c>
@@ -11207,7 +11186,7 @@
       <c r="AB174" s="21"/>
       <c r="AC174" s="21"/>
     </row>
-    <row r="175" spans="1:29" ht="15.75">
+    <row r="175" spans="1:29" ht="15.6">
       <c r="A175" s="105"/>
       <c r="B175" s="359" t="s">
         <v>381</v>
@@ -11246,7 +11225,7 @@
       <c r="AB175" s="21"/>
       <c r="AC175" s="21"/>
     </row>
-    <row r="176" spans="1:29" ht="15.75">
+    <row r="176" spans="1:29" ht="15.6">
       <c r="A176" s="105"/>
       <c r="B176" s="121"/>
       <c r="C176" s="105"/>
@@ -11283,7 +11262,7 @@
       <c r="AB176" s="21"/>
       <c r="AC176" s="21"/>
     </row>
-    <row r="177" spans="1:29" ht="15.75">
+    <row r="177" spans="1:29" ht="15.6">
       <c r="A177" s="105"/>
       <c r="B177" s="231">
         <v>30252</v>
@@ -11322,7 +11301,7 @@
       <c r="AB177" s="21"/>
       <c r="AC177" s="21"/>
     </row>
-    <row r="178" spans="1:29" ht="15.75">
+    <row r="178" spans="1:29" ht="15.6">
       <c r="A178" s="105"/>
       <c r="B178" s="399" t="s">
         <v>385</v>
@@ -11357,7 +11336,7 @@
       <c r="AB178" s="21"/>
       <c r="AC178" s="21"/>
     </row>
-    <row r="179" spans="1:29" ht="15.75">
+    <row r="179" spans="1:29" ht="15.6">
       <c r="A179" s="105"/>
       <c r="B179" s="161"/>
       <c r="C179" s="105"/>
@@ -11390,7 +11369,7 @@
       <c r="AB179" s="21"/>
       <c r="AC179" s="21"/>
     </row>
-    <row r="180" spans="1:29" ht="15.75">
+    <row r="180" spans="1:29" ht="15.6">
       <c r="A180" s="121"/>
       <c r="B180" s="121"/>
       <c r="C180" s="105"/>
@@ -11423,7 +11402,7 @@
       <c r="AB180" s="21"/>
       <c r="AC180" s="21"/>
     </row>
-    <row r="181" spans="1:29" ht="15.75">
+    <row r="181" spans="1:29" ht="15.6">
       <c r="A181" s="121"/>
       <c r="B181" s="121"/>
       <c r="C181" s="105"/>
@@ -11454,7 +11433,7 @@
       <c r="AB181" s="21"/>
       <c r="AC181" s="21"/>
     </row>
-    <row r="182" spans="1:29" ht="15.75">
+    <row r="182" spans="1:29" ht="15.6">
       <c r="A182" s="121"/>
       <c r="B182" s="121"/>
       <c r="C182" s="105"/>
@@ -11485,7 +11464,7 @@
       <c r="AB182" s="21"/>
       <c r="AC182" s="21"/>
     </row>
-    <row r="183" spans="1:29" ht="15.75">
+    <row r="183" spans="1:29" ht="15.6">
       <c r="A183" s="121"/>
       <c r="B183" s="423"/>
       <c r="C183" s="180"/>
@@ -11518,7 +11497,7 @@
       <c r="AB183" s="21"/>
       <c r="AC183" s="21"/>
     </row>
-    <row r="184" spans="1:29" ht="15.75">
+    <row r="184" spans="1:29" ht="15.6">
       <c r="A184" s="91">
         <v>33</v>
       </c>
@@ -11569,7 +11548,7 @@
       <c r="AB184" s="21"/>
       <c r="AC184" s="21"/>
     </row>
-    <row r="185" spans="1:29" ht="15.75">
+    <row r="185" spans="1:29" ht="15.6">
       <c r="A185" s="121"/>
       <c r="B185" s="359" t="s">
         <v>388</v>
@@ -11610,7 +11589,7 @@
       <c r="AB185" s="21"/>
       <c r="AC185" s="21"/>
     </row>
-    <row r="186" spans="1:29" ht="15.75">
+    <row r="186" spans="1:29" ht="15.6">
       <c r="A186" s="121"/>
       <c r="B186" s="121"/>
       <c r="C186" s="38"/>
@@ -11643,7 +11622,7 @@
       <c r="AB186" s="21"/>
       <c r="AC186" s="21"/>
     </row>
-    <row r="187" spans="1:29" ht="15.75">
+    <row r="187" spans="1:29" ht="15.6">
       <c r="A187" s="121"/>
       <c r="B187" s="231">
         <v>32310</v>
@@ -11678,7 +11657,7 @@
       <c r="AB187" s="21"/>
       <c r="AC187" s="21"/>
     </row>
-    <row r="188" spans="1:29" ht="15.75">
+    <row r="188" spans="1:29" ht="15.6">
       <c r="A188" s="121"/>
       <c r="B188" s="399" t="s">
         <v>390</v>
@@ -11713,7 +11692,7 @@
       <c r="AB188" s="21"/>
       <c r="AC188" s="21"/>
     </row>
-    <row r="189" spans="1:29" ht="15.75">
+    <row r="189" spans="1:29" ht="15.6">
       <c r="A189" s="105"/>
       <c r="B189" s="161"/>
       <c r="C189" s="38"/>
@@ -11746,7 +11725,7 @@
       <c r="AB189" s="21"/>
       <c r="AC189" s="21"/>
     </row>
-    <row r="190" spans="1:29" ht="15.75">
+    <row r="190" spans="1:29" ht="15.6">
       <c r="A190" s="105"/>
       <c r="B190" s="121"/>
       <c r="C190" s="38"/>
@@ -11779,7 +11758,7 @@
       <c r="AB190" s="21"/>
       <c r="AC190" s="21"/>
     </row>
-    <row r="191" spans="1:29" ht="15.75">
+    <row r="191" spans="1:29" ht="15.6">
       <c r="A191" s="105"/>
       <c r="B191" s="121"/>
       <c r="C191" s="38"/>
@@ -11810,7 +11789,7 @@
       <c r="AB191" s="21"/>
       <c r="AC191" s="21"/>
     </row>
-    <row r="192" spans="1:29" ht="15.75">
+    <row r="192" spans="1:29" ht="15.6">
       <c r="A192" s="38"/>
       <c r="B192" s="121"/>
       <c r="C192" s="38"/>
@@ -11841,7 +11820,7 @@
       <c r="AB192" s="21"/>
       <c r="AC192" s="21"/>
     </row>
-    <row r="193" spans="1:29" ht="15.75">
+    <row r="193" spans="1:29" ht="15.6">
       <c r="A193" s="38"/>
       <c r="B193" s="121"/>
       <c r="C193" s="38"/>
@@ -11874,7 +11853,7 @@
       <c r="AB193" s="21"/>
       <c r="AC193" s="21"/>
     </row>
-    <row r="194" spans="1:29" ht="15.75">
+    <row r="194" spans="1:29" ht="15.6">
       <c r="A194" s="91">
         <v>34</v>
       </c>
@@ -11925,7 +11904,7 @@
       <c r="AB194" s="21"/>
       <c r="AC194" s="21"/>
     </row>
-    <row r="195" spans="1:29" ht="15.75">
+    <row r="195" spans="1:29" ht="15.6">
       <c r="A195" s="105"/>
       <c r="B195" s="451" t="s">
         <v>393</v>
@@ -11968,7 +11947,7 @@
       <c r="AB195" s="21"/>
       <c r="AC195" s="21"/>
     </row>
-    <row r="196" spans="1:29" ht="15.75">
+    <row r="196" spans="1:29" ht="15.6">
       <c r="A196" s="105"/>
       <c r="B196" s="451"/>
       <c r="C196" s="38"/>
@@ -12009,7 +11988,7 @@
       <c r="AB196" s="21"/>
       <c r="AC196" s="21"/>
     </row>
-    <row r="197" spans="1:29" ht="15.75">
+    <row r="197" spans="1:29" ht="15.6">
       <c r="A197" s="38"/>
       <c r="B197" s="352">
         <v>31962</v>
@@ -12053,7 +12032,7 @@
       <c r="AB197" s="21"/>
       <c r="AC197" s="21"/>
     </row>
-    <row r="198" spans="1:29" ht="15.75">
+    <row r="198" spans="1:29" ht="15.6">
       <c r="A198" s="38"/>
       <c r="B198" s="399" t="s">
         <v>398</v>
@@ -12094,7 +12073,7 @@
       <c r="AB198" s="21"/>
       <c r="AC198" s="21"/>
     </row>
-    <row r="199" spans="1:29" ht="15.75">
+    <row r="199" spans="1:29" ht="15.6">
       <c r="A199" s="105"/>
       <c r="B199" s="161"/>
       <c r="C199" s="38"/>
@@ -12135,7 +12114,7 @@
       <c r="AB199" s="21"/>
       <c r="AC199" s="21"/>
     </row>
-    <row r="200" spans="1:29" ht="15.75">
+    <row r="200" spans="1:29" ht="15.6">
       <c r="A200" s="105"/>
       <c r="B200" s="121"/>
       <c r="C200" s="38"/>
@@ -12172,7 +12151,7 @@
       <c r="AB200" s="21"/>
       <c r="AC200" s="21"/>
     </row>
-    <row r="201" spans="1:29" ht="15.75">
+    <row r="201" spans="1:29" ht="15.6">
       <c r="A201" s="105"/>
       <c r="B201" s="121"/>
       <c r="C201" s="38"/>
@@ -12205,7 +12184,7 @@
       <c r="AB201" s="21"/>
       <c r="AC201" s="21"/>
     </row>
-    <row r="202" spans="1:29" ht="15.75">
+    <row r="202" spans="1:29" ht="15.6">
       <c r="A202" s="38"/>
       <c r="B202" s="121"/>
       <c r="C202" s="38"/>
@@ -12238,7 +12217,7 @@
       <c r="AB202" s="21"/>
       <c r="AC202" s="21"/>
     </row>
-    <row r="203" spans="1:29" ht="15.75">
+    <row r="203" spans="1:29" ht="15.6">
       <c r="A203" s="38"/>
       <c r="B203" s="423"/>
       <c r="C203" s="203"/>
@@ -12271,7 +12250,7 @@
       <c r="AB203" s="21"/>
       <c r="AC203" s="21"/>
     </row>
-    <row r="204" spans="1:29" ht="15.75">
+    <row r="204" spans="1:29" ht="15.6">
       <c r="A204" s="91">
         <v>35</v>
       </c>
@@ -12318,7 +12297,7 @@
       <c r="AB204" s="21"/>
       <c r="AC204" s="21"/>
     </row>
-    <row r="205" spans="1:29" ht="15.75">
+    <row r="205" spans="1:29" ht="15.6">
       <c r="A205" s="105"/>
       <c r="B205" s="106" t="s">
         <v>406</v>
@@ -12355,7 +12334,7 @@
       <c r="AB205" s="21"/>
       <c r="AC205" s="21"/>
     </row>
-    <row r="206" spans="1:29" ht="15.75">
+    <row r="206" spans="1:29" ht="15.6">
       <c r="A206" s="105"/>
       <c r="B206" s="254"/>
       <c r="C206" s="160"/>
@@ -12390,7 +12369,7 @@
       <c r="AB206" s="21"/>
       <c r="AC206" s="21"/>
     </row>
-    <row r="207" spans="1:29" ht="15.75">
+    <row r="207" spans="1:29" ht="15.6">
       <c r="A207" s="105"/>
       <c r="B207" s="364">
         <v>25433</v>
@@ -12427,7 +12406,7 @@
       <c r="AB207" s="21"/>
       <c r="AC207" s="21"/>
     </row>
-    <row r="208" spans="1:29" ht="15.75">
+    <row r="208" spans="1:29" ht="15.6">
       <c r="A208" s="38"/>
       <c r="B208" s="461" t="s">
         <v>408</v>
@@ -12460,7 +12439,7 @@
       <c r="AB208" s="21"/>
       <c r="AC208" s="21"/>
     </row>
-    <row r="209" spans="1:29" ht="15.75">
+    <row r="209" spans="1:29" ht="15.6">
       <c r="A209" s="105"/>
       <c r="B209" s="332"/>
       <c r="C209" s="160"/>
@@ -12491,7 +12470,7 @@
       <c r="AB209" s="21"/>
       <c r="AC209" s="21"/>
     </row>
-    <row r="210" spans="1:29" ht="15.75">
+    <row r="210" spans="1:29" ht="15.6">
       <c r="A210" s="105"/>
       <c r="B210" s="459"/>
       <c r="C210" s="160"/>
@@ -12522,7 +12501,7 @@
       <c r="AB210" s="21"/>
       <c r="AC210" s="21"/>
     </row>
-    <row r="211" spans="1:29" ht="15.75">
+    <row r="211" spans="1:29" ht="15.6">
       <c r="A211" s="105"/>
       <c r="B211" s="459"/>
       <c r="C211" s="160"/>
@@ -12553,7 +12532,7 @@
       <c r="AB211" s="21"/>
       <c r="AC211" s="21"/>
     </row>
-    <row r="212" spans="1:29" ht="15.75">
+    <row r="212" spans="1:29" ht="15.6">
       <c r="A212" s="105"/>
       <c r="B212" s="459"/>
       <c r="C212" s="160"/>
@@ -12584,7 +12563,7 @@
       <c r="AB212" s="21"/>
       <c r="AC212" s="21"/>
     </row>
-    <row r="213" spans="1:29" ht="15.75">
+    <row r="213" spans="1:29" ht="15.6">
       <c r="A213" s="105"/>
       <c r="B213" s="465"/>
       <c r="C213" s="171"/>
@@ -12617,7 +12596,7 @@
       <c r="AB213" s="21"/>
       <c r="AC213" s="21"/>
     </row>
-    <row r="214" spans="1:29" ht="15.75">
+    <row r="214" spans="1:29" ht="15.6">
       <c r="A214" s="91">
         <v>36</v>
       </c>
@@ -12666,7 +12645,7 @@
       <c r="AB214" s="21"/>
       <c r="AC214" s="21"/>
     </row>
-    <row r="215" spans="1:29" ht="15.75">
+    <row r="215" spans="1:29" ht="15.6">
       <c r="A215" s="105"/>
       <c r="B215" s="470" t="s">
         <v>410</v>
@@ -12707,7 +12686,7 @@
       <c r="AB215" s="21"/>
       <c r="AC215" s="21"/>
     </row>
-    <row r="216" spans="1:29" ht="15.75">
+    <row r="216" spans="1:29" ht="15.6">
       <c r="A216" s="105"/>
       <c r="B216" s="459"/>
       <c r="C216" s="247"/>
@@ -12744,7 +12723,7 @@
       <c r="AB216" s="21"/>
       <c r="AC216" s="21"/>
     </row>
-    <row r="217" spans="1:29" ht="15.75">
+    <row r="217" spans="1:29" ht="15.6">
       <c r="A217" s="105"/>
       <c r="B217" s="364">
         <v>28926</v>
@@ -12779,7 +12758,7 @@
       <c r="AB217" s="21"/>
       <c r="AC217" s="21"/>
     </row>
-    <row r="218" spans="1:29" ht="15.75">
+    <row r="218" spans="1:29" ht="15.6">
       <c r="A218" s="105"/>
       <c r="B218" s="399" t="s">
         <v>413</v>
@@ -12814,7 +12793,7 @@
       <c r="AB218" s="21"/>
       <c r="AC218" s="21"/>
     </row>
-    <row r="219" spans="1:29" ht="15.75">
+    <row r="219" spans="1:29" ht="15.6">
       <c r="A219" s="105"/>
       <c r="B219" s="161"/>
       <c r="C219" s="38"/>
@@ -12847,7 +12826,7 @@
       <c r="AB219" s="21"/>
       <c r="AC219" s="21"/>
     </row>
-    <row r="220" spans="1:29" ht="15.75">
+    <row r="220" spans="1:29" ht="15.6">
       <c r="A220" s="105"/>
       <c r="B220" s="121"/>
       <c r="C220" s="38"/>
@@ -12880,7 +12859,7 @@
       <c r="AB220" s="21"/>
       <c r="AC220" s="21"/>
     </row>
-    <row r="221" spans="1:29" ht="15.75">
+    <row r="221" spans="1:29" ht="15.6">
       <c r="A221" s="105"/>
       <c r="B221" s="121"/>
       <c r="C221" s="38"/>
@@ -12911,7 +12890,7 @@
       <c r="AB221" s="21"/>
       <c r="AC221" s="21"/>
     </row>
-    <row r="222" spans="1:29" ht="15.75">
+    <row r="222" spans="1:29" ht="15.6">
       <c r="A222" s="105"/>
       <c r="B222" s="121"/>
       <c r="C222" s="38"/>
@@ -12942,7 +12921,7 @@
       <c r="AB222" s="21"/>
       <c r="AC222" s="21"/>
     </row>
-    <row r="223" spans="1:29" ht="15.75">
+    <row r="223" spans="1:29" ht="15.6">
       <c r="A223" s="105"/>
       <c r="B223" s="121"/>
       <c r="C223" s="38"/>
@@ -12975,7 +12954,7 @@
       <c r="AB223" s="21"/>
       <c r="AC223" s="21"/>
     </row>
-    <row r="224" spans="1:29" ht="15.75">
+    <row r="224" spans="1:29" ht="15.6">
       <c r="A224" s="91">
         <v>37</v>
       </c>
@@ -13024,7 +13003,7 @@
       <c r="AB224" s="21"/>
       <c r="AC224" s="21"/>
     </row>
-    <row r="225" spans="1:29" ht="15.75">
+    <row r="225" spans="1:29" ht="15.6">
       <c r="A225" s="105"/>
       <c r="B225" s="295" t="s">
         <v>416</v>
@@ -13063,7 +13042,7 @@
       <c r="AB225" s="21"/>
       <c r="AC225" s="21"/>
     </row>
-    <row r="226" spans="1:29" ht="15.75">
+    <row r="226" spans="1:29" ht="15.6">
       <c r="A226" s="105"/>
       <c r="B226" s="121"/>
       <c r="C226" s="38"/>
@@ -13100,7 +13079,7 @@
       <c r="AB226" s="21"/>
       <c r="AC226" s="21"/>
     </row>
-    <row r="227" spans="1:29" ht="15.75">
+    <row r="227" spans="1:29" ht="15.6">
       <c r="A227" s="105"/>
       <c r="B227" s="254">
         <v>29212</v>
@@ -13135,7 +13114,7 @@
       <c r="AB227" s="21"/>
       <c r="AC227" s="21"/>
     </row>
-    <row r="228" spans="1:29" ht="15.75">
+    <row r="228" spans="1:29" ht="15.6">
       <c r="A228" s="474"/>
       <c r="B228" s="475" t="s">
         <v>419</v>
@@ -13170,7 +13149,7 @@
       <c r="AB228" s="21"/>
       <c r="AC228" s="21"/>
     </row>
-    <row r="229" spans="1:29" ht="15.75">
+    <row r="229" spans="1:29" ht="15.6">
       <c r="A229" s="105"/>
       <c r="B229" s="161"/>
       <c r="C229" s="38"/>
@@ -13201,7 +13180,7 @@
       <c r="AB229" s="21"/>
       <c r="AC229" s="21"/>
     </row>
-    <row r="230" spans="1:29" ht="15.75">
+    <row r="230" spans="1:29" ht="15.6">
       <c r="A230" s="105"/>
       <c r="B230" s="121"/>
       <c r="C230" s="38"/>
@@ -13232,7 +13211,7 @@
       <c r="AB230" s="21"/>
       <c r="AC230" s="21"/>
     </row>
-    <row r="231" spans="1:29" ht="15.75">
+    <row r="231" spans="1:29" ht="15.6">
       <c r="A231" s="105"/>
       <c r="B231" s="121"/>
       <c r="C231" s="38"/>
@@ -13263,7 +13242,7 @@
       <c r="AB231" s="21"/>
       <c r="AC231" s="21"/>
     </row>
-    <row r="232" spans="1:29" ht="15.75">
+    <row r="232" spans="1:29" ht="15.6">
       <c r="A232" s="105"/>
       <c r="B232" s="121"/>
       <c r="C232" s="38"/>
@@ -13294,7 +13273,7 @@
       <c r="AB232" s="21"/>
       <c r="AC232" s="21"/>
     </row>
-    <row r="233" spans="1:29" ht="15.75">
+    <row r="233" spans="1:29" ht="15.6">
       <c r="A233" s="105"/>
       <c r="B233" s="423"/>
       <c r="C233" s="203"/>
@@ -13327,7 +13306,7 @@
       <c r="AB233" s="21"/>
       <c r="AC233" s="21"/>
     </row>
-    <row r="234" spans="1:29" ht="15.75">
+    <row r="234" spans="1:29" ht="15.6">
       <c r="A234" s="91">
         <v>38</v>
       </c>
@@ -13368,7 +13347,7 @@
       <c r="AB234" s="21"/>
       <c r="AC234" s="21"/>
     </row>
-    <row r="235" spans="1:29" ht="15.75">
+    <row r="235" spans="1:29" ht="15.6">
       <c r="A235" s="105"/>
       <c r="B235" s="451" t="s">
         <v>422</v>
@@ -13403,7 +13382,7 @@
       <c r="AB235" s="21"/>
       <c r="AC235" s="21"/>
     </row>
-    <row r="236" spans="1:29" ht="15.75">
+    <row r="236" spans="1:29" ht="15.6">
       <c r="A236" s="105"/>
       <c r="B236" s="121"/>
       <c r="C236" s="105"/>
@@ -13434,7 +13413,7 @@
       <c r="AB236" s="21"/>
       <c r="AC236" s="21"/>
     </row>
-    <row r="237" spans="1:29" ht="15.75">
+    <row r="237" spans="1:29" ht="15.6">
       <c r="A237" s="105"/>
       <c r="B237" s="478">
         <v>23226</v>
@@ -13467,7 +13446,7 @@
       <c r="AB237" s="21"/>
       <c r="AC237" s="21"/>
     </row>
-    <row r="238" spans="1:29" ht="15.75">
+    <row r="238" spans="1:29" ht="15.6">
       <c r="A238" s="480"/>
       <c r="B238" s="481" t="s">
         <v>423</v>
@@ -13500,7 +13479,7 @@
       <c r="AB238" s="21"/>
       <c r="AC238" s="21"/>
     </row>
-    <row r="239" spans="1:29" ht="15.75">
+    <row r="239" spans="1:29" ht="15.6">
       <c r="A239" s="105"/>
       <c r="B239" s="161"/>
       <c r="C239" s="38"/>
@@ -13531,7 +13510,7 @@
       <c r="AB239" s="21"/>
       <c r="AC239" s="21"/>
     </row>
-    <row r="240" spans="1:29" ht="15.75">
+    <row r="240" spans="1:29" ht="15.6">
       <c r="A240" s="105"/>
       <c r="B240" s="359"/>
       <c r="C240" s="247"/>
@@ -13562,7 +13541,7 @@
       <c r="AB240" s="21"/>
       <c r="AC240" s="21"/>
     </row>
-    <row r="241" spans="1:29" ht="15.75">
+    <row r="241" spans="1:29" ht="15.6">
       <c r="A241" s="105"/>
       <c r="B241" s="459"/>
       <c r="C241" s="247"/>
@@ -13593,7 +13572,7 @@
       <c r="AB241" s="21"/>
       <c r="AC241" s="21"/>
     </row>
-    <row r="242" spans="1:29" ht="15.75">
+    <row r="242" spans="1:29" ht="15.6">
       <c r="A242" s="105"/>
       <c r="B242" s="364"/>
       <c r="C242" s="247"/>
@@ -13624,7 +13603,7 @@
       <c r="AB242" s="21"/>
       <c r="AC242" s="21"/>
     </row>
-    <row r="243" spans="1:29" ht="15.75">
+    <row r="243" spans="1:29" ht="15.6">
       <c r="A243" s="105"/>
       <c r="B243" s="485"/>
       <c r="C243" s="203"/>
@@ -13655,7 +13634,7 @@
       <c r="AB243" s="21"/>
       <c r="AC243" s="21"/>
     </row>
-    <row r="244" spans="1:29" ht="15.75">
+    <row r="244" spans="1:29" ht="15.6">
       <c r="A244" s="91">
         <v>39</v>
       </c>
@@ -13704,7 +13683,7 @@
       <c r="AB244" s="21"/>
       <c r="AC244" s="21"/>
     </row>
-    <row r="245" spans="1:29" ht="15.75">
+    <row r="245" spans="1:29" ht="15.6">
       <c r="A245" s="105"/>
       <c r="B245" s="359" t="s">
         <v>426</v>
@@ -13742,7 +13721,7 @@
       <c r="AB245" s="21"/>
       <c r="AC245" s="21"/>
     </row>
-    <row r="246" spans="1:29" ht="15.75">
+    <row r="246" spans="1:29" ht="15.6">
       <c r="A246" s="105"/>
       <c r="B246" s="121"/>
       <c r="C246" s="38"/>
@@ -13778,7 +13757,7 @@
       <c r="AB246" s="21"/>
       <c r="AC246" s="21"/>
     </row>
-    <row r="247" spans="1:29" ht="15.75">
+    <row r="247" spans="1:29" ht="15.6">
       <c r="A247" s="105"/>
       <c r="B247" s="231">
         <v>23792</v>
@@ -13816,7 +13795,7 @@
       <c r="AB247" s="21"/>
       <c r="AC247" s="21"/>
     </row>
-    <row r="248" spans="1:29" ht="15.75">
+    <row r="248" spans="1:29" ht="15.6">
       <c r="A248" s="474"/>
       <c r="B248" s="399" t="s">
         <v>430</v>
@@ -13852,7 +13831,7 @@
       <c r="AB248" s="21"/>
       <c r="AC248" s="21"/>
     </row>
-    <row r="249" spans="1:29" ht="15.75">
+    <row r="249" spans="1:29" ht="15.6">
       <c r="A249" s="105"/>
       <c r="B249" s="161"/>
       <c r="C249" s="38"/>
@@ -13882,7 +13861,7 @@
       <c r="AB249" s="21"/>
       <c r="AC249" s="21"/>
     </row>
-    <row r="250" spans="1:29" ht="15.75">
+    <row r="250" spans="1:29" ht="15.6">
       <c r="A250" s="105"/>
       <c r="B250" s="121"/>
       <c r="C250" s="38"/>
@@ -13912,7 +13891,7 @@
       <c r="AB250" s="21"/>
       <c r="AC250" s="21"/>
     </row>
-    <row r="251" spans="1:29" ht="15.75">
+    <row r="251" spans="1:29" ht="15.6">
       <c r="A251" s="105"/>
       <c r="B251" s="121"/>
       <c r="C251" s="38"/>
@@ -13942,7 +13921,7 @@
       <c r="AB251" s="21"/>
       <c r="AC251" s="21"/>
     </row>
-    <row r="252" spans="1:29" ht="15.75">
+    <row r="252" spans="1:29" ht="15.6">
       <c r="A252" s="105"/>
       <c r="B252" s="121"/>
       <c r="C252" s="38"/>
@@ -13972,7 +13951,7 @@
       <c r="AB252" s="21"/>
       <c r="AC252" s="21"/>
     </row>
-    <row r="253" spans="1:29" ht="15.75">
+    <row r="253" spans="1:29" ht="15.6">
       <c r="A253" s="105"/>
       <c r="B253" s="423"/>
       <c r="C253" s="203"/>
@@ -14003,7 +13982,7 @@
       <c r="AB253" s="21"/>
       <c r="AC253" s="21"/>
     </row>
-    <row r="254" spans="1:29" ht="15.75">
+    <row r="254" spans="1:29" ht="15.6">
       <c r="A254" s="91">
         <v>40</v>
       </c>
@@ -14052,7 +14031,7 @@
       <c r="AB254" s="21"/>
       <c r="AC254" s="21"/>
     </row>
-    <row r="255" spans="1:29" ht="15.75">
+    <row r="255" spans="1:29" ht="15.6">
       <c r="A255" s="105"/>
       <c r="B255" s="295" t="s">
         <v>432</v>
@@ -14093,7 +14072,7 @@
       <c r="AB255" s="21"/>
       <c r="AC255" s="21"/>
     </row>
-    <row r="256" spans="1:29" ht="15.75">
+    <row r="256" spans="1:29" ht="15.6">
       <c r="A256" s="105"/>
       <c r="B256" s="459"/>
       <c r="C256" s="247"/>
@@ -14130,7 +14109,7 @@
       <c r="AB256" s="21"/>
       <c r="AC256" s="21"/>
     </row>
-    <row r="257" spans="1:29" ht="15.75">
+    <row r="257" spans="1:29" ht="15.6">
       <c r="A257" s="105"/>
       <c r="B257" s="364">
         <v>22744</v>
@@ -14167,7 +14146,7 @@
       <c r="AB257" s="21"/>
       <c r="AC257" s="21"/>
     </row>
-    <row r="258" spans="1:29" ht="15.75">
+    <row r="258" spans="1:29" ht="15.6">
       <c r="A258" s="105"/>
       <c r="B258" s="399" t="s">
         <v>434</v>
@@ -14204,7 +14183,7 @@
       <c r="AB258" s="21"/>
       <c r="AC258" s="21"/>
     </row>
-    <row r="259" spans="1:29" ht="15.75">
+    <row r="259" spans="1:29" ht="15.6">
       <c r="A259" s="105"/>
       <c r="B259" s="161"/>
       <c r="C259" s="105"/>
@@ -14239,7 +14218,7 @@
       <c r="AB259" s="21"/>
       <c r="AC259" s="21"/>
     </row>
-    <row r="260" spans="1:29" ht="15.75">
+    <row r="260" spans="1:29" ht="15.6">
       <c r="A260" s="105"/>
       <c r="B260" s="121"/>
       <c r="C260" s="105"/>
@@ -14272,7 +14251,7 @@
       <c r="AB260" s="21"/>
       <c r="AC260" s="21"/>
     </row>
-    <row r="261" spans="1:29" ht="15.75">
+    <row r="261" spans="1:29" ht="15.6">
       <c r="A261" s="105"/>
       <c r="B261" s="121"/>
       <c r="C261" s="105"/>
@@ -14303,7 +14282,7 @@
       <c r="AB261" s="21"/>
       <c r="AC261" s="21"/>
     </row>
-    <row r="262" spans="1:29" ht="15.75">
+    <row r="262" spans="1:29" ht="15.6">
       <c r="A262" s="105"/>
       <c r="B262" s="121"/>
       <c r="C262" s="105"/>
@@ -14334,7 +14313,7 @@
       <c r="AB262" s="21"/>
       <c r="AC262" s="21"/>
     </row>
-    <row r="263" spans="1:29" ht="15.75">
+    <row r="263" spans="1:29" ht="15.6">
       <c r="A263" s="105"/>
       <c r="B263" s="121"/>
       <c r="C263" s="105"/>
@@ -14367,7 +14346,7 @@
       <c r="AB263" s="21"/>
       <c r="AC263" s="21"/>
     </row>
-    <row r="264" spans="1:29" ht="15.75">
+    <row r="264" spans="1:29" ht="15.6">
       <c r="A264" s="91">
         <v>41</v>
       </c>
@@ -14416,7 +14395,7 @@
       <c r="AB264" s="21"/>
       <c r="AC264" s="21"/>
     </row>
-    <row r="265" spans="1:29" ht="15.75">
+    <row r="265" spans="1:29" ht="15.6">
       <c r="A265" s="105"/>
       <c r="B265" s="359" t="s">
         <v>437</v>
@@ -14461,7 +14440,7 @@
       <c r="AB265" s="21"/>
       <c r="AC265" s="21"/>
     </row>
-    <row r="266" spans="1:29" ht="15.75">
+    <row r="266" spans="1:29" ht="15.6">
       <c r="B266" s="121"/>
       <c r="C266" s="38"/>
       <c r="D266" s="307"/>
@@ -14503,7 +14482,7 @@
       <c r="AB266" s="21"/>
       <c r="AC266" s="21"/>
     </row>
-    <row r="267" spans="1:29" ht="15.75">
+    <row r="267" spans="1:29" ht="15.6">
       <c r="A267" s="105"/>
       <c r="B267" s="231">
         <v>31930</v>
@@ -14546,7 +14525,7 @@
       <c r="AB267" s="21"/>
       <c r="AC267" s="21"/>
     </row>
-    <row r="268" spans="1:29" ht="15.75">
+    <row r="268" spans="1:29" ht="15.6">
       <c r="A268" s="105"/>
       <c r="B268" s="422" t="s">
         <v>442</v>
@@ -14587,7 +14566,7 @@
       <c r="AB268" s="21"/>
       <c r="AC268" s="21"/>
     </row>
-    <row r="269" spans="1:29" ht="15.75">
+    <row r="269" spans="1:29" ht="15.6">
       <c r="A269" s="105"/>
       <c r="B269" s="161"/>
       <c r="C269" s="105"/>
@@ -14626,7 +14605,7 @@
       <c r="AB269" s="21"/>
       <c r="AC269" s="21"/>
     </row>
-    <row r="270" spans="1:29" ht="15.75">
+    <row r="270" spans="1:29" ht="15.6">
       <c r="A270" s="105"/>
       <c r="B270" s="121"/>
       <c r="C270" s="105"/>
@@ -14661,7 +14640,7 @@
       <c r="AB270" s="21"/>
       <c r="AC270" s="21"/>
     </row>
-    <row r="271" spans="1:29" ht="15.75">
+    <row r="271" spans="1:29" ht="15.6">
       <c r="A271" s="105"/>
       <c r="B271" s="121"/>
       <c r="C271" s="105"/>
@@ -14692,7 +14671,7 @@
       <c r="AB271" s="21"/>
       <c r="AC271" s="21"/>
     </row>
-    <row r="272" spans="1:29" ht="15.75">
+    <row r="272" spans="1:29" ht="15.6">
       <c r="A272" s="105"/>
       <c r="B272" s="121"/>
       <c r="C272" s="105"/>
@@ -14723,7 +14702,7 @@
       <c r="AB272" s="21"/>
       <c r="AC272" s="21"/>
     </row>
-    <row r="273" spans="1:20" ht="15.75">
+    <row r="273" spans="1:20" ht="15.6">
       <c r="A273" s="121"/>
       <c r="B273" s="423"/>
       <c r="C273" s="180"/>
@@ -14747,7 +14726,7 @@
       <c r="S273" s="317"/>
       <c r="T273" s="21"/>
     </row>
-    <row r="274" spans="1:20" ht="15.75">
+    <row r="274" spans="1:20" ht="15.6">
       <c r="A274" s="91">
         <v>42</v>
       </c>
@@ -14784,7 +14763,7 @@
       </c>
       <c r="S274" s="305"/>
     </row>
-    <row r="275" spans="1:20" ht="15.75">
+    <row r="275" spans="1:20" ht="15.6">
       <c r="A275" s="105"/>
       <c r="B275" s="359" t="s">
         <v>444</v>
@@ -14813,7 +14792,7 @@
       </c>
       <c r="S275" s="247"/>
     </row>
-    <row r="276" spans="1:20" ht="15.75">
+    <row r="276" spans="1:20" ht="15.6">
       <c r="A276" s="105"/>
       <c r="B276" s="121"/>
       <c r="C276" s="105"/>
@@ -14840,7 +14819,7 @@
       </c>
       <c r="S276" s="247"/>
     </row>
-    <row r="277" spans="1:20" ht="15.75">
+    <row r="277" spans="1:20" ht="15.6">
       <c r="A277" s="105"/>
       <c r="B277" s="231">
         <v>22475</v>
@@ -14867,7 +14846,7 @@
       </c>
       <c r="S277" s="247"/>
     </row>
-    <row r="278" spans="1:20" ht="15.75">
+    <row r="278" spans="1:20" ht="15.6">
       <c r="A278" s="105"/>
       <c r="B278" s="399" t="s">
         <v>408</v>
@@ -14894,7 +14873,7 @@
       </c>
       <c r="S278" s="247"/>
     </row>
-    <row r="279" spans="1:20" ht="15.75">
+    <row r="279" spans="1:20" ht="15.6">
       <c r="A279" s="105"/>
       <c r="B279" s="161"/>
       <c r="C279" s="105"/>
@@ -14919,7 +14898,7 @@
       </c>
       <c r="S279" s="247"/>
     </row>
-    <row r="280" spans="1:20" ht="15.75">
+    <row r="280" spans="1:20" ht="15.6">
       <c r="A280" s="105"/>
       <c r="B280" s="121"/>
       <c r="C280" s="105"/>
@@ -14944,7 +14923,7 @@
       </c>
       <c r="S280" s="247"/>
     </row>
-    <row r="281" spans="1:20" ht="15.75">
+    <row r="281" spans="1:20" ht="15.6">
       <c r="A281" s="105"/>
       <c r="B281" s="121"/>
       <c r="C281" s="105"/>
@@ -14965,7 +14944,7 @@
       <c r="R281" s="223"/>
       <c r="S281" s="247"/>
     </row>
-    <row r="282" spans="1:20" ht="15.75">
+    <row r="282" spans="1:20" ht="15.6">
       <c r="A282" s="105"/>
       <c r="B282" s="121"/>
       <c r="C282" s="105"/>
@@ -14986,7 +14965,7 @@
       <c r="R282" s="223"/>
       <c r="S282" s="247"/>
     </row>
-    <row r="283" spans="1:20" ht="15.75">
+    <row r="283" spans="1:20" ht="15.6">
       <c r="A283" s="105"/>
       <c r="B283" s="423"/>
       <c r="C283" s="180"/>
@@ -15009,7 +14988,7 @@
       <c r="R283" s="445"/>
       <c r="S283" s="317"/>
     </row>
-    <row r="284" spans="1:20" ht="15.75">
+    <row r="284" spans="1:20" ht="15.6">
       <c r="A284" s="91">
         <v>43</v>
       </c>
@@ -15046,7 +15025,7 @@
       </c>
       <c r="S284" s="305"/>
     </row>
-    <row r="285" spans="1:20" ht="15.75">
+    <row r="285" spans="1:20" ht="15.6">
       <c r="A285" s="105"/>
       <c r="B285" s="359" t="s">
         <v>451</v>
@@ -15075,7 +15054,7 @@
       </c>
       <c r="S285" s="247"/>
     </row>
-    <row r="286" spans="1:20" ht="15.75">
+    <row r="286" spans="1:20" ht="15.6">
       <c r="A286" s="105"/>
       <c r="B286" s="121"/>
       <c r="C286" s="105"/>
@@ -15102,7 +15081,7 @@
       </c>
       <c r="S286" s="247"/>
     </row>
-    <row r="287" spans="1:20" ht="15.75">
+    <row r="287" spans="1:20" ht="15.6">
       <c r="A287" s="105"/>
       <c r="B287" s="231">
         <v>23290</v>
@@ -15129,7 +15108,7 @@
       </c>
       <c r="S287" s="247"/>
     </row>
-    <row r="288" spans="1:20" ht="15.75">
+    <row r="288" spans="1:20" ht="15.6">
       <c r="A288" s="121"/>
       <c r="B288" s="399" t="s">
         <v>408</v>
@@ -15156,7 +15135,7 @@
       </c>
       <c r="S288" s="247"/>
     </row>
-    <row r="289" spans="1:19" ht="15.75">
+    <row r="289" spans="1:19" ht="15.6">
       <c r="A289" s="105"/>
       <c r="B289" s="161"/>
       <c r="C289" s="105"/>
@@ -15179,7 +15158,7 @@
       </c>
       <c r="S289" s="247"/>
     </row>
-    <row r="290" spans="1:19" ht="15.75">
+    <row r="290" spans="1:19" ht="15.6">
       <c r="A290" s="105"/>
       <c r="B290" s="121"/>
       <c r="C290" s="105"/>
@@ -15202,7 +15181,7 @@
       </c>
       <c r="S290" s="247"/>
     </row>
-    <row r="291" spans="1:19" ht="15.75">
+    <row r="291" spans="1:19" ht="15.6">
       <c r="A291" s="105"/>
       <c r="B291" s="121"/>
       <c r="C291" s="105"/>
@@ -15223,7 +15202,7 @@
       <c r="R291" s="223"/>
       <c r="S291" s="247"/>
     </row>
-    <row r="292" spans="1:19" ht="15.75">
+    <row r="292" spans="1:19" ht="15.6">
       <c r="A292" s="105"/>
       <c r="B292" s="121"/>
       <c r="C292" s="105"/>
@@ -15244,7 +15223,7 @@
       <c r="R292" s="223"/>
       <c r="S292" s="247"/>
     </row>
-    <row r="293" spans="1:19" ht="15.75">
+    <row r="293" spans="1:19" ht="15.6">
       <c r="A293" s="105"/>
       <c r="B293" s="423"/>
       <c r="C293" s="180"/>
@@ -15267,7 +15246,7 @@
       <c r="R293" s="445"/>
       <c r="S293" s="317"/>
     </row>
-    <row r="294" spans="1:19" ht="15.75">
+    <row r="294" spans="1:19" ht="15.6">
       <c r="A294" s="92">
         <v>44</v>
       </c>
@@ -15306,7 +15285,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="295" spans="1:19" ht="15.75">
+    <row r="295" spans="1:19" ht="15.6">
       <c r="A295" s="105"/>
       <c r="B295" s="359" t="s">
         <v>455</v>
@@ -15337,7 +15316,7 @@
       </c>
       <c r="S295" s="247"/>
     </row>
-    <row r="296" spans="1:19" ht="15.75">
+    <row r="296" spans="1:19" ht="15.6">
       <c r="A296" s="105"/>
       <c r="B296" s="121"/>
       <c r="C296" s="105"/>
@@ -15364,7 +15343,7 @@
       </c>
       <c r="S296" s="247"/>
     </row>
-    <row r="297" spans="1:19" ht="15.75">
+    <row r="297" spans="1:19" ht="15.6">
       <c r="A297" s="105"/>
       <c r="B297" s="231">
         <v>23455</v>
@@ -15393,7 +15372,7 @@
       </c>
       <c r="S297" s="247"/>
     </row>
-    <row r="298" spans="1:19" ht="15.75">
+    <row r="298" spans="1:19" ht="15.6">
       <c r="A298" s="105"/>
       <c r="B298" s="461" t="s">
         <v>459</v>
@@ -15422,7 +15401,7 @@
       </c>
       <c r="S298" s="247"/>
     </row>
-    <row r="299" spans="1:19" ht="15.75">
+    <row r="299" spans="1:19" ht="15.6">
       <c r="A299" s="105"/>
       <c r="B299" s="161"/>
       <c r="C299" s="105"/>
@@ -15445,7 +15424,7 @@
       <c r="R299" s="223"/>
       <c r="S299" s="247"/>
     </row>
-    <row r="300" spans="1:19" ht="15.75">
+    <row r="300" spans="1:19" ht="15.6">
       <c r="A300" s="105"/>
       <c r="B300" s="121"/>
       <c r="C300" s="105"/>
@@ -15468,7 +15447,7 @@
       <c r="R300" s="223"/>
       <c r="S300" s="247"/>
     </row>
-    <row r="301" spans="1:19" ht="15.75">
+    <row r="301" spans="1:19" ht="15.6">
       <c r="A301" s="105"/>
       <c r="B301" s="121"/>
       <c r="C301" s="105"/>
@@ -15491,7 +15470,7 @@
       <c r="R301" s="223"/>
       <c r="S301" s="247"/>
     </row>
-    <row r="302" spans="1:19" ht="15.75">
+    <row r="302" spans="1:19" ht="15.6">
       <c r="A302" s="105"/>
       <c r="B302" s="121"/>
       <c r="C302" s="105"/>
@@ -15512,7 +15491,7 @@
       <c r="R302" s="223"/>
       <c r="S302" s="247"/>
     </row>
-    <row r="303" spans="1:19" ht="15.75">
+    <row r="303" spans="1:19" ht="15.6">
       <c r="A303" s="105"/>
       <c r="B303" s="423"/>
       <c r="C303" s="180"/>
@@ -15535,7 +15514,7 @@
       <c r="R303" s="445"/>
       <c r="S303" s="317"/>
     </row>
-    <row r="304" spans="1:19" ht="15.75">
+    <row r="304" spans="1:19" ht="15.6">
       <c r="A304" s="92">
         <v>45</v>
       </c>
@@ -15572,7 +15551,7 @@
       </c>
       <c r="S304" s="305"/>
     </row>
-    <row r="305" spans="1:19" ht="15.75">
+    <row r="305" spans="1:19" ht="15.6">
       <c r="A305" s="105"/>
       <c r="B305" s="359" t="s">
         <v>462</v>
@@ -15603,7 +15582,7 @@
       </c>
       <c r="S305" s="247"/>
     </row>
-    <row r="306" spans="1:19" ht="15.75">
+    <row r="306" spans="1:19" ht="15.6">
       <c r="A306" s="105"/>
       <c r="B306" s="121"/>
       <c r="C306" s="105"/>
@@ -15630,7 +15609,7 @@
       </c>
       <c r="S306" s="247"/>
     </row>
-    <row r="307" spans="1:19" ht="15.75">
+    <row r="307" spans="1:19" ht="15.6">
       <c r="A307" s="121"/>
       <c r="B307" s="231">
         <v>32670</v>
@@ -15659,7 +15638,7 @@
       </c>
       <c r="S307" s="247"/>
     </row>
-    <row r="308" spans="1:19" ht="15.75">
+    <row r="308" spans="1:19" ht="15.6">
       <c r="A308" s="105"/>
       <c r="B308" s="399" t="s">
         <v>463</v>
@@ -15686,7 +15665,7 @@
       </c>
       <c r="S308" s="247"/>
     </row>
-    <row r="309" spans="1:19" ht="15.75">
+    <row r="309" spans="1:19" ht="15.6">
       <c r="A309" s="38"/>
       <c r="B309" s="161"/>
       <c r="C309" s="105"/>
@@ -15711,7 +15690,7 @@
       </c>
       <c r="S309" s="247"/>
     </row>
-    <row r="310" spans="1:19" ht="15.75">
+    <row r="310" spans="1:19" ht="15.6">
       <c r="A310" s="105"/>
       <c r="B310" s="121"/>
       <c r="C310" s="105"/>
@@ -15736,7 +15715,7 @@
       </c>
       <c r="S310" s="247"/>
     </row>
-    <row r="311" spans="1:19" ht="15.75">
+    <row r="311" spans="1:19" ht="15.6">
       <c r="A311" s="105"/>
       <c r="B311" s="121"/>
       <c r="C311" s="105"/>
@@ -15757,7 +15736,7 @@
       <c r="R311" s="223"/>
       <c r="S311" s="247"/>
     </row>
-    <row r="312" spans="1:19" ht="15.75">
+    <row r="312" spans="1:19" ht="15.6">
       <c r="A312" s="105"/>
       <c r="B312" s="121"/>
       <c r="C312" s="105"/>
@@ -15778,7 +15757,7 @@
       <c r="R312" s="223"/>
       <c r="S312" s="247"/>
     </row>
-    <row r="313" spans="1:19" ht="15.75">
+    <row r="313" spans="1:19" ht="15.6">
       <c r="A313" s="105"/>
       <c r="B313" s="423"/>
       <c r="C313" s="180"/>
@@ -15801,7 +15780,7 @@
       <c r="R313" s="445"/>
       <c r="S313" s="317"/>
     </row>
-    <row r="314" spans="1:19" ht="15.75">
+    <row r="314" spans="1:19" ht="15.6">
       <c r="A314" s="56">
         <v>46</v>
       </c>
@@ -15840,7 +15819,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="315" spans="1:19" ht="15.75">
+    <row r="315" spans="1:19" ht="15.6">
       <c r="A315" s="105"/>
       <c r="B315" s="359" t="s">
         <v>467</v>
@@ -15869,7 +15848,7 @@
       </c>
       <c r="S315" s="247"/>
     </row>
-    <row r="316" spans="1:19" ht="15.75">
+    <row r="316" spans="1:19" ht="15.6">
       <c r="A316" s="105"/>
       <c r="B316" s="121"/>
       <c r="C316" s="105"/>
@@ -15898,7 +15877,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="317" spans="1:19" ht="15.75">
+    <row r="317" spans="1:19" ht="15.6">
       <c r="A317" s="105"/>
       <c r="B317" s="231">
         <v>25998</v>
@@ -15927,7 +15906,7 @@
       </c>
       <c r="S317" s="247"/>
     </row>
-    <row r="318" spans="1:19" ht="15.75">
+    <row r="318" spans="1:19" ht="15.6">
       <c r="A318" s="105"/>
       <c r="B318" s="399" t="s">
         <v>468</v>
@@ -15956,7 +15935,7 @@
       </c>
       <c r="S318" s="247"/>
     </row>
-    <row r="319" spans="1:19" ht="15.75">
+    <row r="319" spans="1:19" ht="15.6">
       <c r="A319" s="38"/>
       <c r="B319" s="497"/>
       <c r="C319" s="105"/>
@@ -15979,7 +15958,7 @@
       <c r="R319" s="119"/>
       <c r="S319" s="247"/>
     </row>
-    <row r="320" spans="1:19" ht="15.75">
+    <row r="320" spans="1:19" ht="15.6">
       <c r="A320" s="105"/>
       <c r="B320" s="121"/>
       <c r="C320" s="105"/>
@@ -16002,7 +15981,7 @@
       <c r="R320" s="119"/>
       <c r="S320" s="247"/>
     </row>
-    <row r="321" spans="1:19" ht="15.75">
+    <row r="321" spans="1:19" ht="15.6">
       <c r="A321" s="105"/>
       <c r="B321" s="121"/>
       <c r="C321" s="105"/>
@@ -16025,7 +16004,7 @@
       <c r="R321" s="119"/>
       <c r="S321" s="247"/>
     </row>
-    <row r="322" spans="1:19" ht="15.75">
+    <row r="322" spans="1:19" ht="15.6">
       <c r="A322" s="105"/>
       <c r="B322" s="121"/>
       <c r="C322" s="105"/>
@@ -16048,7 +16027,7 @@
       <c r="R322" s="119"/>
       <c r="S322" s="247"/>
     </row>
-    <row r="323" spans="1:19" ht="15.75">
+    <row r="323" spans="1:19" ht="15.6">
       <c r="A323" s="105"/>
       <c r="B323" s="423"/>
       <c r="C323" s="180"/>
@@ -16071,7 +16050,7 @@
       <c r="R323" s="145"/>
       <c r="S323" s="317"/>
     </row>
-    <row r="324" spans="1:19" ht="15.75">
+    <row r="324" spans="1:19" ht="15.6">
       <c r="A324" s="56">
         <v>47</v>
       </c>
@@ -16108,7 +16087,7 @@
       </c>
       <c r="S324" s="305"/>
     </row>
-    <row r="325" spans="1:19" ht="15.75">
+    <row r="325" spans="1:19" ht="15.6">
       <c r="A325" s="105"/>
       <c r="B325" s="359" t="s">
         <v>470</v>
@@ -16139,7 +16118,7 @@
       </c>
       <c r="S325" s="431"/>
     </row>
-    <row r="326" spans="1:19" ht="15.75">
+    <row r="326" spans="1:19" ht="15.6">
       <c r="A326" s="105"/>
       <c r="B326" s="121"/>
       <c r="C326" s="105"/>
@@ -16166,7 +16145,7 @@
       </c>
       <c r="S326" s="247"/>
     </row>
-    <row r="327" spans="1:19" ht="15.75">
+    <row r="327" spans="1:19" ht="15.6">
       <c r="A327" s="38"/>
       <c r="B327" s="231">
         <v>32853</v>
@@ -16195,7 +16174,7 @@
       </c>
       <c r="S327" s="247"/>
     </row>
-    <row r="328" spans="1:19" ht="15.75">
+    <row r="328" spans="1:19" ht="15.6">
       <c r="A328" s="105"/>
       <c r="B328" s="399" t="s">
         <v>471</v>
@@ -16222,7 +16201,7 @@
       </c>
       <c r="S328" s="247"/>
     </row>
-    <row r="329" spans="1:19" ht="15.75">
+    <row r="329" spans="1:19" ht="15.6">
       <c r="A329" s="38"/>
       <c r="B329" s="121"/>
       <c r="C329" s="105"/>
@@ -16247,7 +16226,7 @@
       </c>
       <c r="S329" s="160"/>
     </row>
-    <row r="330" spans="1:19" ht="15.75">
+    <row r="330" spans="1:19" ht="15.6">
       <c r="A330" s="105"/>
       <c r="B330" s="121"/>
       <c r="C330" s="105"/>
@@ -16272,7 +16251,7 @@
       </c>
       <c r="S330" s="160"/>
     </row>
-    <row r="331" spans="1:19" ht="15.75">
+    <row r="331" spans="1:19" ht="15.6">
       <c r="A331" s="200"/>
       <c r="B331" s="121"/>
       <c r="C331" s="105"/>
@@ -16293,7 +16272,7 @@
       <c r="R331" s="223"/>
       <c r="S331" s="160"/>
     </row>
-    <row r="332" spans="1:19" ht="15.75">
+    <row r="332" spans="1:19" ht="15.6">
       <c r="A332" s="200"/>
       <c r="B332" s="121"/>
       <c r="C332" s="105"/>
@@ -16314,7 +16293,7 @@
       <c r="R332" s="223"/>
       <c r="S332" s="160"/>
     </row>
-    <row r="333" spans="1:19" ht="15.75">
+    <row r="333" spans="1:19" ht="15.6">
       <c r="A333" s="121"/>
       <c r="B333" s="423"/>
       <c r="C333" s="180"/>
@@ -16337,7 +16316,7 @@
       <c r="R333" s="445"/>
       <c r="S333" s="171"/>
     </row>
-    <row r="334" spans="1:19" ht="15.75">
+    <row r="334" spans="1:19" ht="15.6">
       <c r="A334" s="56">
         <v>48</v>
       </c>
@@ -16374,7 +16353,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="335" spans="1:19" ht="15.75">
+    <row r="335" spans="1:19" ht="15.6">
       <c r="A335" s="38"/>
       <c r="B335" s="359" t="s">
         <v>475</v>
@@ -16403,7 +16382,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="336" spans="1:19" ht="15.75">
+    <row r="336" spans="1:19" ht="15.6">
       <c r="A336" s="38"/>
       <c r="B336" s="121"/>
       <c r="C336" s="105"/>
@@ -16428,7 +16407,7 @@
       </c>
       <c r="S336" s="123"/>
     </row>
-    <row r="337" spans="1:19" ht="15.75">
+    <row r="337" spans="1:19" ht="15.6">
       <c r="A337" s="38"/>
       <c r="B337" s="231">
         <v>29791</v>
@@ -16455,7 +16434,7 @@
       </c>
       <c r="S337" s="123"/>
     </row>
-    <row r="338" spans="1:19" ht="15.75">
+    <row r="338" spans="1:19" ht="15.6">
       <c r="A338" s="38"/>
       <c r="B338" s="399" t="s">
         <v>408</v>
@@ -16482,7 +16461,7 @@
       </c>
       <c r="S338" s="123"/>
     </row>
-    <row r="339" spans="1:19" ht="15.75">
+    <row r="339" spans="1:19" ht="15.6">
       <c r="A339" s="105"/>
       <c r="B339" s="161"/>
       <c r="C339" s="105"/>
@@ -16507,7 +16486,7 @@
       </c>
       <c r="S339" s="123"/>
     </row>
-    <row r="340" spans="1:19" ht="15.75">
+    <row r="340" spans="1:19" ht="15.6">
       <c r="A340" s="38"/>
       <c r="B340" s="121"/>
       <c r="C340" s="105"/>
@@ -16528,7 +16507,7 @@
       <c r="R340" s="223"/>
       <c r="S340" s="123"/>
     </row>
-    <row r="341" spans="1:19" ht="15.75">
+    <row r="341" spans="1:19" ht="15.6">
       <c r="A341" s="38"/>
       <c r="B341" s="121"/>
       <c r="C341" s="105"/>
@@ -16549,7 +16528,7 @@
       <c r="R341" s="223"/>
       <c r="S341" s="123"/>
     </row>
-    <row r="342" spans="1:19" ht="15.75">
+    <row r="342" spans="1:19" ht="15.6">
       <c r="A342" s="38"/>
       <c r="B342" s="121"/>
       <c r="C342" s="105"/>
@@ -16570,7 +16549,7 @@
       <c r="R342" s="223"/>
       <c r="S342" s="123"/>
     </row>
-    <row r="343" spans="1:19" ht="15.75">
+    <row r="343" spans="1:19" ht="15.6">
       <c r="A343" s="38"/>
       <c r="B343" s="423"/>
       <c r="C343" s="180"/>
@@ -16593,7 +16572,7 @@
       <c r="R343" s="445"/>
       <c r="S343" s="133"/>
     </row>
-    <row r="344" spans="1:19" ht="15.75">
+    <row r="344" spans="1:19" ht="15.6">
       <c r="A344" s="91">
         <v>49</v>
       </c>
@@ -16634,7 +16613,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="345" spans="1:19" ht="15.75">
+    <row r="345" spans="1:19" ht="15.6">
       <c r="A345" s="38"/>
       <c r="B345" s="359" t="s">
         <v>484</v>
@@ -16665,7 +16644,7 @@
       </c>
       <c r="S345" s="247"/>
     </row>
-    <row r="346" spans="1:19" ht="15.75">
+    <row r="346" spans="1:19" ht="15.6">
       <c r="A346" s="38"/>
       <c r="B346" s="121"/>
       <c r="C346" s="38"/>
@@ -16694,7 +16673,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="347" spans="1:19" ht="15.75">
+    <row r="347" spans="1:19" ht="15.6">
       <c r="A347" s="38"/>
       <c r="B347" s="231">
         <v>20697</v>
@@ -16723,7 +16702,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="348" spans="1:19" ht="15.75">
+    <row r="348" spans="1:19" ht="15.6">
       <c r="A348" s="38"/>
       <c r="B348" s="436" t="s">
         <v>490</v>
@@ -16750,7 +16729,7 @@
       </c>
       <c r="S348" s="123"/>
     </row>
-    <row r="349" spans="1:19" ht="15.75">
+    <row r="349" spans="1:19" ht="15.6">
       <c r="A349" s="105"/>
       <c r="B349" s="121"/>
       <c r="C349" s="105"/>
@@ -16777,7 +16756,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="350" spans="1:19" ht="15.75">
+    <row r="350" spans="1:19" ht="15.6">
       <c r="A350" s="105"/>
       <c r="B350" s="121"/>
       <c r="C350" s="105"/>
@@ -16802,7 +16781,7 @@
       </c>
       <c r="S350" s="123"/>
     </row>
-    <row r="351" spans="1:19" ht="15.75">
+    <row r="351" spans="1:19" ht="15.6">
       <c r="A351" s="38"/>
       <c r="B351" s="121"/>
       <c r="C351" s="105"/>
@@ -16823,7 +16802,7 @@
       <c r="R351" s="223"/>
       <c r="S351" s="123"/>
     </row>
-    <row r="352" spans="1:19" ht="15.75">
+    <row r="352" spans="1:19" ht="15.6">
       <c r="A352" s="38"/>
       <c r="B352" s="121"/>
       <c r="C352" s="105"/>
@@ -16844,7 +16823,7 @@
       <c r="R352" s="223"/>
       <c r="S352" s="123"/>
     </row>
-    <row r="353" spans="1:19" ht="15.75">
+    <row r="353" spans="1:19" ht="15.6">
       <c r="A353" s="38"/>
       <c r="B353" s="423"/>
       <c r="C353" s="180"/>
@@ -16867,7 +16846,7 @@
       <c r="R353" s="445"/>
       <c r="S353" s="133"/>
     </row>
-    <row r="354" spans="1:19" ht="15.75">
+    <row r="354" spans="1:19" ht="15.6">
       <c r="A354" s="91">
         <v>50</v>
       </c>
@@ -16906,7 +16885,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="355" spans="1:19" ht="15.75">
+    <row r="355" spans="1:19" ht="15.6">
       <c r="A355" s="38"/>
       <c r="B355" s="359" t="s">
         <v>495</v>
@@ -16937,7 +16916,7 @@
       </c>
       <c r="S355" s="123"/>
     </row>
-    <row r="356" spans="1:19" ht="15.75">
+    <row r="356" spans="1:19" ht="15.6">
       <c r="A356" s="38"/>
       <c r="B356" s="121"/>
       <c r="C356" s="105"/>
@@ -16966,7 +16945,7 @@
       </c>
       <c r="S356" s="123"/>
     </row>
-    <row r="357" spans="1:19" ht="15.75">
+    <row r="357" spans="1:19" ht="15.6">
       <c r="A357" s="105"/>
       <c r="B357" s="231">
         <v>30148</v>
@@ -16995,7 +16974,7 @@
       </c>
       <c r="S357" s="123"/>
     </row>
-    <row r="358" spans="1:19" ht="15.75">
+    <row r="358" spans="1:19" ht="15.6">
       <c r="A358" s="105"/>
       <c r="B358" s="399" t="s">
         <v>496</v>
@@ -17020,7 +16999,7 @@
       <c r="R358" s="223"/>
       <c r="S358" s="123"/>
     </row>
-    <row r="359" spans="1:19" ht="15.75">
+    <row r="359" spans="1:19" ht="15.6">
       <c r="A359" s="105"/>
       <c r="B359" s="161"/>
       <c r="C359" s="105"/>
@@ -17043,7 +17022,7 @@
       <c r="R359" s="223"/>
       <c r="S359" s="123"/>
     </row>
-    <row r="360" spans="1:19" ht="15.75">
+    <row r="360" spans="1:19" ht="15.6">
       <c r="A360" s="38"/>
       <c r="B360" s="121"/>
       <c r="C360" s="105"/>
@@ -17066,7 +17045,7 @@
       <c r="R360" s="223"/>
       <c r="S360" s="123"/>
     </row>
-    <row r="361" spans="1:19" ht="15.75">
+    <row r="361" spans="1:19" ht="15.6">
       <c r="A361" s="38"/>
       <c r="B361" s="121"/>
       <c r="C361" s="105"/>
@@ -17089,7 +17068,7 @@
       <c r="R361" s="223"/>
       <c r="S361" s="123"/>
     </row>
-    <row r="362" spans="1:19" ht="15.75">
+    <row r="362" spans="1:19" ht="15.6">
       <c r="A362" s="105"/>
       <c r="B362" s="121"/>
       <c r="C362" s="105"/>
@@ -17112,7 +17091,7 @@
       <c r="R362" s="223"/>
       <c r="S362" s="123"/>
     </row>
-    <row r="363" spans="1:19" ht="15.75">
+    <row r="363" spans="1:19" ht="15.6">
       <c r="A363" s="105"/>
       <c r="B363" s="423"/>
       <c r="C363" s="180"/>
@@ -17135,7 +17114,7 @@
       <c r="R363" s="445"/>
       <c r="S363" s="133"/>
     </row>
-    <row r="364" spans="1:19" ht="15.75">
+    <row r="364" spans="1:19" ht="15.6">
       <c r="A364" s="91">
         <v>51</v>
       </c>
@@ -17174,7 +17153,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="365" spans="1:19" ht="15.75">
+    <row r="365" spans="1:19" ht="15.6">
       <c r="A365" s="105"/>
       <c r="B365" s="359" t="s">
         <v>500</v>
@@ -17201,7 +17180,7 @@
       </c>
       <c r="S365" s="123"/>
     </row>
-    <row r="366" spans="1:19" ht="15.75">
+    <row r="366" spans="1:19" ht="15.6">
       <c r="A366" s="299"/>
       <c r="B366" s="121"/>
       <c r="C366" s="105"/>
@@ -17226,7 +17205,7 @@
       </c>
       <c r="S366" s="123"/>
     </row>
-    <row r="367" spans="1:19" ht="15.75">
+    <row r="367" spans="1:19" ht="15.6">
       <c r="A367" s="105"/>
       <c r="B367" s="231">
         <v>27463</v>
@@ -17253,7 +17232,7 @@
       </c>
       <c r="S367" s="123"/>
     </row>
-    <row r="368" spans="1:19" ht="15.75">
+    <row r="368" spans="1:19" ht="15.6">
       <c r="A368" s="105"/>
       <c r="B368" s="399" t="s">
         <v>501</v>
@@ -17280,7 +17259,7 @@
       </c>
       <c r="S368" s="123"/>
     </row>
-    <row r="369" spans="1:19" ht="15.75">
+    <row r="369" spans="1:19" ht="15.6">
       <c r="A369" s="105"/>
       <c r="B369" s="161"/>
       <c r="C369" s="105"/>
@@ -17305,7 +17284,7 @@
       </c>
       <c r="S369" s="123"/>
     </row>
-    <row r="370" spans="1:19" ht="15.75">
+    <row r="370" spans="1:19" ht="15.6">
       <c r="A370" s="105"/>
       <c r="B370" s="121"/>
       <c r="C370" s="105"/>
@@ -17326,7 +17305,7 @@
       <c r="R370" s="223"/>
       <c r="S370" s="123"/>
     </row>
-    <row r="371" spans="1:19" ht="15.75">
+    <row r="371" spans="1:19" ht="15.6">
       <c r="A371" s="299"/>
       <c r="B371" s="121"/>
       <c r="C371" s="105"/>
@@ -17347,7 +17326,7 @@
       <c r="R371" s="223"/>
       <c r="S371" s="123"/>
     </row>
-    <row r="372" spans="1:19" ht="15.75">
+    <row r="372" spans="1:19" ht="15.6">
       <c r="A372" s="105"/>
       <c r="B372" s="121"/>
       <c r="C372" s="105"/>
@@ -17368,7 +17347,7 @@
       <c r="R372" s="223"/>
       <c r="S372" s="123"/>
     </row>
-    <row r="373" spans="1:19" ht="15.75">
+    <row r="373" spans="1:19" ht="15.6">
       <c r="A373" s="105"/>
       <c r="B373" s="423"/>
       <c r="C373" s="180"/>
@@ -17391,7 +17370,7 @@
       <c r="R373" s="445"/>
       <c r="S373" s="133"/>
     </row>
-    <row r="374" spans="1:19" ht="15.75">
+    <row r="374" spans="1:19" ht="15.6">
       <c r="A374" s="91">
         <v>52</v>
       </c>
@@ -17430,7 +17409,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="375" spans="1:19" ht="15.75">
+    <row r="375" spans="1:19" ht="15.6">
       <c r="A375" s="38"/>
       <c r="B375" s="451" t="s">
         <v>503</v>
@@ -17460,7 +17439,7 @@
       <c r="R375" s="221"/>
       <c r="S375" s="160"/>
     </row>
-    <row r="376" spans="1:19" ht="15.75">
+    <row r="376" spans="1:19" ht="15.6">
       <c r="A376" s="38"/>
       <c r="B376" s="231"/>
       <c r="C376" s="38"/>
@@ -17484,7 +17463,7 @@
       <c r="R376" s="221"/>
       <c r="S376" s="160"/>
     </row>
-    <row r="377" spans="1:19" ht="15.75">
+    <row r="377" spans="1:19" ht="15.6">
       <c r="A377" s="38"/>
       <c r="B377" s="231">
         <v>34294</v>
@@ -17508,7 +17487,7 @@
       <c r="R377" s="221"/>
       <c r="S377" s="160"/>
     </row>
-    <row r="378" spans="1:19" ht="15.75">
+    <row r="378" spans="1:19" ht="15.6">
       <c r="A378" s="38"/>
       <c r="B378" s="436" t="s">
         <v>504</v>
@@ -17533,7 +17512,7 @@
       <c r="R378" s="221"/>
       <c r="S378" s="160"/>
     </row>
-    <row r="379" spans="1:19" ht="15.75">
+    <row r="379" spans="1:19" ht="15.6">
       <c r="A379" s="105"/>
       <c r="B379" s="105"/>
       <c r="C379" s="373"/>
@@ -17556,7 +17535,7 @@
       <c r="R379" s="221"/>
       <c r="S379" s="160"/>
     </row>
-    <row r="380" spans="1:19" ht="15.75">
+    <row r="380" spans="1:19" ht="15.6">
       <c r="A380" s="38"/>
       <c r="B380" s="105"/>
       <c r="C380" s="373"/>
@@ -17577,7 +17556,7 @@
       <c r="R380" s="221"/>
       <c r="S380" s="160"/>
     </row>
-    <row r="381" spans="1:19" ht="15.75">
+    <row r="381" spans="1:19" ht="15.6">
       <c r="A381" s="38"/>
       <c r="B381" s="105"/>
       <c r="C381" s="373"/>
@@ -17598,7 +17577,7 @@
       <c r="R381" s="221"/>
       <c r="S381" s="160"/>
     </row>
-    <row r="382" spans="1:19" ht="15.75">
+    <row r="382" spans="1:19" ht="15.6">
       <c r="A382" s="38"/>
       <c r="B382" s="105"/>
       <c r="C382" s="373"/>
@@ -17619,7 +17598,7 @@
       <c r="R382" s="221"/>
       <c r="S382" s="160"/>
     </row>
-    <row r="383" spans="1:19" ht="15.75">
+    <row r="383" spans="1:19" ht="15.6">
       <c r="A383" s="38"/>
       <c r="B383" s="180"/>
       <c r="C383" s="376"/>
@@ -17642,7 +17621,7 @@
       <c r="R383" s="426"/>
       <c r="S383" s="171"/>
     </row>
-    <row r="384" spans="1:19" ht="15.75">
+    <row r="384" spans="1:19" ht="15.6">
       <c r="A384" s="91">
         <v>53</v>
       </c>
@@ -17683,7 +17662,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="385" spans="1:19" ht="15.75">
+    <row r="385" spans="1:19" ht="15.6">
       <c r="A385" s="38"/>
       <c r="B385" s="451" t="s">
         <v>510</v>
@@ -17710,7 +17689,7 @@
       <c r="R385" s="119"/>
       <c r="S385" s="120"/>
     </row>
-    <row r="386" spans="1:19" ht="15.75">
+    <row r="386" spans="1:19" ht="15.6">
       <c r="A386" s="38"/>
       <c r="B386" s="121"/>
       <c r="C386" s="105"/>
@@ -17733,7 +17712,7 @@
       <c r="R386" s="119"/>
       <c r="S386" s="120"/>
     </row>
-    <row r="387" spans="1:19" ht="15.75">
+    <row r="387" spans="1:19" ht="15.6">
       <c r="A387" s="38"/>
       <c r="B387" s="478">
         <v>37695</v>
@@ -17758,7 +17737,7 @@
       <c r="R387" s="119"/>
       <c r="S387" s="120"/>
     </row>
-    <row r="388" spans="1:19" ht="15.75">
+    <row r="388" spans="1:19" ht="15.6">
       <c r="A388" s="105"/>
       <c r="B388" s="481" t="s">
         <v>513</v>
@@ -17783,7 +17762,7 @@
       <c r="R388" s="119"/>
       <c r="S388" s="120"/>
     </row>
-    <row r="389" spans="1:19" ht="15.75">
+    <row r="389" spans="1:19" ht="15.6">
       <c r="A389" s="38"/>
       <c r="B389" s="161"/>
       <c r="C389" s="38"/>
@@ -17804,7 +17783,7 @@
       <c r="R389" s="175"/>
       <c r="S389" s="330"/>
     </row>
-    <row r="390" spans="1:19" ht="15.75">
+    <row r="390" spans="1:19" ht="15.6">
       <c r="A390" s="38"/>
       <c r="B390" s="359"/>
       <c r="C390" s="247"/>
@@ -17825,7 +17804,7 @@
       <c r="R390" s="175"/>
       <c r="S390" s="330"/>
     </row>
-    <row r="391" spans="1:19" ht="15.75">
+    <row r="391" spans="1:19" ht="15.6">
       <c r="A391" s="38"/>
       <c r="B391" s="459"/>
       <c r="C391" s="247"/>
@@ -17846,7 +17825,7 @@
       <c r="R391" s="199"/>
       <c r="S391" s="330"/>
     </row>
-    <row r="392" spans="1:19" ht="15.75">
+    <row r="392" spans="1:19" ht="15.6">
       <c r="A392" s="38"/>
       <c r="B392" s="364"/>
       <c r="C392" s="247"/>
@@ -17867,7 +17846,7 @@
       <c r="R392" s="199"/>
       <c r="S392" s="330"/>
     </row>
-    <row r="393" spans="1:19" ht="15.75">
+    <row r="393" spans="1:19" ht="15.6">
       <c r="A393" s="105"/>
       <c r="B393" s="485"/>
       <c r="C393" s="203"/>
@@ -17956,7 +17935,7 @@
       <c r="R395" s="159"/>
       <c r="S395" s="120"/>
     </row>
-    <row r="396" spans="1:19" ht="15.75">
+    <row r="396" spans="1:19" ht="15.6">
       <c r="A396" s="105"/>
       <c r="B396" s="121"/>
       <c r="C396" s="38"/>
@@ -17979,7 +17958,7 @@
       <c r="R396" s="159"/>
       <c r="S396" s="120"/>
     </row>
-    <row r="397" spans="1:19" ht="15.75">
+    <row r="397" spans="1:19" ht="15.6">
       <c r="A397" s="105"/>
       <c r="B397" s="254">
         <v>32707</v>
@@ -18004,7 +17983,7 @@
       <c r="R397" s="159"/>
       <c r="S397" s="120"/>
     </row>
-    <row r="398" spans="1:19" ht="15.75">
+    <row r="398" spans="1:19" ht="15.6">
       <c r="A398" s="105"/>
       <c r="B398" s="461" t="s">
         <v>516</v>
@@ -18027,7 +18006,7 @@
       <c r="R398" s="159"/>
       <c r="S398" s="120"/>
     </row>
-    <row r="399" spans="1:19" ht="15.75">
+    <row r="399" spans="1:19" ht="15.6">
       <c r="A399" s="105"/>
       <c r="B399" s="161"/>
       <c r="C399" s="38"/>
@@ -18048,7 +18027,7 @@
       <c r="R399" s="159"/>
       <c r="S399" s="120"/>
     </row>
-    <row r="400" spans="1:19" ht="15.75">
+    <row r="400" spans="1:19" ht="15.6">
       <c r="A400" s="105"/>
       <c r="B400" s="121"/>
       <c r="C400" s="38"/>
@@ -18069,7 +18048,7 @@
       <c r="R400" s="159"/>
       <c r="S400" s="120"/>
     </row>
-    <row r="401" spans="1:19" ht="15.75">
+    <row r="401" spans="1:19" ht="15.6">
       <c r="A401" s="105"/>
       <c r="B401" s="121"/>
       <c r="C401" s="38"/>
@@ -18090,7 +18069,7 @@
       <c r="R401" s="159"/>
       <c r="S401" s="120"/>
     </row>
-    <row r="402" spans="1:19" ht="15.75">
+    <row r="402" spans="1:19" ht="15.6">
       <c r="A402" s="105"/>
       <c r="B402" s="121"/>
       <c r="C402" s="38"/>
@@ -18111,7 +18090,7 @@
       <c r="R402" s="159"/>
       <c r="S402" s="120"/>
     </row>
-    <row r="403" spans="1:19" ht="15.75">
+    <row r="403" spans="1:19" ht="15.6">
       <c r="A403" s="105"/>
       <c r="B403" s="121"/>
       <c r="C403" s="38"/>
@@ -18134,7 +18113,7 @@
       <c r="R403" s="159"/>
       <c r="S403" s="120"/>
     </row>
-    <row r="404" spans="1:19" ht="15.75">
+    <row r="404" spans="1:19" ht="15.6">
       <c r="A404" s="91">
         <v>55</v>
       </c>
@@ -18173,7 +18152,7 @@
       </c>
       <c r="S404" s="82"/>
     </row>
-    <row r="405" spans="1:19" ht="15.75">
+    <row r="405" spans="1:19" ht="15.6">
       <c r="A405" s="105"/>
       <c r="B405" s="451" t="s">
         <v>517</v>
@@ -18202,7 +18181,7 @@
       <c r="R405" s="215"/>
       <c r="S405" s="415"/>
     </row>
-    <row r="406" spans="1:19" ht="15.75">
+    <row r="406" spans="1:19" ht="15.6">
       <c r="A406" s="105"/>
       <c r="B406" s="121"/>
       <c r="C406" s="38"/>
@@ -18225,7 +18204,7 @@
       <c r="R406" s="215"/>
       <c r="S406" s="415"/>
     </row>
-    <row r="407" spans="1:19" ht="15.75">
+    <row r="407" spans="1:19" ht="15.6">
       <c r="A407" s="105"/>
       <c r="B407" s="231">
         <v>30127</v>
@@ -18250,7 +18229,7 @@
       <c r="R407" s="215"/>
       <c r="S407" s="415"/>
     </row>
-    <row r="408" spans="1:19" ht="15.75">
+    <row r="408" spans="1:19" ht="15.6">
       <c r="A408" s="105"/>
       <c r="B408" s="475" t="s">
         <v>518</v>
@@ -18275,7 +18254,7 @@
       <c r="R408" s="215"/>
       <c r="S408" s="415"/>
     </row>
-    <row r="409" spans="1:19" ht="15.75">
+    <row r="409" spans="1:19" ht="15.6">
       <c r="A409" s="105"/>
       <c r="B409" s="161"/>
       <c r="C409" s="38"/>
@@ -18298,7 +18277,7 @@
       <c r="R409" s="215"/>
       <c r="S409" s="415"/>
     </row>
-    <row r="410" spans="1:19" ht="15.75">
+    <row r="410" spans="1:19" ht="15.6">
       <c r="A410" s="38"/>
       <c r="B410" s="121"/>
       <c r="C410" s="38"/>
@@ -18321,7 +18300,7 @@
       <c r="R410" s="215"/>
       <c r="S410" s="415"/>
     </row>
-    <row r="411" spans="1:19" ht="15.75">
+    <row r="411" spans="1:19" ht="15.6">
       <c r="A411" s="38"/>
       <c r="B411" s="121"/>
       <c r="C411" s="38"/>
@@ -18342,7 +18321,7 @@
       <c r="R411" s="215"/>
       <c r="S411" s="415"/>
     </row>
-    <row r="412" spans="1:19" ht="15.75">
+    <row r="412" spans="1:19" ht="15.6">
       <c r="A412" s="105"/>
       <c r="B412" s="121"/>
       <c r="C412" s="38"/>
@@ -18363,7 +18342,7 @@
       <c r="R412" s="215"/>
       <c r="S412" s="415"/>
     </row>
-    <row r="413" spans="1:19" ht="15.75">
+    <row r="413" spans="1:19" ht="15.6">
       <c r="A413" s="38"/>
       <c r="B413" s="423"/>
       <c r="C413" s="203"/>
@@ -18386,7 +18365,7 @@
       <c r="R413" s="503"/>
       <c r="S413" s="416"/>
     </row>
-    <row r="414" spans="1:19" ht="15.75">
+    <row r="414" spans="1:19" ht="15.6">
       <c r="A414" s="91">
         <v>56</v>
       </c>
@@ -18423,7 +18402,7 @@
       </c>
       <c r="S414" s="147"/>
     </row>
-    <row r="415" spans="1:19" ht="15.75">
+    <row r="415" spans="1:19" ht="15.6">
       <c r="A415" s="38"/>
       <c r="B415" s="295" t="s">
         <v>520</v>
@@ -18448,7 +18427,7 @@
       <c r="R415" s="226"/>
       <c r="S415" s="247"/>
     </row>
-    <row r="416" spans="1:19" ht="15.75">
+    <row r="416" spans="1:19" ht="15.6">
       <c r="A416" s="38"/>
       <c r="B416" s="105"/>
       <c r="C416" s="299"/>
@@ -18471,7 +18450,7 @@
       <c r="R416" s="226"/>
       <c r="S416" s="247"/>
     </row>
-    <row r="417" spans="1:19" ht="15.75">
+    <row r="417" spans="1:19" ht="15.6">
       <c r="A417" s="38"/>
       <c r="B417" s="298">
         <v>30771</v>
@@ -18496,7 +18475,7 @@
       <c r="R417" s="226"/>
       <c r="S417" s="247"/>
     </row>
-    <row r="418" spans="1:19" ht="15.75">
+    <row r="418" spans="1:19" ht="15.6">
       <c r="A418" s="38"/>
       <c r="B418" s="461" t="s">
         <v>521</v>
@@ -18521,7 +18500,7 @@
       <c r="R418" s="226"/>
       <c r="S418" s="123"/>
     </row>
-    <row r="419" spans="1:19" ht="15.75">
+    <row r="419" spans="1:19" ht="15.6">
       <c r="A419" s="105"/>
       <c r="B419" s="373"/>
       <c r="C419" s="38"/>
@@ -18544,7 +18523,7 @@
       <c r="R419" s="221"/>
       <c r="S419" s="123"/>
     </row>
-    <row r="420" spans="1:19" ht="15.75">
+    <row r="420" spans="1:19" ht="15.6">
       <c r="A420" s="38"/>
       <c r="B420" s="230"/>
       <c r="C420" s="38"/>
@@ -18567,7 +18546,7 @@
       <c r="R420" s="221"/>
       <c r="S420" s="247"/>
     </row>
-    <row r="421" spans="1:19" ht="15.75">
+    <row r="421" spans="1:19" ht="15.6">
       <c r="A421" s="38"/>
       <c r="B421" s="105"/>
       <c r="C421" s="38"/>
@@ -18588,7 +18567,7 @@
       <c r="R421" s="221"/>
       <c r="S421" s="123"/>
     </row>
-    <row r="422" spans="1:19" ht="15.75">
+    <row r="422" spans="1:19" ht="15.6">
       <c r="A422" s="38"/>
       <c r="B422" s="298"/>
       <c r="C422" s="38"/>
@@ -18609,7 +18588,7 @@
       <c r="R422" s="221"/>
       <c r="S422" s="123"/>
     </row>
-    <row r="423" spans="1:19" ht="15.75">
+    <row r="423" spans="1:19" ht="15.6">
       <c r="A423" s="38"/>
       <c r="B423" s="338"/>
       <c r="C423" s="203"/>
@@ -18632,7 +18611,7 @@
       <c r="R423" s="445"/>
       <c r="S423" s="133"/>
     </row>
-    <row r="424" spans="1:19" ht="15.75">
+    <row r="424" spans="1:19" ht="15.6">
       <c r="A424" s="91">
         <v>57</v>
       </c>
@@ -18706,7 +18685,7 @@
       </c>
       <c r="S425" s="160"/>
     </row>
-    <row r="426" spans="1:19" ht="15.75">
+    <row r="426" spans="1:19" ht="15.6">
       <c r="A426" s="38"/>
       <c r="B426" s="121"/>
       <c r="C426" s="38"/>
@@ -18733,7 +18712,7 @@
       <c r="R426" s="221"/>
       <c r="S426" s="160"/>
     </row>
-    <row r="427" spans="1:19" ht="15.75">
+    <row r="427" spans="1:19" ht="15.6">
       <c r="A427" s="105"/>
       <c r="B427" s="231">
         <v>22786</v>
@@ -18758,7 +18737,7 @@
       <c r="R427" s="221"/>
       <c r="S427" s="160"/>
     </row>
-    <row r="428" spans="1:19" ht="15.75">
+    <row r="428" spans="1:19" ht="15.6">
       <c r="A428" s="105"/>
       <c r="B428" s="436" t="s">
         <v>528</v>
@@ -18785,7 +18764,7 @@
       <c r="R428" s="221"/>
       <c r="S428" s="160"/>
     </row>
-    <row r="429" spans="1:19" ht="15.75">
+    <row r="429" spans="1:19" ht="15.6">
       <c r="A429" s="105"/>
       <c r="B429" s="373"/>
       <c r="C429" s="373"/>
@@ -18808,7 +18787,7 @@
       <c r="R429" s="221"/>
       <c r="S429" s="160"/>
     </row>
-    <row r="430" spans="1:19" ht="15.75">
+    <row r="430" spans="1:19" ht="15.6">
       <c r="A430" s="200"/>
       <c r="B430" s="105"/>
       <c r="C430" s="373"/>
@@ -18831,7 +18810,7 @@
       <c r="R430" s="221"/>
       <c r="S430" s="160"/>
     </row>
-    <row r="431" spans="1:19" ht="15.75">
+    <row r="431" spans="1:19" ht="15.6">
       <c r="A431" s="200"/>
       <c r="B431" s="105"/>
       <c r="C431" s="373"/>
@@ -18854,7 +18833,7 @@
       <c r="R431" s="221"/>
       <c r="S431" s="160"/>
     </row>
-    <row r="432" spans="1:19" ht="15.75">
+    <row r="432" spans="1:19" ht="15.6">
       <c r="A432" s="121"/>
       <c r="B432" s="105"/>
       <c r="C432" s="373"/>
@@ -18877,7 +18856,7 @@
       <c r="R432" s="221"/>
       <c r="S432" s="160"/>
     </row>
-    <row r="433" spans="1:19" ht="15.75">
+    <row r="433" spans="1:19" ht="15.6">
       <c r="A433" s="121"/>
       <c r="B433" s="105"/>
       <c r="C433" s="373"/>
@@ -18902,7 +18881,7 @@
       <c r="R433" s="426"/>
       <c r="S433" s="171"/>
     </row>
-    <row r="434" spans="1:19" ht="15.75">
+    <row r="434" spans="1:19" ht="15.6">
       <c r="A434" s="92">
         <v>58</v>
       </c>
@@ -18943,7 +18922,7 @@
       </c>
       <c r="S434" s="160"/>
     </row>
-    <row r="435" spans="1:19" ht="15.75">
+    <row r="435" spans="1:19" ht="15.6">
       <c r="A435" s="105"/>
       <c r="B435" s="513" t="s">
         <v>538</v>
@@ -18978,7 +18957,7 @@
       </c>
       <c r="S435" s="160"/>
     </row>
-    <row r="436" spans="1:19" ht="15.75">
+    <row r="436" spans="1:19" ht="15.6">
       <c r="A436" s="38"/>
       <c r="B436" s="105"/>
       <c r="C436" s="38"/>
@@ -19005,7 +18984,7 @@
       <c r="R436" s="463"/>
       <c r="S436" s="160"/>
     </row>
-    <row r="437" spans="1:19" ht="15.75">
+    <row r="437" spans="1:19" ht="15.6">
       <c r="A437" s="105"/>
       <c r="B437" s="283">
         <v>36121</v>
@@ -19033,7 +19012,7 @@
       <c r="R437" s="463"/>
       <c r="S437" s="160"/>
     </row>
-    <row r="438" spans="1:19" ht="15.75">
+    <row r="438" spans="1:19" ht="15.6">
       <c r="A438" s="105"/>
       <c r="B438" s="516" t="s">
         <v>542</v>
@@ -19058,7 +19037,7 @@
       <c r="R438" s="519"/>
       <c r="S438" s="160"/>
     </row>
-    <row r="439" spans="1:19" ht="15.75">
+    <row r="439" spans="1:19" ht="15.6">
       <c r="A439" s="56">
         <v>59</v>
       </c>
@@ -19099,7 +19078,7 @@
       </c>
       <c r="S439" s="305"/>
     </row>
-    <row r="440" spans="1:19" ht="15.75">
+    <row r="440" spans="1:19" ht="15.6">
       <c r="A440" s="105"/>
       <c r="B440" s="230" t="s">
         <v>544</v>
@@ -19132,7 +19111,7 @@
       </c>
       <c r="S440" s="247"/>
     </row>
-    <row r="441" spans="1:19" ht="15.75">
+    <row r="441" spans="1:19" ht="15.6">
       <c r="A441" s="200"/>
       <c r="B441" s="247"/>
       <c r="C441" s="330"/>
@@ -19159,7 +19138,7 @@
       </c>
       <c r="S441" s="247"/>
     </row>
-    <row r="442" spans="1:19" ht="15.75">
+    <row r="442" spans="1:19" ht="15.6">
       <c r="A442" s="38"/>
       <c r="B442" s="310">
         <v>23334</v>
@@ -19184,7 +19163,7 @@
       <c r="R442" s="463"/>
       <c r="S442" s="247"/>
     </row>
-    <row r="443" spans="1:19" ht="15.75">
+    <row r="443" spans="1:19" ht="15.6">
       <c r="A443" s="38"/>
       <c r="B443" s="485" t="s">
         <v>547</v>
@@ -19207,7 +19186,7 @@
       <c r="R443" s="519"/>
       <c r="S443" s="317"/>
     </row>
-    <row r="444" spans="1:19" ht="15.75">
+    <row r="444" spans="1:19" ht="15.6">
       <c r="A444" s="56">
         <v>60</v>
       </c>
@@ -19250,7 +19229,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="445" spans="1:19" ht="15.75">
+    <row r="445" spans="1:19" ht="15.6">
       <c r="A445" s="105"/>
       <c r="B445" s="359" t="s">
         <v>549</v>
@@ -19279,7 +19258,7 @@
       </c>
       <c r="S445" s="160"/>
     </row>
-    <row r="446" spans="1:19" ht="15.75">
+    <row r="446" spans="1:19" ht="15.6">
       <c r="A446" s="38"/>
       <c r="B446" s="231"/>
       <c r="C446" s="105"/>
@@ -19302,7 +19281,7 @@
       <c r="R446" s="463"/>
       <c r="S446" s="160"/>
     </row>
-    <row r="447" spans="1:19" ht="15.75">
+    <row r="447" spans="1:19" ht="15.6">
       <c r="A447" s="105"/>
       <c r="B447" s="231">
         <v>26388</v>
@@ -19327,7 +19306,7 @@
       <c r="R447" s="463"/>
       <c r="S447" s="160"/>
     </row>
-    <row r="448" spans="1:19" ht="15.75">
+    <row r="448" spans="1:19" ht="15.6">
       <c r="A448" s="200"/>
       <c r="B448" s="353" t="s">
         <v>547</v>
@@ -19350,7 +19329,7 @@
       <c r="R448" s="519"/>
       <c r="S448" s="171"/>
     </row>
-    <row r="449" spans="1:19" ht="15.75">
+    <row r="449" spans="1:19" ht="15.6">
       <c r="A449" s="56">
         <v>61</v>
       </c>
@@ -19393,7 +19372,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="450" spans="1:19" ht="15.75">
+    <row r="450" spans="1:19" ht="15.6">
       <c r="A450" s="105"/>
       <c r="B450" s="359" t="s">
         <v>552</v>
@@ -19426,7 +19405,7 @@
       </c>
       <c r="S450" s="247"/>
     </row>
-    <row r="451" spans="1:19" ht="15.75">
+    <row r="451" spans="1:19" ht="15.6">
       <c r="A451" s="38"/>
       <c r="B451" s="121"/>
       <c r="C451" s="38"/>
@@ -19453,7 +19432,7 @@
       </c>
       <c r="S451" s="247"/>
     </row>
-    <row r="452" spans="1:19" ht="15.75">
+    <row r="452" spans="1:19" ht="15.6">
       <c r="A452" s="105"/>
       <c r="B452" s="231">
         <v>31511</v>
@@ -19480,7 +19459,7 @@
       </c>
       <c r="S452" s="247"/>
     </row>
-    <row r="453" spans="1:19" ht="15.75">
+    <row r="453" spans="1:19" ht="15.6">
       <c r="A453" s="38"/>
       <c r="B453" s="353" t="s">
         <v>556</v>
@@ -19505,7 +19484,7 @@
       </c>
       <c r="S453" s="317"/>
     </row>
-    <row r="454" spans="1:19" ht="15.75">
+    <row r="454" spans="1:19" ht="15.6">
       <c r="A454" s="56">
         <v>62</v>
       </c>
@@ -19544,7 +19523,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="455" spans="1:19" ht="15.75">
+    <row r="455" spans="1:19" ht="15.6">
       <c r="A455" s="200"/>
       <c r="B455" s="230" t="s">
         <v>561</v>
@@ -19573,7 +19552,7 @@
       </c>
       <c r="S455" s="160"/>
     </row>
-    <row r="456" spans="1:19" ht="15.75">
+    <row r="456" spans="1:19" ht="15.6">
       <c r="A456" s="200"/>
       <c r="B456" s="247"/>
       <c r="C456" s="330"/>
@@ -19594,7 +19573,7 @@
       <c r="R456" s="199"/>
       <c r="S456" s="160"/>
     </row>
-    <row r="457" spans="1:19" ht="15.75">
+    <row r="457" spans="1:19" ht="15.6">
       <c r="A457" s="200"/>
       <c r="B457" s="310">
         <v>34599</v>
@@ -19617,7 +19596,7 @@
       <c r="R457" s="199"/>
       <c r="S457" s="160"/>
     </row>
-    <row r="458" spans="1:19" ht="15.75">
+    <row r="458" spans="1:19" ht="15.6">
       <c r="A458" s="200"/>
       <c r="B458" s="338" t="s">
         <v>562</v>
@@ -19640,7 +19619,7 @@
       <c r="R458" s="388"/>
       <c r="S458" s="171"/>
     </row>
-    <row r="459" spans="1:19" ht="15.75">
+    <row r="459" spans="1:19" ht="15.6">
       <c r="A459" s="56">
         <v>63</v>
       </c>
@@ -19681,7 +19660,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="460" spans="1:19" ht="15.75">
+    <row r="460" spans="1:19" ht="15.6">
       <c r="A460" s="200"/>
       <c r="B460" s="359" t="s">
         <v>564</v>
@@ -19708,7 +19687,7 @@
       <c r="R460" s="221"/>
       <c r="S460" s="160"/>
     </row>
-    <row r="461" spans="1:19" ht="15.75">
+    <row r="461" spans="1:19" ht="15.6">
       <c r="A461" s="200"/>
       <c r="B461" s="121"/>
       <c r="C461" s="38"/>
@@ -19729,7 +19708,7 @@
       <c r="R461" s="221"/>
       <c r="S461" s="160"/>
     </row>
-    <row r="462" spans="1:19" ht="15.75">
+    <row r="462" spans="1:19" ht="15.6">
       <c r="A462" s="200"/>
       <c r="B462" s="231">
         <v>29145</v>
@@ -19752,7 +19731,7 @@
       <c r="R462" s="221"/>
       <c r="S462" s="160"/>
     </row>
-    <row r="463" spans="1:19" ht="15.75">
+    <row r="463" spans="1:19" ht="15.6">
       <c r="A463" s="200"/>
       <c r="B463" s="353" t="s">
         <v>565</v>
@@ -19775,7 +19754,7 @@
       <c r="R463" s="426"/>
       <c r="S463" s="171"/>
     </row>
-    <row r="464" spans="1:19" ht="15.75">
+    <row r="464" spans="1:19" ht="15.6">
       <c r="A464" s="56">
         <v>64</v>
       </c>
@@ -19812,7 +19791,7 @@
       </c>
       <c r="S464" s="156"/>
     </row>
-    <row r="465" spans="1:19" ht="15.75">
+    <row r="465" spans="1:19" ht="15.6">
       <c r="A465" s="38"/>
       <c r="B465" s="295" t="s">
         <v>566</v>
@@ -19835,7 +19814,7 @@
       <c r="R465" s="221"/>
       <c r="S465" s="160"/>
     </row>
-    <row r="466" spans="1:19" ht="15.75">
+    <row r="466" spans="1:19" ht="15.6">
       <c r="A466" s="38"/>
       <c r="B466" s="121"/>
       <c r="C466" s="38"/>
@@ -19856,7 +19835,7 @@
       <c r="R466" s="221"/>
       <c r="S466" s="160"/>
     </row>
-    <row r="467" spans="1:19" ht="15.75">
+    <row r="467" spans="1:19" ht="15.6">
       <c r="A467" s="38"/>
       <c r="B467" s="231">
         <v>32497</v>
@@ -19879,7 +19858,7 @@
       <c r="R467" s="221"/>
       <c r="S467" s="160"/>
     </row>
-    <row r="468" spans="1:19" ht="15.75">
+    <row r="468" spans="1:19" ht="15.6">
       <c r="A468" s="38"/>
       <c r="B468" s="528" t="s">
         <v>567</v>
@@ -19902,7 +19881,7 @@
       <c r="R468" s="426"/>
       <c r="S468" s="171"/>
     </row>
-    <row r="469" spans="1:19" ht="15.75">
+    <row r="469" spans="1:19" ht="15.6">
       <c r="A469" s="56">
         <v>65</v>
       </c>
@@ -19945,7 +19924,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="470" spans="1:19" ht="15.75">
+    <row r="470" spans="1:19" ht="15.6">
       <c r="A470" s="38"/>
       <c r="B470" s="359" t="s">
         <v>569</v>
@@ -19974,7 +19953,7 @@
       </c>
       <c r="S470" s="247"/>
     </row>
-    <row r="471" spans="1:19" ht="15.75">
+    <row r="471" spans="1:19" ht="15.6">
       <c r="A471" s="38"/>
       <c r="B471" s="121"/>
       <c r="C471" s="38"/>
@@ -20003,7 +19982,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="472" spans="1:19" ht="15.75">
+    <row r="472" spans="1:19" ht="15.6">
       <c r="A472" s="38"/>
       <c r="B472" s="231">
         <v>28776</v>
@@ -20030,7 +20009,7 @@
       <c r="R472" s="221"/>
       <c r="S472" s="247"/>
     </row>
-    <row r="473" spans="1:19" ht="15.75">
+    <row r="473" spans="1:19" ht="15.6">
       <c r="A473" s="38"/>
       <c r="B473" s="353" t="s">
         <v>398</v>
@@ -20053,7 +20032,7 @@
       <c r="R473" s="388"/>
       <c r="S473" s="171"/>
     </row>
-    <row r="474" spans="1:19" ht="15.75">
+    <row r="474" spans="1:19" ht="15.6">
       <c r="A474" s="56">
         <v>66</v>
       </c>
@@ -20090,7 +20069,7 @@
       </c>
       <c r="S474" s="147"/>
     </row>
-    <row r="475" spans="1:19" ht="15.75">
+    <row r="475" spans="1:19" ht="15.6">
       <c r="A475" s="452"/>
       <c r="B475" s="230" t="s">
         <v>572</v>
@@ -20121,7 +20100,7 @@
       </c>
       <c r="S475" s="123"/>
     </row>
-    <row r="476" spans="1:19" ht="15.75">
+    <row r="476" spans="1:19" ht="15.6">
       <c r="A476" s="532"/>
       <c r="B476" s="105"/>
       <c r="C476" s="373"/>
@@ -20146,7 +20125,7 @@
       </c>
       <c r="S476" s="160"/>
     </row>
-    <row r="477" spans="1:19" ht="15.75">
+    <row r="477" spans="1:19" ht="15.6">
       <c r="A477" s="532"/>
       <c r="B477" s="298">
         <v>35307</v>
@@ -20169,7 +20148,7 @@
       <c r="R477" s="119"/>
       <c r="S477" s="160"/>
     </row>
-    <row r="478" spans="1:19" ht="15.75">
+    <row r="478" spans="1:19" ht="15.6">
       <c r="A478" s="38"/>
       <c r="B478" s="436" t="s">
         <v>574</v>
@@ -20192,7 +20171,7 @@
       <c r="R478" s="119"/>
       <c r="S478" s="171"/>
     </row>
-    <row r="479" spans="1:19" ht="15.75">
+    <row r="479" spans="1:19" ht="15.6">
       <c r="A479" s="56">
         <v>67</v>
       </c>
@@ -20233,7 +20212,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="480" spans="1:19" ht="15.75">
+    <row r="480" spans="1:19" ht="15.6">
       <c r="A480" s="452"/>
       <c r="B480" s="230" t="s">
         <v>578</v>
@@ -20266,7 +20245,7 @@
       </c>
       <c r="S480" s="160"/>
     </row>
-    <row r="481" spans="1:19" ht="15.75">
+    <row r="481" spans="1:19" ht="15.6">
       <c r="A481" s="532"/>
       <c r="B481" s="105"/>
       <c r="C481" s="373"/>
@@ -20295,7 +20274,7 @@
       </c>
       <c r="S481" s="120"/>
     </row>
-    <row r="482" spans="1:19" ht="15.75">
+    <row r="482" spans="1:19" ht="15.6">
       <c r="A482" s="532"/>
       <c r="B482" s="298">
         <v>30407</v>
@@ -20322,7 +20301,7 @@
       <c r="R482" s="119"/>
       <c r="S482" s="120"/>
     </row>
-    <row r="483" spans="1:19" ht="15.75">
+    <row r="483" spans="1:19" ht="15.6">
       <c r="A483" s="38"/>
       <c r="B483" s="338" t="s">
         <v>581</v>
@@ -20345,7 +20324,7 @@
       <c r="R483" s="145"/>
       <c r="S483" s="146"/>
     </row>
-    <row r="484" spans="1:19" ht="15.75">
+    <row r="484" spans="1:19" ht="15.6">
       <c r="A484" s="56">
         <v>68</v>
       </c>
@@ -20384,7 +20363,7 @@
       </c>
       <c r="S484" s="247"/>
     </row>
-    <row r="485" spans="1:19" ht="15.75">
+    <row r="485" spans="1:19" ht="15.6">
       <c r="A485" s="532"/>
       <c r="B485" s="359" t="s">
         <v>583</v>
@@ -20411,7 +20390,7 @@
       <c r="R485" s="159"/>
       <c r="S485" s="247"/>
     </row>
-    <row r="486" spans="1:19" ht="15.75">
+    <row r="486" spans="1:19" ht="15.6">
       <c r="A486" s="123"/>
       <c r="B486" s="121"/>
       <c r="C486" s="38"/>
@@ -20434,7 +20413,7 @@
       <c r="R486" s="159"/>
       <c r="S486" s="247"/>
     </row>
-    <row r="487" spans="1:19" ht="15.75">
+    <row r="487" spans="1:19" ht="15.6">
       <c r="A487" s="123"/>
       <c r="B487" s="231">
         <v>33589</v>
@@ -20457,7 +20436,7 @@
       <c r="R487" s="159"/>
       <c r="S487" s="247"/>
     </row>
-    <row r="488" spans="1:19" ht="15.75">
+    <row r="488" spans="1:19" ht="15.6">
       <c r="A488" s="123"/>
       <c r="B488" s="399" t="s">
         <v>584</v>
@@ -20480,7 +20459,7 @@
       <c r="R488" s="159"/>
       <c r="S488" s="247"/>
     </row>
-    <row r="489" spans="1:19" ht="15.75">
+    <row r="489" spans="1:19" ht="15.6">
       <c r="A489" s="56">
         <v>69</v>
       </c>
@@ -20517,7 +20496,7 @@
       </c>
       <c r="S489" s="305"/>
     </row>
-    <row r="490" spans="1:19" ht="15.75">
+    <row r="490" spans="1:19" ht="15.6">
       <c r="A490" s="537"/>
       <c r="B490" s="295" t="s">
         <v>588</v>
@@ -20544,7 +20523,7 @@
       <c r="R490" s="119"/>
       <c r="S490" s="247"/>
     </row>
-    <row r="491" spans="1:19" ht="15.75">
+    <row r="491" spans="1:19" ht="15.6">
       <c r="A491" s="452"/>
       <c r="B491" s="121"/>
       <c r="C491" s="38"/>
@@ -20569,7 +20548,7 @@
       <c r="R491" s="119"/>
       <c r="S491" s="247"/>
     </row>
-    <row r="492" spans="1:19" ht="15.75">
+    <row r="492" spans="1:19" ht="15.6">
       <c r="B492" s="231">
         <v>32554</v>
       </c>
@@ -20593,7 +20572,7 @@
       <c r="R492" s="119"/>
       <c r="S492" s="247"/>
     </row>
-    <row r="493" spans="1:19" ht="15.75">
+    <row r="493" spans="1:19" ht="15.6">
       <c r="A493" s="123"/>
       <c r="B493" s="353" t="s">
         <v>589</v>
@@ -20618,7 +20597,7 @@
       <c r="R493" s="145"/>
       <c r="S493" s="317"/>
     </row>
-    <row r="494" spans="1:19" ht="15.75">
+    <row r="494" spans="1:19" ht="15.6">
       <c r="A494" s="56">
         <v>70</v>
       </c>
@@ -20657,7 +20636,7 @@
       </c>
       <c r="S494" s="305"/>
     </row>
-    <row r="495" spans="1:19" ht="15.75">
+    <row r="495" spans="1:19" ht="15.6">
       <c r="A495" s="38"/>
       <c r="B495" s="295" t="s">
         <v>591</v>
@@ -20682,7 +20661,7 @@
       <c r="R495" s="119"/>
       <c r="S495" s="247"/>
     </row>
-    <row r="496" spans="1:19" ht="15.75">
+    <row r="496" spans="1:19" ht="15.6">
       <c r="A496" s="452"/>
       <c r="B496" s="121"/>
       <c r="C496" s="38"/>
@@ -20705,7 +20684,7 @@
       <c r="R496" s="119"/>
       <c r="S496" s="247"/>
     </row>
-    <row r="497" spans="1:28" ht="15.75">
+    <row r="497" spans="1:28" ht="15.6">
       <c r="B497" s="231">
         <v>32406</v>
       </c>
@@ -20729,7 +20708,7 @@
       <c r="R497" s="119"/>
       <c r="S497" s="247"/>
     </row>
-    <row r="498" spans="1:28" ht="15.75">
+    <row r="498" spans="1:28" ht="15.6">
       <c r="A498" s="123"/>
       <c r="B498" s="353" t="s">
         <v>592</v>
@@ -20752,7 +20731,7 @@
       <c r="R498" s="145"/>
       <c r="S498" s="317"/>
     </row>
-    <row r="499" spans="1:28" ht="15.75">
+    <row r="499" spans="1:28" ht="15.6">
       <c r="A499" s="56">
         <v>71</v>
       </c>
@@ -20793,7 +20772,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="500" spans="1:28" ht="15.75">
+    <row r="500" spans="1:28" ht="15.6">
       <c r="A500" s="415"/>
       <c r="B500" s="306" t="s">
         <v>596</v>
@@ -20824,7 +20803,7 @@
       </c>
       <c r="S500" s="160"/>
     </row>
-    <row r="501" spans="1:28">
+    <row r="501" spans="1:28" ht="14.4">
       <c r="A501" s="415"/>
       <c r="B501" s="254"/>
       <c r="C501" s="160"/>
@@ -20861,7 +20840,7 @@
       <c r="AA501" s="81"/>
       <c r="AB501" s="81"/>
     </row>
-    <row r="502" spans="1:28" ht="15.75">
+    <row r="502" spans="1:28" ht="15.6">
       <c r="A502" s="415"/>
       <c r="B502" s="364">
         <v>27711</v>
@@ -20890,7 +20869,7 @@
       </c>
       <c r="S502" s="160"/>
     </row>
-    <row r="503" spans="1:28">
+    <row r="503" spans="1:28" ht="14.4">
       <c r="A503" s="415"/>
       <c r="B503" s="399" t="s">
         <v>601</v>
@@ -20915,7 +20894,7 @@
       <c r="R503" s="519"/>
       <c r="S503" s="317"/>
     </row>
-    <row r="504" spans="1:28" ht="15.75">
+    <row r="504" spans="1:28" ht="15.6">
       <c r="A504" s="56">
         <v>72</v>
       </c>
@@ -20954,7 +20933,7 @@
       </c>
       <c r="S504" s="241"/>
     </row>
-    <row r="505" spans="1:28" ht="15.75">
+    <row r="505" spans="1:28" ht="15.6">
       <c r="A505" s="415"/>
       <c r="B505" s="295" t="s">
         <v>606</v>
@@ -20983,7 +20962,7 @@
       <c r="R505" s="175"/>
       <c r="S505" s="330"/>
     </row>
-    <row r="506" spans="1:28">
+    <row r="506" spans="1:28" ht="14.4">
       <c r="A506" s="415"/>
       <c r="B506" s="247"/>
       <c r="C506" s="330"/>
@@ -21008,7 +20987,7 @@
       <c r="R506" s="175"/>
       <c r="S506" s="330"/>
     </row>
-    <row r="507" spans="1:28" ht="15.75">
+    <row r="507" spans="1:28" ht="15.6">
       <c r="A507" s="415"/>
       <c r="B507" s="310">
         <v>32692</v>
@@ -21035,7 +21014,7 @@
       <c r="R507" s="175"/>
       <c r="S507" s="330"/>
     </row>
-    <row r="508" spans="1:28" ht="15.75">
+    <row r="508" spans="1:28" ht="15.6">
       <c r="A508" s="415"/>
       <c r="B508" s="338" t="s">
         <v>610</v>
@@ -21060,7 +21039,7 @@
       <c r="R508" s="350"/>
       <c r="S508" s="339"/>
     </row>
-    <row r="509" spans="1:28" ht="15.75">
+    <row r="509" spans="1:28" ht="15.6">
       <c r="A509" s="56">
         <v>73</v>
       </c>
@@ -21099,7 +21078,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="510" spans="1:28" ht="15.75">
+    <row r="510" spans="1:28" ht="15.6">
       <c r="A510" s="415"/>
       <c r="B510" s="230" t="s">
         <v>612</v>
@@ -21130,7 +21109,7 @@
       </c>
       <c r="S510" s="160"/>
     </row>
-    <row r="511" spans="1:28" ht="15.75">
+    <row r="511" spans="1:28" ht="15.6">
       <c r="A511" s="415"/>
       <c r="B511" s="105"/>
       <c r="C511" s="105"/>
@@ -21157,7 +21136,7 @@
       </c>
       <c r="S511" s="120"/>
     </row>
-    <row r="512" spans="1:28" ht="15.75">
+    <row r="512" spans="1:28" ht="15.6">
       <c r="A512" s="415"/>
       <c r="B512" s="298">
         <v>30160</v>
@@ -21182,7 +21161,7 @@
       <c r="R512" s="199"/>
       <c r="S512" s="120"/>
     </row>
-    <row r="513" spans="1:19" ht="15.75">
+    <row r="513" spans="1:19" ht="15.6">
       <c r="A513" s="415"/>
       <c r="B513" s="338" t="s">
         <v>613</v>
@@ -21205,7 +21184,7 @@
       <c r="R513" s="388"/>
       <c r="S513" s="146"/>
     </row>
-    <row r="514" spans="1:19" ht="15.75">
+    <row r="514" spans="1:19" ht="15.6">
       <c r="A514" s="56">
         <v>74</v>
       </c>
@@ -21242,7 +21221,7 @@
       </c>
       <c r="S514" s="104"/>
     </row>
-    <row r="515" spans="1:19" ht="15.75">
+    <row r="515" spans="1:19" ht="15.6">
       <c r="A515" s="262"/>
       <c r="B515" s="230" t="s">
         <v>614</v>
@@ -21269,7 +21248,7 @@
       <c r="R515" s="199"/>
       <c r="S515" s="120"/>
     </row>
-    <row r="516" spans="1:19" ht="15.75">
+    <row r="516" spans="1:19" ht="15.6">
       <c r="A516" s="262"/>
       <c r="B516" s="105"/>
       <c r="C516" s="105"/>
@@ -21292,7 +21271,7 @@
       <c r="R516" s="199"/>
       <c r="S516" s="120"/>
     </row>
-    <row r="517" spans="1:19" ht="15.75">
+    <row r="517" spans="1:19" ht="15.6">
       <c r="A517" s="262"/>
       <c r="B517" s="298">
         <v>23632</v>
@@ -21315,7 +21294,7 @@
       <c r="R517" s="199"/>
       <c r="S517" s="120"/>
     </row>
-    <row r="518" spans="1:19" ht="15.75">
+    <row r="518" spans="1:19" ht="15.6">
       <c r="A518" s="38"/>
       <c r="B518" s="338" t="s">
         <v>615</v>
@@ -21338,7 +21317,7 @@
       <c r="R518" s="388"/>
       <c r="S518" s="146"/>
     </row>
-    <row r="519" spans="1:19" ht="15.75">
+    <row r="519" spans="1:19" ht="15.6">
       <c r="A519" s="56">
         <v>75</v>
       </c>
@@ -21379,7 +21358,7 @@
       </c>
       <c r="S519" s="104"/>
     </row>
-    <row r="520" spans="1:19" ht="15.75">
+    <row r="520" spans="1:19" ht="15.6">
       <c r="A520" s="262"/>
       <c r="B520" s="230" t="s">
         <v>616</v>
@@ -21410,7 +21389,7 @@
       <c r="R520" s="199"/>
       <c r="S520" s="120"/>
     </row>
-    <row r="521" spans="1:19" ht="15.75">
+    <row r="521" spans="1:19" ht="15.6">
       <c r="A521" s="262"/>
       <c r="B521" s="105"/>
       <c r="C521" s="105"/>
@@ -21435,7 +21414,7 @@
       <c r="R521" s="199"/>
       <c r="S521" s="120"/>
     </row>
-    <row r="522" spans="1:19" ht="15.75">
+    <row r="522" spans="1:19" ht="15.6">
       <c r="A522" s="262"/>
       <c r="B522" s="298">
         <v>37222</v>
@@ -21462,7 +21441,7 @@
       <c r="R522" s="199"/>
       <c r="S522" s="120"/>
     </row>
-    <row r="523" spans="1:19" ht="15.75">
+    <row r="523" spans="1:19" ht="15.6">
       <c r="A523" s="38"/>
       <c r="B523" s="338" t="s">
         <v>617</v>
@@ -21485,7 +21464,7 @@
       <c r="R523" s="388"/>
       <c r="S523" s="146"/>
     </row>
-    <row r="524" spans="1:19" ht="15.75">
+    <row r="524" spans="1:19" ht="15.6">
       <c r="A524" s="56">
         <v>76</v>
       </c>
@@ -21522,7 +21501,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="525" spans="1:19" ht="15.75">
+    <row r="525" spans="1:19" ht="15.6">
       <c r="A525" s="38"/>
       <c r="B525" s="295" t="s">
         <v>618</v>
@@ -21549,7 +21528,7 @@
       </c>
       <c r="S525" s="160"/>
     </row>
-    <row r="526" spans="1:19" ht="15.75">
+    <row r="526" spans="1:19" ht="15.6">
       <c r="A526" s="38"/>
       <c r="B526" s="247"/>
       <c r="C526" s="247"/>
@@ -21574,7 +21553,7 @@
       </c>
       <c r="S526" s="160"/>
     </row>
-    <row r="527" spans="1:19" ht="15.75">
+    <row r="527" spans="1:19" ht="15.6">
       <c r="A527" s="38"/>
       <c r="B527" s="310">
         <v>32508</v>
@@ -21597,7 +21576,7 @@
       <c r="R527" s="159"/>
       <c r="S527" s="160"/>
     </row>
-    <row r="528" spans="1:19" ht="15.75">
+    <row r="528" spans="1:19" ht="15.6">
       <c r="A528" s="200"/>
       <c r="B528" s="338" t="s">
         <v>619</v>
@@ -21622,7 +21601,7 @@
       <c r="R528" s="316"/>
       <c r="S528" s="171"/>
     </row>
-    <row r="529" spans="1:19" ht="15.75">
+    <row r="529" spans="1:19" ht="15.6">
       <c r="A529" s="56">
         <v>77</v>
       </c>
@@ -21661,7 +21640,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="530" spans="1:19" ht="15.75">
+    <row r="530" spans="1:19" ht="15.6">
       <c r="A530" s="38"/>
       <c r="B530" s="295" t="s">
         <v>622</v>
@@ -21688,7 +21667,7 @@
       </c>
       <c r="S530" s="247"/>
     </row>
-    <row r="531" spans="1:19" ht="15.75">
+    <row r="531" spans="1:19" ht="15.6">
       <c r="A531" s="38"/>
       <c r="B531" s="246">
         <v>33501</v>
@@ -21715,7 +21694,7 @@
       </c>
       <c r="S531" s="247"/>
     </row>
-    <row r="532" spans="1:19" ht="15.75">
+    <row r="532" spans="1:19" ht="15.6">
       <c r="A532" s="38"/>
       <c r="B532" s="310"/>
       <c r="C532" s="247"/>
@@ -21736,7 +21715,7 @@
       <c r="R532" s="159"/>
       <c r="S532" s="247"/>
     </row>
-    <row r="533" spans="1:19" ht="15.75">
+    <row r="533" spans="1:19" ht="15.6">
       <c r="A533" s="38"/>
       <c r="B533" s="338" t="s">
         <v>623</v>
@@ -21759,7 +21738,7 @@
       <c r="R533" s="316"/>
       <c r="S533" s="317"/>
     </row>
-    <row r="534" spans="1:19" ht="15.75">
+    <row r="534" spans="1:19" ht="15.6">
       <c r="A534" s="56">
         <v>78</v>
       </c>
@@ -21796,7 +21775,7 @@
       </c>
       <c r="S534" s="305"/>
     </row>
-    <row r="535" spans="1:19" ht="15.75">
+    <row r="535" spans="1:19" ht="15.6">
       <c r="A535" s="415"/>
       <c r="B535" s="359" t="s">
         <v>625</v>
@@ -21823,7 +21802,7 @@
       <c r="R535" s="221"/>
       <c r="S535" s="247"/>
     </row>
-    <row r="536" spans="1:19" ht="15.75">
+    <row r="536" spans="1:19" ht="15.6">
       <c r="A536" s="415"/>
       <c r="B536" s="121"/>
       <c r="C536" s="38"/>
@@ -21846,7 +21825,7 @@
       <c r="R536" s="221"/>
       <c r="S536" s="247"/>
     </row>
-    <row r="537" spans="1:19" ht="15.75">
+    <row r="537" spans="1:19" ht="15.6">
       <c r="A537" s="415"/>
       <c r="B537" s="231">
         <v>25728</v>
@@ -21871,7 +21850,7 @@
       <c r="R537" s="221"/>
       <c r="S537" s="247"/>
     </row>
-    <row r="538" spans="1:19" ht="15.75">
+    <row r="538" spans="1:19" ht="15.6">
       <c r="A538" s="415"/>
       <c r="B538" s="353" t="s">
         <v>626</v>
@@ -21894,7 +21873,7 @@
       <c r="R538" s="426"/>
       <c r="S538" s="317"/>
     </row>
-    <row r="539" spans="1:19" ht="15.75">
+    <row r="539" spans="1:19" ht="15.6">
       <c r="A539" s="56">
         <v>79</v>
       </c>
@@ -21935,7 +21914,7 @@
       </c>
       <c r="S539" s="305"/>
     </row>
-    <row r="540" spans="1:19" ht="15.75">
+    <row r="540" spans="1:19" ht="15.6">
       <c r="A540" s="415"/>
       <c r="B540" s="295" t="s">
         <v>628</v>
@@ -21968,7 +21947,7 @@
       </c>
       <c r="S540" s="247"/>
     </row>
-    <row r="541" spans="1:19" ht="15.75">
+    <row r="541" spans="1:19" ht="15.6">
       <c r="A541" s="415"/>
       <c r="B541" s="121"/>
       <c r="C541" s="38"/>
@@ -21995,7 +21974,7 @@
       </c>
       <c r="S541" s="247"/>
     </row>
-    <row r="542" spans="1:19" ht="15.75">
+    <row r="542" spans="1:19" ht="15.6">
       <c r="A542" s="415"/>
       <c r="B542" s="231">
         <v>20964</v>
@@ -22024,7 +22003,7 @@
       </c>
       <c r="S542" s="247"/>
     </row>
-    <row r="543" spans="1:19" ht="15.75">
+    <row r="543" spans="1:19" ht="15.6">
       <c r="A543" s="415"/>
       <c r="B543" s="353" t="s">
         <v>632</v>
@@ -22049,7 +22028,7 @@
       </c>
       <c r="S543" s="317"/>
     </row>
-    <row r="544" spans="1:19" ht="15.75">
+    <row r="544" spans="1:19" ht="15.6">
       <c r="A544" s="56">
         <v>80</v>
       </c>
@@ -22088,7 +22067,7 @@
       </c>
       <c r="S544" s="305"/>
     </row>
-    <row r="545" spans="1:19" ht="15.75">
+    <row r="545" spans="1:19" ht="15.6">
       <c r="A545" s="415"/>
       <c r="B545" s="359" t="s">
         <v>635</v>
@@ -22115,7 +22094,7 @@
       <c r="R545" s="221"/>
       <c r="S545" s="247"/>
     </row>
-    <row r="546" spans="1:19" ht="15.75">
+    <row r="546" spans="1:19" ht="15.6">
       <c r="B546" s="121"/>
       <c r="C546" s="38"/>
       <c r="D546" s="296"/>
@@ -22137,7 +22116,7 @@
       <c r="R546" s="221"/>
       <c r="S546" s="247"/>
     </row>
-    <row r="547" spans="1:19" ht="15.75">
+    <row r="547" spans="1:19" ht="15.6">
       <c r="B547" s="231">
         <v>29416</v>
       </c>
@@ -22161,7 +22140,7 @@
       <c r="R547" s="221"/>
       <c r="S547" s="247"/>
     </row>
-    <row r="548" spans="1:19" ht="15.75">
+    <row r="548" spans="1:19" ht="15.6">
       <c r="B548" s="353" t="s">
         <v>636</v>
       </c>
@@ -22183,7 +22162,7 @@
       <c r="R548" s="426"/>
       <c r="S548" s="317"/>
     </row>
-    <row r="549" spans="1:19" ht="15.75">
+    <row r="549" spans="1:19" ht="15.6">
       <c r="A549" s="56">
         <v>81</v>
       </c>
@@ -22226,7 +22205,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="550" spans="1:19" ht="15.75">
+    <row r="550" spans="1:19" ht="15.6">
       <c r="B550" s="451" t="s">
         <v>639</v>
       </c>
@@ -22256,7 +22235,7 @@
       </c>
       <c r="S550" s="247"/>
     </row>
-    <row r="551" spans="1:19">
+    <row r="551" spans="1:19" ht="14.4">
       <c r="B551" s="247"/>
       <c r="C551" s="330"/>
       <c r="D551" s="331"/>
@@ -22284,7 +22263,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="552" spans="1:19" ht="15.75">
+    <row r="552" spans="1:19" ht="15.6">
       <c r="B552" s="310">
         <v>29149</v>
       </c>
@@ -22312,7 +22291,7 @@
       </c>
       <c r="S552" s="247"/>
     </row>
-    <row r="553" spans="1:19" ht="15.75">
+    <row r="553" spans="1:19" ht="15.6">
       <c r="B553" s="353" t="s">
         <v>644</v>
       </c>
@@ -22336,7 +22315,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="554" spans="1:19" ht="15.75">
+    <row r="554" spans="1:19" ht="15.6">
       <c r="A554" s="56">
         <v>82</v>
       </c>
@@ -22377,7 +22356,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="555" spans="1:19" ht="15.75">
+    <row r="555" spans="1:19" ht="15.6">
       <c r="B555" s="359" t="s">
         <v>648</v>
       </c>
@@ -22405,7 +22384,7 @@
       </c>
       <c r="S555" s="247"/>
     </row>
-    <row r="556" spans="1:19" ht="15.75">
+    <row r="556" spans="1:19" ht="15.6">
       <c r="B556" s="121"/>
       <c r="C556" s="105"/>
       <c r="D556" s="222"/>
@@ -22431,7 +22410,7 @@
       </c>
       <c r="S556" s="247"/>
     </row>
-    <row r="557" spans="1:19" ht="15.75">
+    <row r="557" spans="1:19" ht="15.6">
       <c r="B557" s="231">
         <v>33075</v>
       </c>
@@ -22459,7 +22438,7 @@
       </c>
       <c r="S557" s="247"/>
     </row>
-    <row r="558" spans="1:19" ht="15.75">
+    <row r="558" spans="1:19" ht="15.6">
       <c r="B558" s="399" t="s">
         <v>651</v>
       </c>
@@ -22481,7 +22460,7 @@
       <c r="R558" s="221"/>
       <c r="S558" s="247"/>
     </row>
-    <row r="559" spans="1:19" ht="15.75">
+    <row r="559" spans="1:19" ht="15.6">
       <c r="A559" s="56">
         <v>83</v>
       </c>
@@ -22520,7 +22499,7 @@
       </c>
       <c r="S559" s="305"/>
     </row>
-    <row r="560" spans="1:19" ht="15.75">
+    <row r="560" spans="1:19" ht="15.6">
       <c r="B560" s="359" t="s">
         <v>652</v>
       </c>
@@ -22546,7 +22525,7 @@
       <c r="R560" s="221"/>
       <c r="S560" s="247"/>
     </row>
-    <row r="561" spans="1:19" ht="15.75">
+    <row r="561" spans="1:19" ht="15.6">
       <c r="B561" s="121"/>
       <c r="C561" s="38"/>
       <c r="D561" s="296"/>
@@ -22568,7 +22547,7 @@
       <c r="R561" s="221"/>
       <c r="S561" s="247"/>
     </row>
-    <row r="562" spans="1:19" ht="15.75">
+    <row r="562" spans="1:19" ht="15.6">
       <c r="B562" s="231">
         <v>24853</v>
       </c>
@@ -22592,7 +22571,7 @@
       <c r="R562" s="221"/>
       <c r="S562" s="247"/>
     </row>
-    <row r="563" spans="1:19" ht="15.75">
+    <row r="563" spans="1:19" ht="15.6">
       <c r="B563" s="353" t="s">
         <v>636</v>
       </c>
@@ -22616,7 +22595,7 @@
       <c r="R563" s="426"/>
       <c r="S563" s="317"/>
     </row>
-    <row r="564" spans="1:19" ht="15.75">
+    <row r="564" spans="1:19" ht="15.6">
       <c r="A564" s="56">
         <v>84</v>
       </c>
@@ -22655,7 +22634,7 @@
       </c>
       <c r="S564" s="156"/>
     </row>
-    <row r="565" spans="1:19" ht="15.75">
+    <row r="565" spans="1:19" ht="15.6">
       <c r="B565" s="295" t="s">
         <v>655</v>
       </c>
@@ -22685,7 +22664,7 @@
       </c>
       <c r="S565" s="123"/>
     </row>
-    <row r="566" spans="1:19" ht="15.75">
+    <row r="566" spans="1:19" ht="15.6">
       <c r="B566" s="121"/>
       <c r="C566" s="38"/>
       <c r="D566" s="296"/>
@@ -22707,7 +22686,7 @@
       <c r="R566" s="221"/>
       <c r="S566" s="160"/>
     </row>
-    <row r="567" spans="1:19" ht="15.75">
+    <row r="567" spans="1:19" ht="15.6">
       <c r="B567" s="231">
         <v>27776</v>
       </c>
@@ -22731,7 +22710,7 @@
       <c r="R567" s="221"/>
       <c r="S567" s="160"/>
     </row>
-    <row r="568" spans="1:19" ht="15.75">
+    <row r="568" spans="1:19" ht="15.6">
       <c r="B568" s="353" t="s">
         <v>656</v>
       </c>
@@ -22755,7 +22734,7 @@
       <c r="R568" s="426"/>
       <c r="S568" s="171"/>
     </row>
-    <row r="569" spans="1:19" ht="15.75">
+    <row r="569" spans="1:19" ht="15.6">
       <c r="A569" s="56">
         <v>85</v>
       </c>
@@ -22798,7 +22777,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="570" spans="1:19" ht="15.75">
+    <row r="570" spans="1:19" ht="15.6">
       <c r="B570" s="451" t="s">
         <v>659</v>
       </c>
@@ -22829,7 +22808,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="571" spans="1:19">
+    <row r="571" spans="1:19" ht="14.4">
       <c r="B571" s="247"/>
       <c r="C571" s="330"/>
       <c r="D571" s="331"/>
@@ -22854,7 +22833,7 @@
       </c>
       <c r="S571" s="160"/>
     </row>
-    <row r="572" spans="1:19" ht="15.75">
+    <row r="572" spans="1:19" ht="15.6">
       <c r="B572" s="310">
         <v>26607</v>
       </c>
@@ -22877,7 +22856,7 @@
       </c>
       <c r="S572" s="123"/>
     </row>
-    <row r="573" spans="1:19" ht="15.75">
+    <row r="573" spans="1:19" ht="15.6">
       <c r="B573" s="338" t="s">
         <v>664</v>
       </c>
@@ -22899,7 +22878,7 @@
       <c r="R573" s="145"/>
       <c r="S573" s="146"/>
     </row>
-    <row r="574" spans="1:19" ht="15.75">
+    <row r="574" spans="1:19" ht="15.6">
       <c r="A574" s="56">
         <v>86</v>
       </c>
@@ -22940,7 +22919,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="575" spans="1:19" ht="15.75">
+    <row r="575" spans="1:19" ht="15.6">
       <c r="B575" s="295" t="s">
         <v>669</v>
       </c>
@@ -22964,7 +22943,7 @@
       </c>
       <c r="S575" s="160"/>
     </row>
-    <row r="576" spans="1:19">
+    <row r="576" spans="1:19" ht="14.4">
       <c r="B576" s="247"/>
       <c r="C576" s="330"/>
       <c r="D576" s="331"/>
@@ -22986,7 +22965,7 @@
       </c>
       <c r="S576" s="160"/>
     </row>
-    <row r="577" spans="1:19" ht="15.75">
+    <row r="577" spans="1:19" ht="15.6">
       <c r="B577" s="310">
         <v>25084</v>
       </c>
@@ -23010,7 +22989,7 @@
       </c>
       <c r="S577" s="160"/>
     </row>
-    <row r="578" spans="1:19" ht="15.75">
+    <row r="578" spans="1:19" ht="15.6">
       <c r="A578" s="123"/>
       <c r="B578" s="353" t="s">
         <v>430</v>
@@ -23035,7 +23014,7 @@
       </c>
       <c r="S578" s="133"/>
     </row>
-    <row r="579" spans="1:19" ht="15.75">
+    <row r="579" spans="1:19" ht="15.6">
       <c r="A579" s="56">
         <v>87</v>
       </c>
@@ -23076,7 +23055,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="580" spans="1:19" ht="15.75">
+    <row r="580" spans="1:19" ht="15.6">
       <c r="B580" s="359" t="s">
         <v>484</v>
       </c>
@@ -23100,7 +23079,7 @@
       </c>
       <c r="S580" s="247"/>
     </row>
-    <row r="581" spans="1:19" ht="15.75">
+    <row r="581" spans="1:19" ht="15.6">
       <c r="B581" s="121"/>
       <c r="C581" s="38"/>
       <c r="D581" s="296"/>
@@ -23122,7 +23101,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="582" spans="1:19" ht="15.75">
+    <row r="582" spans="1:19" ht="15.6">
       <c r="B582" s="231">
         <v>20697</v>
       </c>
@@ -23146,7 +23125,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="583" spans="1:19" ht="15.75">
+    <row r="583" spans="1:19" ht="15.6">
       <c r="A583" s="123"/>
       <c r="B583" s="353" t="s">
         <v>490</v>
@@ -23175,7 +23154,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="584" spans="1:19" ht="15.75">
+    <row r="584" spans="1:19" ht="15.6">
       <c r="A584" s="56">
         <v>88</v>
       </c>
@@ -23212,7 +23191,7 @@
       </c>
       <c r="S584" s="156"/>
     </row>
-    <row r="585" spans="1:19" ht="15.75">
+    <row r="585" spans="1:19" ht="15.6">
       <c r="B585" s="359" t="s">
         <v>678</v>
       </c>
@@ -23236,7 +23215,7 @@
       <c r="R585" s="221"/>
       <c r="S585" s="160"/>
     </row>
-    <row r="586" spans="1:19" ht="15.75">
+    <row r="586" spans="1:19" ht="15.6">
       <c r="B586" s="121"/>
       <c r="C586" s="105"/>
       <c r="D586" s="222"/>
@@ -23258,7 +23237,7 @@
       <c r="R586" s="221"/>
       <c r="S586" s="160"/>
     </row>
-    <row r="587" spans="1:19" ht="15.75">
+    <row r="587" spans="1:19" ht="15.6">
       <c r="B587" s="231">
         <v>29183</v>
       </c>
@@ -23282,7 +23261,7 @@
       <c r="R587" s="221"/>
       <c r="S587" s="160"/>
     </row>
-    <row r="588" spans="1:19" ht="15.75">
+    <row r="588" spans="1:19" ht="15.6">
       <c r="A588" s="123"/>
       <c r="B588" s="353" t="s">
         <v>679</v>
@@ -23305,7 +23284,7 @@
       <c r="R588" s="426"/>
       <c r="S588" s="171"/>
     </row>
-    <row r="589" spans="1:19" ht="15.75">
+    <row r="589" spans="1:19" ht="15.6">
       <c r="A589" s="56">
         <v>89</v>
       </c>
@@ -23348,7 +23327,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="590" spans="1:19" ht="15.75">
+    <row r="590" spans="1:19" ht="15.6">
       <c r="A590" s="299"/>
       <c r="B590" s="230" t="s">
         <v>682</v>
@@ -23379,7 +23358,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="591" spans="1:19" ht="15.75">
+    <row r="591" spans="1:19" ht="15.6">
       <c r="A591" s="299"/>
       <c r="B591" s="577">
         <v>30432636770</v>
@@ -23408,7 +23387,7 @@
       </c>
       <c r="S591" s="160"/>
     </row>
-    <row r="592" spans="1:19" ht="15.75">
+    <row r="592" spans="1:19" ht="15.6">
       <c r="A592" s="299"/>
       <c r="B592" s="298">
         <v>28263</v>
@@ -23435,7 +23414,7 @@
       </c>
       <c r="S592" s="160"/>
     </row>
-    <row r="593" spans="1:19" ht="15.75">
+    <row r="593" spans="1:19" ht="15.6">
       <c r="A593" s="299"/>
       <c r="B593" s="516" t="s">
         <v>687</v>
@@ -23460,7 +23439,7 @@
       </c>
       <c r="S593" s="171"/>
     </row>
-    <row r="594" spans="1:19" ht="15.75">
+    <row r="594" spans="1:19" ht="15.6">
       <c r="A594" s="56">
         <v>90</v>
       </c>
@@ -23501,7 +23480,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="595" spans="1:19" ht="15.75">
+    <row r="595" spans="1:19" ht="15.6">
       <c r="A595" s="299"/>
       <c r="B595" s="451" t="s">
         <v>503</v>
@@ -23532,7 +23511,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="596" spans="1:19" ht="15.75">
+    <row r="596" spans="1:19" ht="15.6">
       <c r="A596" s="299"/>
       <c r="B596" s="231"/>
       <c r="C596" s="38"/>
@@ -23555,7 +23534,7 @@
       </c>
       <c r="S596" s="160"/>
     </row>
-    <row r="597" spans="1:19" ht="15.75">
+    <row r="597" spans="1:19" ht="15.6">
       <c r="A597" s="299"/>
       <c r="B597" s="231">
         <v>34294</v>
@@ -23580,7 +23559,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="598" spans="1:19" ht="15.75">
+    <row r="598" spans="1:19" ht="15.6">
       <c r="A598" s="210"/>
       <c r="B598" s="353" t="s">
         <v>698</v>
@@ -23605,7 +23584,7 @@
       <c r="R598" s="221"/>
       <c r="S598" s="133"/>
     </row>
-    <row r="599" spans="1:19" ht="15.75">
+    <row r="599" spans="1:19" ht="15.6">
       <c r="A599" s="299">
         <v>91</v>
       </c>
@@ -23646,7 +23625,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="600" spans="1:19" ht="15.75">
+    <row r="600" spans="1:19" ht="15.6">
       <c r="A600" s="299"/>
       <c r="B600" s="230" t="s">
         <v>701</v>
@@ -23677,7 +23656,7 @@
       </c>
       <c r="S600" s="123"/>
     </row>
-    <row r="601" spans="1:19" ht="15.75">
+    <row r="601" spans="1:19" ht="15.6">
       <c r="A601" s="299"/>
       <c r="B601" s="105"/>
       <c r="C601" s="373"/>
@@ -23706,7 +23685,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="602" spans="1:19" ht="15.75">
+    <row r="602" spans="1:19" ht="15.6">
       <c r="A602" s="299"/>
       <c r="B602" s="298">
         <v>29027</v>
@@ -23735,7 +23714,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="603" spans="1:19" ht="15.75">
+    <row r="603" spans="1:19" ht="15.6">
       <c r="A603" s="299"/>
       <c r="B603" s="338" t="s">
         <v>707</v>
@@ -23758,7 +23737,7 @@
       <c r="R603" s="388"/>
       <c r="S603" s="123"/>
     </row>
-    <row r="604" spans="1:19" ht="15.75">
+    <row r="604" spans="1:19" ht="15.6">
       <c r="A604" s="147">
         <v>92</v>
       </c>
@@ -23799,7 +23778,7 @@
       </c>
       <c r="S604" s="305"/>
     </row>
-    <row r="605" spans="1:19" ht="15.75">
+    <row r="605" spans="1:19" ht="15.6">
       <c r="B605" s="359" t="s">
         <v>710</v>
       </c>
@@ -23831,7 +23810,7 @@
       </c>
       <c r="S605" s="247"/>
     </row>
-    <row r="606" spans="1:19" ht="15.75">
+    <row r="606" spans="1:19" ht="15.6">
       <c r="B606" s="121"/>
       <c r="C606" s="38"/>
       <c r="D606" s="296"/>
@@ -23859,7 +23838,7 @@
       </c>
       <c r="S606" s="247"/>
     </row>
-    <row r="607" spans="1:19" ht="15.75">
+    <row r="607" spans="1:19" ht="15.6">
       <c r="B607" s="231">
         <v>34190</v>
       </c>
@@ -23887,7 +23866,7 @@
       </c>
       <c r="S607" s="247"/>
     </row>
-    <row r="608" spans="1:19" ht="15.75">
+    <row r="608" spans="1:19" ht="15.6">
       <c r="B608" s="353" t="s">
         <v>714</v>
       </c>
@@ -23911,7 +23890,7 @@
       </c>
       <c r="S608" s="317"/>
     </row>
-    <row r="609" spans="1:19" ht="15.75">
+    <row r="609" spans="1:19" ht="15.6">
       <c r="A609" s="81">
         <v>93</v>
       </c>
@@ -23952,7 +23931,7 @@
       </c>
       <c r="S609" s="305"/>
     </row>
-    <row r="610" spans="1:19" ht="15.75">
+    <row r="610" spans="1:19" ht="15.6">
       <c r="B610" s="359" t="s">
         <v>717</v>
       </c>
@@ -23982,7 +23961,7 @@
       <c r="R610" s="221"/>
       <c r="S610" s="247"/>
     </row>
-    <row r="611" spans="1:19" ht="15.75">
+    <row r="611" spans="1:19" ht="15.6">
       <c r="B611" s="121"/>
       <c r="C611" s="38"/>
       <c r="D611" s="296"/>
@@ -24006,7 +23985,7 @@
       <c r="R611" s="119"/>
       <c r="S611" s="247"/>
     </row>
-    <row r="612" spans="1:19" ht="15.75">
+    <row r="612" spans="1:19" ht="15.6">
       <c r="B612" s="231">
         <v>23649</v>
       </c>
@@ -24032,7 +24011,7 @@
       <c r="R612" s="221"/>
       <c r="S612" s="247"/>
     </row>
-    <row r="613" spans="1:19" ht="15.75">
+    <row r="613" spans="1:19" ht="15.6">
       <c r="B613" s="353" t="s">
         <v>718</v>
       </c>
@@ -24054,7 +24033,7 @@
       <c r="R613" s="145"/>
       <c r="S613" s="317"/>
     </row>
-    <row r="614" spans="1:19" ht="15.75">
+    <row r="614" spans="1:19" ht="15.6">
       <c r="A614" s="147">
         <v>94</v>
       </c>
@@ -24089,7 +24068,7 @@
       </c>
       <c r="S614" s="147"/>
     </row>
-    <row r="615" spans="1:19" ht="15.75">
+    <row r="615" spans="1:19" ht="15.6">
       <c r="B615" s="580" t="s">
         <v>719</v>
       </c>
@@ -24117,7 +24096,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="616" spans="1:19" ht="15.75">
+    <row r="616" spans="1:19" ht="15.6">
       <c r="B616" s="121"/>
       <c r="C616" s="38"/>
       <c r="D616" s="307"/>
@@ -24137,7 +24116,7 @@
       <c r="R616" s="119"/>
       <c r="S616" s="330"/>
     </row>
-    <row r="617" spans="1:19" ht="15.75">
+    <row r="617" spans="1:19" ht="15.6">
       <c r="B617" s="231">
         <v>37687</v>
       </c>
@@ -24159,7 +24138,7 @@
       <c r="R617" s="119"/>
       <c r="S617" s="247"/>
     </row>
-    <row r="618" spans="1:19" ht="15.75">
+    <row r="618" spans="1:19" ht="15.6">
       <c r="B618" s="353" t="s">
         <v>721</v>
       </c>
@@ -24181,7 +24160,7 @@
       <c r="R618" s="145"/>
       <c r="S618" s="133"/>
     </row>
-    <row r="619" spans="1:19" ht="15.75">
+    <row r="619" spans="1:19" ht="15.6">
       <c r="A619" s="147">
         <v>95</v>
       </c>
@@ -24220,7 +24199,7 @@
       </c>
       <c r="S619" s="82"/>
     </row>
-    <row r="620" spans="1:19" ht="15.75">
+    <row r="620" spans="1:19" ht="15.6">
       <c r="B620" s="359" t="s">
         <v>723</v>
       </c>
@@ -24250,7 +24229,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="621" spans="1:19" ht="15.75">
+    <row r="621" spans="1:19" ht="15.6">
       <c r="B621" s="121"/>
       <c r="C621" s="38"/>
       <c r="D621" s="296"/>
@@ -24274,7 +24253,7 @@
       </c>
       <c r="S621" s="415"/>
     </row>
-    <row r="622" spans="1:19" ht="15.75">
+    <row r="622" spans="1:19" ht="15.6">
       <c r="B622" s="231">
         <v>29957</v>
       </c>
@@ -24298,7 +24277,7 @@
       </c>
       <c r="S622" s="415"/>
     </row>
-    <row r="623" spans="1:19" ht="15.75">
+    <row r="623" spans="1:19" ht="15.6">
       <c r="B623" s="353" t="s">
         <v>728</v>
       </c>
@@ -24322,7 +24301,7 @@
       </c>
       <c r="S623" s="416"/>
     </row>
-    <row r="624" spans="1:19" ht="15.75">
+    <row r="624" spans="1:19" ht="15.6">
       <c r="A624" s="147">
         <v>96</v>
       </c>
@@ -24361,7 +24340,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="625" spans="1:19" ht="15.75">
+    <row r="625" spans="1:19" ht="15.6">
       <c r="B625" s="359" t="s">
         <v>734</v>
       </c>
@@ -24387,7 +24366,7 @@
       </c>
       <c r="S625" s="120"/>
     </row>
-    <row r="626" spans="1:19" ht="15.75">
+    <row r="626" spans="1:19" ht="15.6">
       <c r="B626" s="121"/>
       <c r="C626" s="105"/>
       <c r="D626" s="222"/>
@@ -24411,7 +24390,7 @@
       </c>
       <c r="S626" s="120"/>
     </row>
-    <row r="627" spans="1:19" ht="15.75">
+    <row r="627" spans="1:19" ht="15.6">
       <c r="B627" s="231">
         <v>29077</v>
       </c>
@@ -24435,7 +24414,7 @@
       </c>
       <c r="S627" s="120"/>
     </row>
-    <row r="628" spans="1:19" ht="15.75">
+    <row r="628" spans="1:19" ht="15.6">
       <c r="B628" s="399" t="s">
         <v>408</v>
       </c>
@@ -24459,7 +24438,7 @@
       <c r="R628" s="388"/>
       <c r="S628" s="416"/>
     </row>
-    <row r="629" spans="1:19" ht="15.75">
+    <row r="629" spans="1:19" ht="15.6">
       <c r="A629" s="147">
         <v>97</v>
       </c>
@@ -24502,7 +24481,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="630" spans="1:19" ht="15.75">
+    <row r="630" spans="1:19" ht="15.6">
       <c r="B630" s="295" t="s">
         <v>740</v>
       </c>
@@ -24534,7 +24513,7 @@
       </c>
       <c r="S630" s="120"/>
     </row>
-    <row r="631" spans="1:19">
+    <row r="631" spans="1:19" ht="14.4">
       <c r="B631" s="247"/>
       <c r="C631" s="330"/>
       <c r="D631" s="331"/>
@@ -24560,7 +24539,7 @@
       </c>
       <c r="S631" s="120"/>
     </row>
-    <row r="632" spans="1:19" ht="15.75">
+    <row r="632" spans="1:19" ht="15.6">
       <c r="B632" s="310">
         <v>27797</v>
       </c>
@@ -24584,7 +24563,7 @@
       <c r="R632" s="119"/>
       <c r="S632" s="120"/>
     </row>
-    <row r="633" spans="1:19" ht="15.75">
+    <row r="633" spans="1:19" ht="15.6">
       <c r="B633" s="485" t="s">
         <v>398</v>
       </c>
@@ -24606,7 +24585,7 @@
       <c r="R633" s="388"/>
       <c r="S633" s="416"/>
     </row>
-    <row r="634" spans="1:19" ht="15.75">
+    <row r="634" spans="1:19" ht="15.6">
       <c r="A634" s="147">
         <v>98</v>
       </c>
@@ -24645,7 +24624,7 @@
       </c>
       <c r="S634" s="104"/>
     </row>
-    <row r="635" spans="1:19" ht="15.75">
+    <row r="635" spans="1:19" ht="15.6">
       <c r="B635" s="359" t="s">
         <v>743</v>
       </c>
@@ -24669,7 +24648,7 @@
       <c r="R635" s="119"/>
       <c r="S635" s="120"/>
     </row>
-    <row r="636" spans="1:19" ht="15.75">
+    <row r="636" spans="1:19" ht="15.6">
       <c r="B636" s="121"/>
       <c r="C636" s="105"/>
       <c r="D636" s="331"/>
@@ -24689,7 +24668,7 @@
       <c r="R636" s="119"/>
       <c r="S636" s="120"/>
     </row>
-    <row r="637" spans="1:19" ht="15.75">
+    <row r="637" spans="1:19" ht="15.6">
       <c r="B637" s="231">
         <v>29482</v>
       </c>
@@ -24711,7 +24690,7 @@
       <c r="R637" s="119"/>
       <c r="S637" s="120"/>
     </row>
-    <row r="638" spans="1:19" ht="15.75">
+    <row r="638" spans="1:19" ht="15.6">
       <c r="B638" s="353" t="s">
         <v>744</v>
       </c>
@@ -24735,7 +24714,7 @@
       <c r="R638" s="145"/>
       <c r="S638" s="146"/>
     </row>
-    <row r="639" spans="1:19" ht="15.75">
+    <row r="639" spans="1:19" ht="15.6">
       <c r="A639" s="147">
         <v>99</v>
       </c>
@@ -24768,7 +24747,7 @@
       <c r="R639" s="103"/>
       <c r="S639" s="104"/>
     </row>
-    <row r="640" spans="1:19" ht="15.75">
+    <row r="640" spans="1:19" ht="15.6">
       <c r="B640" s="295" t="s">
         <v>745</v>
       </c>
@@ -24792,7 +24771,7 @@
       <c r="R640" s="119"/>
       <c r="S640" s="120"/>
     </row>
-    <row r="641" spans="1:19">
+    <row r="641" spans="1:19" ht="14.4">
       <c r="B641" s="247"/>
       <c r="C641" s="330"/>
       <c r="D641" s="331" t="s">
@@ -24814,7 +24793,7 @@
       <c r="R641" s="119"/>
       <c r="S641" s="120"/>
     </row>
-    <row r="642" spans="1:19" ht="15.75">
+    <row r="642" spans="1:19" ht="15.6">
       <c r="B642" s="310">
         <v>28820</v>
       </c>
@@ -24836,7 +24815,7 @@
       <c r="R642" s="119"/>
       <c r="S642" s="120"/>
     </row>
-    <row r="643" spans="1:19" ht="15.75">
+    <row r="643" spans="1:19" ht="15.6">
       <c r="B643" s="485" t="s">
         <v>601</v>
       </c>
@@ -24858,7 +24837,7 @@
       <c r="R643" s="388"/>
       <c r="S643" s="416"/>
     </row>
-    <row r="644" spans="1:19" ht="15.75">
+    <row r="644" spans="1:19" ht="15.6">
       <c r="A644" s="147">
         <v>100</v>
       </c>
@@ -24899,7 +24878,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="645" spans="1:19" ht="15.75">
+    <row r="645" spans="1:19" ht="15.6">
       <c r="B645" s="359" t="s">
         <v>746</v>
       </c>
@@ -24931,7 +24910,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="646" spans="1:19" ht="15.75">
+    <row r="646" spans="1:19" ht="15.6">
       <c r="B646" s="121"/>
       <c r="C646" s="38"/>
       <c r="D646" s="296"/>
@@ -24959,7 +24938,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="647" spans="1:19" ht="15.75">
+    <row r="647" spans="1:19" ht="15.6">
       <c r="B647" s="231">
         <v>22402</v>
       </c>
@@ -24987,7 +24966,7 @@
       </c>
       <c r="S647" s="160"/>
     </row>
-    <row r="648" spans="1:19" ht="15.75">
+    <row r="648" spans="1:19" ht="15.6">
       <c r="A648" s="183"/>
       <c r="B648" s="353" t="s">
         <v>750</v>
@@ -25012,13 +24991,13 @@
         <v>751</v>
       </c>
     </row>
-    <row r="649" spans="1:19">
-      <c r="A649" s="585">
+    <row r="649" spans="1:19" ht="14.4">
+      <c r="A649" s="585"/>
+    </row>
+    <row r="654" spans="1:19" ht="15.6">
+      <c r="A654" s="147">
         <v>101</v>
       </c>
-    </row>
-    <row r="654" spans="1:19" ht="15.75">
-      <c r="A654" s="147"/>
       <c r="B654" s="586" t="s">
         <v>535</v>
       </c>
@@ -25062,7 +25041,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="655" spans="1:19" ht="15.75">
+    <row r="655" spans="1:19" ht="15.6">
       <c r="B655" s="590" t="s">
         <v>757</v>
       </c>
@@ -25098,7 +25077,7 @@
       </c>
       <c r="S655" s="160"/>
     </row>
-    <row r="656" spans="1:19" ht="15.75">
+    <row r="656" spans="1:19" ht="15.6">
       <c r="B656" s="593"/>
       <c r="C656" s="593"/>
       <c r="D656" s="391"/>
@@ -25126,7 +25105,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="657" spans="1:19">
+    <row r="657" spans="1:19" ht="14.4">
       <c r="B657" s="594">
         <v>36121</v>
       </c>
@@ -25156,7 +25135,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="658" spans="1:19">
+    <row r="658" spans="1:19" ht="14.4">
       <c r="A658" s="133"/>
       <c r="B658" s="595" t="s">
         <v>766</v>
@@ -25185,116 +25164,379 @@
       <c r="R658" s="268"/>
       <c r="S658" s="171"/>
     </row>
-    <row r="659" spans="1:19">
-      <c r="A659" s="585">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="664" spans="1:19">
+    <row r="659" spans="1:19" ht="14.4">
+      <c r="A659" s="585"/>
+    </row>
+    <row r="662" spans="1:19" ht="15" customHeight="1">
+      <c r="A662" s="147">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="664" spans="1:19" ht="15.6">
       <c r="A664" s="147">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="669" spans="1:19">
-      <c r="A669" s="147">
         <v>103</v>
       </c>
-    </row>
-    <row r="674" spans="1:1">
+      <c r="B664" s="586"/>
+      <c r="C664" s="586"/>
+      <c r="D664" s="551"/>
+      <c r="E664" s="551"/>
+      <c r="F664" s="322"/>
+      <c r="G664" s="259"/>
+      <c r="H664" s="587"/>
+      <c r="I664" s="588"/>
+      <c r="J664" s="589"/>
+      <c r="K664" s="191"/>
+      <c r="L664" s="427"/>
+      <c r="M664" s="192"/>
+      <c r="N664" s="149"/>
+      <c r="O664" s="351"/>
+      <c r="P664" s="587"/>
+      <c r="Q664" s="190"/>
+      <c r="R664" s="149"/>
+      <c r="S664" s="147"/>
+    </row>
+    <row r="665" spans="1:19" ht="15" customHeight="1">
+      <c r="B665" s="590"/>
+      <c r="C665" s="591"/>
+      <c r="D665" s="391"/>
+      <c r="E665" s="391"/>
+      <c r="F665" s="122"/>
+      <c r="G665" s="122"/>
+      <c r="H665" s="148"/>
+      <c r="I665" s="314"/>
+      <c r="J665" s="148"/>
+      <c r="K665" s="197"/>
+      <c r="L665" s="202"/>
+      <c r="M665" s="219"/>
+      <c r="N665" s="109"/>
+      <c r="O665" s="148"/>
+      <c r="P665" s="148"/>
+      <c r="Q665" s="592"/>
+      <c r="R665" s="122"/>
+      <c r="S665" s="160"/>
+    </row>
+    <row r="666" spans="1:19" ht="15" customHeight="1">
+      <c r="B666" s="593"/>
+      <c r="C666" s="593"/>
+      <c r="D666" s="391"/>
+      <c r="E666" s="391"/>
+      <c r="F666" s="122"/>
+      <c r="G666" s="282"/>
+      <c r="H666" s="148"/>
+      <c r="I666" s="314"/>
+      <c r="J666" s="122"/>
+      <c r="K666" s="197"/>
+      <c r="L666" s="202"/>
+      <c r="M666" s="219"/>
+      <c r="N666" s="213"/>
+      <c r="O666" s="148"/>
+      <c r="P666" s="148"/>
+      <c r="Q666" s="592"/>
+      <c r="R666" s="148"/>
+      <c r="S666" s="160"/>
+    </row>
+    <row r="667" spans="1:19" ht="15" customHeight="1">
+      <c r="B667" s="594"/>
+      <c r="C667" s="581"/>
+      <c r="D667" s="263"/>
+      <c r="E667" s="309"/>
+      <c r="F667" s="581"/>
+      <c r="G667" s="282"/>
+      <c r="H667" s="122"/>
+      <c r="I667" s="314"/>
+      <c r="J667" s="148"/>
+      <c r="K667" s="197"/>
+      <c r="L667" s="202"/>
+      <c r="M667" s="158"/>
+      <c r="N667" s="213"/>
+      <c r="O667" s="337"/>
+      <c r="P667" s="148"/>
+      <c r="Q667" s="592"/>
+      <c r="R667" s="148"/>
+      <c r="S667" s="160"/>
+    </row>
+    <row r="668" spans="1:19" ht="15" customHeight="1">
+      <c r="A668" s="133"/>
+      <c r="B668" s="595"/>
+      <c r="C668" s="596"/>
+      <c r="D668" s="361"/>
+      <c r="E668" s="355"/>
+      <c r="F668" s="184"/>
+      <c r="G668" s="361"/>
+      <c r="H668" s="425"/>
+      <c r="I668" s="204"/>
+      <c r="J668" s="425"/>
+      <c r="K668" s="138"/>
+      <c r="L668" s="287"/>
+      <c r="M668" s="288"/>
+      <c r="N668" s="355"/>
+      <c r="O668" s="204"/>
+      <c r="P668" s="303"/>
+      <c r="Q668" s="395"/>
+      <c r="R668" s="268"/>
+      <c r="S668" s="171"/>
+    </row>
+    <row r="669" spans="1:19" ht="15.6">
+      <c r="B669" s="586" t="s">
+        <v>768</v>
+      </c>
+      <c r="C669" s="586" t="s">
+        <v>769</v>
+      </c>
+      <c r="D669" s="551" t="s">
+        <v>118</v>
+      </c>
+      <c r="E669" s="551"/>
+      <c r="F669" s="322">
+        <v>45979</v>
+      </c>
+      <c r="G669" s="259"/>
+      <c r="H669" s="587" t="s">
+        <v>752</v>
+      </c>
+      <c r="I669" s="588">
+        <v>35</v>
+      </c>
+      <c r="J669" s="589" t="s">
+        <v>753</v>
+      </c>
+      <c r="K669" s="191"/>
+      <c r="L669" s="427"/>
+      <c r="M669" s="192"/>
+      <c r="N669" s="149">
+        <v>46024</v>
+      </c>
+      <c r="O669" s="351" t="s">
+        <v>754</v>
+      </c>
+      <c r="P669" s="587"/>
+      <c r="Q669" s="190" t="s">
+        <v>755</v>
+      </c>
+      <c r="R669" s="149">
+        <v>46040</v>
+      </c>
+      <c r="S669" s="147" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="670" spans="1:19" ht="15" customHeight="1">
+      <c r="B670" s="590" t="s">
+        <v>770</v>
+      </c>
+      <c r="C670" s="591"/>
+      <c r="D670" s="391" t="s">
+        <v>30</v>
+      </c>
+      <c r="E670" s="391"/>
+      <c r="F670" s="122"/>
+      <c r="G670" s="122"/>
+      <c r="H670" s="148" t="s">
+        <v>758</v>
+      </c>
+      <c r="I670" s="314"/>
+      <c r="J670" s="148" t="s">
+        <v>759</v>
+      </c>
+      <c r="K670" s="197"/>
+      <c r="L670" s="202"/>
+      <c r="M670" s="219"/>
+      <c r="N670" s="109">
+        <v>46027</v>
+      </c>
+      <c r="O670" s="148" t="s">
+        <v>760</v>
+      </c>
+      <c r="P670" s="148"/>
+      <c r="Q670" s="592" t="s">
+        <v>761</v>
+      </c>
+      <c r="R670" s="122">
+        <v>45715</v>
+      </c>
+      <c r="S670" s="160"/>
+    </row>
+    <row r="671" spans="1:19" ht="15" customHeight="1">
+      <c r="B671" s="593"/>
+      <c r="C671" s="593"/>
+      <c r="D671" s="391"/>
+      <c r="E671" s="391"/>
+      <c r="F671" s="122"/>
+      <c r="G671" s="282"/>
+      <c r="H671" s="148" t="s">
+        <v>762</v>
+      </c>
+      <c r="I671" s="314"/>
+      <c r="J671" s="122">
+        <v>45989</v>
+      </c>
+      <c r="K671" s="197"/>
+      <c r="L671" s="202"/>
+      <c r="M671" s="219"/>
+      <c r="N671" s="213"/>
+      <c r="O671" s="148" t="s">
+        <v>763</v>
+      </c>
+      <c r="P671" s="148"/>
+      <c r="Q671" s="592"/>
+      <c r="R671" s="148"/>
+      <c r="S671" s="160" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="672" spans="1:19" ht="15" customHeight="1">
+      <c r="B672" s="594">
+        <v>36121</v>
+      </c>
+      <c r="C672" s="581"/>
+      <c r="D672" s="263"/>
+      <c r="E672" s="309"/>
+      <c r="F672" s="581"/>
+      <c r="G672" s="282"/>
+      <c r="H672" s="122">
+        <v>46017</v>
+      </c>
+      <c r="I672" s="314"/>
+      <c r="J672" s="148" t="s">
+        <v>764</v>
+      </c>
+      <c r="K672" s="197"/>
+      <c r="L672" s="202"/>
+      <c r="M672" s="158"/>
+      <c r="N672" s="213"/>
+      <c r="O672" s="337">
+        <v>46020</v>
+      </c>
+      <c r="P672" s="148"/>
+      <c r="Q672" s="592"/>
+      <c r="R672" s="148"/>
+      <c r="S672" s="160" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="673" spans="1:19" ht="15" customHeight="1">
+      <c r="B673" s="595" t="s">
+        <v>766</v>
+      </c>
+      <c r="C673" s="596"/>
+      <c r="D673" s="361"/>
+      <c r="E673" s="355"/>
+      <c r="F673" s="184"/>
+      <c r="G673" s="361"/>
+      <c r="H673" s="425" t="s">
+        <v>112</v>
+      </c>
+      <c r="I673" s="204"/>
+      <c r="J673" s="425" t="s">
+        <v>112</v>
+      </c>
+      <c r="K673" s="138"/>
+      <c r="L673" s="287"/>
+      <c r="M673" s="288"/>
+      <c r="N673" s="355"/>
+      <c r="O673" s="204" t="s">
+        <v>767</v>
+      </c>
+      <c r="P673" s="303"/>
+      <c r="Q673" s="395"/>
+      <c r="R673" s="268"/>
+      <c r="S673" s="171"/>
+    </row>
+    <row r="674" spans="1:19" ht="14.4">
       <c r="A674" s="147">
         <v>104</v>
       </c>
     </row>
-    <row r="679" spans="1:1">
+    <row r="679" spans="1:19" ht="14.4">
       <c r="A679" s="147">
         <v>105</v>
       </c>
     </row>
-    <row r="684" spans="1:1">
+    <row r="684" spans="1:19" ht="14.4">
       <c r="A684" s="147">
         <v>106</v>
       </c>
     </row>
-    <row r="689" spans="1:1">
+    <row r="689" spans="1:1" ht="14.4">
       <c r="A689" s="147"/>
     </row>
-    <row r="694" spans="1:1">
+    <row r="694" spans="1:1" ht="14.4">
       <c r="A694" s="147"/>
     </row>
-    <row r="699" spans="1:1">
+    <row r="699" spans="1:1" ht="14.4">
       <c r="A699" s="147"/>
     </row>
-    <row r="704" spans="1:1">
+    <row r="704" spans="1:1" ht="14.4">
       <c r="A704" s="147">
         <v>106</v>
       </c>
     </row>
-    <row r="709" spans="1:1">
+    <row r="709" spans="1:1" ht="14.4">
       <c r="A709" s="147">
         <v>107</v>
       </c>
     </row>
-    <row r="714" spans="1:1">
+    <row r="714" spans="1:1" ht="14.4">
       <c r="A714" s="147">
         <v>108</v>
       </c>
     </row>
-    <row r="719" spans="1:1">
+    <row r="719" spans="1:1" ht="14.4">
       <c r="A719" s="147">
         <v>109</v>
       </c>
     </row>
-    <row r="724" spans="1:1">
+    <row r="724" spans="1:1" ht="14.4">
       <c r="A724" s="147">
         <v>110</v>
       </c>
     </row>
-    <row r="729" spans="1:1">
+    <row r="729" spans="1:1" ht="14.4">
       <c r="A729" s="147"/>
     </row>
-    <row r="733" spans="1:1">
+    <row r="733" spans="1:1" ht="14.4">
       <c r="A733" s="133"/>
     </row>
-    <row r="739" spans="1:1">
+    <row r="739" spans="1:1" ht="14.4">
       <c r="A739" s="147"/>
     </row>
-    <row r="744" spans="1:1">
+    <row r="744" spans="1:1" ht="14.4">
       <c r="A744" s="147"/>
     </row>
-    <row r="748" spans="1:1">
+    <row r="748" spans="1:1" ht="14.4">
       <c r="A748" s="123"/>
     </row>
-    <row r="749" spans="1:1">
+    <row r="749" spans="1:1" ht="14.4">
       <c r="A749" s="147"/>
     </row>
-    <row r="754" spans="1:1">
+    <row r="754" spans="1:1" ht="14.4">
       <c r="A754" s="81"/>
     </row>
-    <row r="758" spans="1:1">
+    <row r="758" spans="1:1" ht="14.4">
       <c r="A758" s="133"/>
     </row>
-    <row r="763" spans="1:1">
+    <row r="763" spans="1:1" ht="14.4">
       <c r="A763" s="133"/>
     </row>
-    <row r="768" spans="1:1">
+    <row r="768" spans="1:1" ht="14.4">
       <c r="A768" s="133"/>
     </row>
-    <row r="773" spans="1:1">
+    <row r="773" spans="1:1" ht="14.4">
       <c r="A773" s="133"/>
     </row>
-    <row r="778" spans="1:1">
+    <row r="778" spans="1:1" ht="14.4">
       <c r="A778" s="133"/>
     </row>
-    <row r="783" spans="1:1">
+    <row r="783" spans="1:1" ht="14.4">
       <c r="A783" s="133"/>
     </row>
-    <row r="788" spans="1:1">
+    <row r="788" spans="1:1" ht="14.4">
       <c r="A788" s="133"/>
     </row>
-    <row r="793" spans="1:1">
+    <row r="793" spans="1:1" ht="14.4">
       <c r="A793" s="133"/>
     </row>
-    <row r="798" spans="1:1">
+    <row r="798" spans="1:1" ht="14.4">
       <c r="A798" s="147"/>
     </row>
   </sheetData>
